--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B61E17-3D76-4B70-BCB2-0B6904AF46CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7CD53A-3D5A-4525-96F1-5AD738C74078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="660" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="345" yWindow="1260" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -6840,7 +6840,7 @@
         <v>58</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -6966,7 +6966,7 @@
         <v>58</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -7092,7 +7092,7 @@
         <v>58</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -7218,7 +7218,7 @@
         <v>58</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -7344,7 +7344,7 @@
         <v>58</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -7470,7 +7470,7 @@
         <v>58</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -7596,7 +7596,7 @@
         <v>58</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -7722,7 +7722,7 @@
         <v>58</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -7848,7 +7848,7 @@
         <v>48</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -7974,7 +7974,7 @@
         <v>48</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -8100,7 +8100,7 @@
         <v>48</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -8226,7 +8226,7 @@
         <v>48</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -8856,7 +8856,7 @@
         <v>48</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>151</v>
       </c>
       <c r="F19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>263</v>
       </c>
       <c r="F30">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -10494,7 +10494,7 @@
         <v>116</v>
       </c>
       <c r="F31">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G31">
         <v>500</v>
@@ -10620,7 +10620,7 @@
         <v>116</v>
       </c>
       <c r="F32">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G32">
         <v>800</v>
@@ -10746,7 +10746,7 @@
         <v>50</v>
       </c>
       <c r="F33">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G33">
         <v>1200</v>
@@ -11277,7 +11277,7 @@
         <v>142</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -11403,7 +11403,7 @@
         <v>142</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -11529,7 +11529,7 @@
         <v>142</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -11655,7 +11655,7 @@
         <v>142</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -11781,7 +11781,7 @@
         <v>142</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -11907,7 +11907,7 @@
         <v>142</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -12033,7 +12033,7 @@
         <v>142</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -12159,7 +12159,7 @@
         <v>142</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -12285,7 +12285,7 @@
         <v>142</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -12411,7 +12411,7 @@
         <v>142</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -12537,7 +12537,7 @@
         <v>142</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -12663,7 +12663,7 @@
         <v>142</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -13293,7 +13293,7 @@
         <v>142</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>142</v>
       </c>
       <c r="F19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -14805,7 +14805,7 @@
         <v>142</v>
       </c>
       <c r="F30">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -14931,7 +14931,7 @@
         <v>142</v>
       </c>
       <c r="F31">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G31">
         <v>500</v>
@@ -15057,7 +15057,7 @@
         <v>142</v>
       </c>
       <c r="F32">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G32">
         <v>800</v>
@@ -15183,7 +15183,7 @@
         <v>142</v>
       </c>
       <c r="F33">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G33">
         <v>1200</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7CD53A-3D5A-4525-96F1-5AD738C74078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9596DDF-C665-4B42-A8A9-2266F61F1905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="1260" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="465" yWindow="1635" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9596DDF-C665-4B42-A8A9-2266F61F1905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE9C63C-06AF-471B-8C32-1F30FD287539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="465" yWindow="1635" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="345" yWindow="1260" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -7848,7 +7848,7 @@
         <v>48</v>
       </c>
       <c r="F10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -7974,7 +7974,7 @@
         <v>48</v>
       </c>
       <c r="F11">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -8226,7 +8226,7 @@
         <v>48</v>
       </c>
       <c r="F13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -8856,7 +8856,7 @@
         <v>48</v>
       </c>
       <c r="F18">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -9108,7 +9108,7 @@
         <v>151</v>
       </c>
       <c r="F20">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -9234,7 +9234,7 @@
         <v>151</v>
       </c>
       <c r="F21">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -12285,7 +12285,7 @@
         <v>142</v>
       </c>
       <c r="F10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -12411,7 +12411,7 @@
         <v>142</v>
       </c>
       <c r="F11">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -12663,7 +12663,7 @@
         <v>142</v>
       </c>
       <c r="F13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -13293,7 +13293,7 @@
         <v>142</v>
       </c>
       <c r="F18">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -13545,7 +13545,7 @@
         <v>142</v>
       </c>
       <c r="F20">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -13671,7 +13671,7 @@
         <v>142</v>
       </c>
       <c r="F21">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE9C63C-06AF-471B-8C32-1F30FD287539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D06799B-55B8-4585-B1EA-3E08AC9F3990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="1260" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2640" yWindow="1155" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="287">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -1704,6 +1704,10 @@
     <rPh sb="3" eb="4">
       <t>ミセ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kirakira_stone1</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -9777,7 +9781,7 @@
         <v>103</v>
       </c>
       <c r="S25" t="s">
-        <v>27</v>
+        <v>286</v>
       </c>
       <c r="T25" t="s">
         <v>194</v>
@@ -9798,10 +9802,10 @@
         <v>83</v>
       </c>
       <c r="Z25">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA25">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB25">
         <v>17</v>
@@ -9816,10 +9820,10 @@
         <v>10</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG25">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AH25">
         <v>0</v>
@@ -14214,7 +14218,7 @@
         <v>103</v>
       </c>
       <c r="S25" t="s">
-        <v>27</v>
+        <v>286</v>
       </c>
       <c r="T25" t="s">
         <v>194</v>
@@ -14235,10 +14239,10 @@
         <v>83</v>
       </c>
       <c r="Z25">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA25">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB25">
         <v>17</v>
@@ -14253,10 +14257,10 @@
         <v>10</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG25">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AH25">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D06799B-55B8-4585-B1EA-3E08AC9F3990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE576C7A-568C-4355-93E2-3796B18BAF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="1155" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2835" yWindow="1215" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE576C7A-568C-4355-93E2-3796B18BAF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA744D9-227D-49A3-A5DB-6115CDAE543A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="1215" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1230" yWindow="1050" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="286">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -1175,14 +1175,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Or_Emerald_Shop</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>オランジーナエメラルショップ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>MapBG_Ido</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1708,6 +1700,10 @@
   </si>
   <si>
     <t>kirakira_stone1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Or_EmeraldShop_A1</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2145,7 +2141,7 @@
         <v>98</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
@@ -2985,7 +2981,7 @@
         <v>89</v>
       </c>
       <c r="AN7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AO7">
         <v>0</v>
@@ -3111,7 +3107,7 @@
         <v>84</v>
       </c>
       <c r="AN8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AO8">
         <v>0</v>
@@ -3237,7 +3233,7 @@
         <v>84</v>
       </c>
       <c r="AN9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AO9">
         <v>0</v>
@@ -3363,7 +3359,7 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AO10">
         <v>0</v>
@@ -3489,7 +3485,7 @@
         <v>84</v>
       </c>
       <c r="AN11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -3615,7 +3611,7 @@
         <v>91</v>
       </c>
       <c r="AN12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -3741,7 +3737,7 @@
         <v>87</v>
       </c>
       <c r="AN13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -3867,7 +3863,7 @@
         <v>88</v>
       </c>
       <c r="AN14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -3993,7 +3989,7 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -4119,7 +4115,7 @@
         <v>84</v>
       </c>
       <c r="AN16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -4245,7 +4241,7 @@
         <v>84</v>
       </c>
       <c r="AN17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO17">
         <v>0</v>
@@ -4371,7 +4367,7 @@
         <v>84</v>
       </c>
       <c r="AN18" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO18">
         <v>1</v>
@@ -4441,7 +4437,7 @@
         <v>98</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
@@ -5281,7 +5277,7 @@
         <v>89</v>
       </c>
       <c r="AN7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AO7">
         <v>0</v>
@@ -5407,7 +5403,7 @@
         <v>84</v>
       </c>
       <c r="AN8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AO8">
         <v>0</v>
@@ -5533,7 +5529,7 @@
         <v>84</v>
       </c>
       <c r="AN9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AO9">
         <v>0</v>
@@ -5659,7 +5655,7 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AO10">
         <v>0</v>
@@ -5785,7 +5781,7 @@
         <v>84</v>
       </c>
       <c r="AN11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -5911,7 +5907,7 @@
         <v>91</v>
       </c>
       <c r="AN12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -6037,7 +6033,7 @@
         <v>87</v>
       </c>
       <c r="AN13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -6163,7 +6159,7 @@
         <v>88</v>
       </c>
       <c r="AN14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -6289,7 +6285,7 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -6415,7 +6411,7 @@
         <v>84</v>
       </c>
       <c r="AN16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -6541,7 +6537,7 @@
         <v>84</v>
       </c>
       <c r="AN17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO17">
         <v>0</v>
@@ -6667,7 +6663,7 @@
         <v>84</v>
       </c>
       <c r="AN18" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO18">
         <v>1</v>
@@ -6736,7 +6732,7 @@
         <v>98</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
@@ -6838,7 +6834,7 @@
         <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E2" t="s">
         <v>58</v>
@@ -6958,13 +6954,13 @@
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C3" t="s">
         <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E3" t="s">
         <v>58</v>
@@ -7084,13 +7080,13 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C4" t="s">
         <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E4" t="s">
         <v>58</v>
@@ -7210,13 +7206,13 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C5" t="s">
         <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E5" t="s">
         <v>58</v>
@@ -7588,7 +7584,7 @@
         <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C8" t="s">
         <v>169</v>
@@ -7840,7 +7836,7 @@
         <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C10" t="s">
         <v>174</v>
@@ -7864,7 +7860,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -7954,7 +7950,7 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO10">
         <v>0</v>
@@ -7966,7 +7962,7 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C11" t="s">
         <v>176</v>
@@ -7990,7 +7986,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -8080,7 +8076,7 @@
         <v>84</v>
       </c>
       <c r="AN11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -8092,7 +8088,7 @@
         <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C12" t="s">
         <v>177</v>
@@ -8116,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -8206,7 +8202,7 @@
         <v>84</v>
       </c>
       <c r="AN12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -8218,7 +8214,7 @@
         <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C13" t="s">
         <v>178</v>
@@ -8242,7 +8238,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -8332,7 +8328,7 @@
         <v>84</v>
       </c>
       <c r="AN13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -8344,13 +8340,13 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D14" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E14" t="s">
         <v>48</v>
@@ -8458,7 +8454,7 @@
         <v>84</v>
       </c>
       <c r="AN14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -8470,13 +8466,13 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C15" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D15" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E15" t="s">
         <v>48</v>
@@ -8584,7 +8580,7 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -8596,13 +8592,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C16" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D16" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E16" t="s">
         <v>48</v>
@@ -8710,7 +8706,7 @@
         <v>84</v>
       </c>
       <c r="AN16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -8722,13 +8718,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C17" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D17" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E17" t="s">
         <v>48</v>
@@ -8836,7 +8832,7 @@
         <v>84</v>
       </c>
       <c r="AN17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO17">
         <v>0</v>
@@ -8848,13 +8844,13 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C18" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D18" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E18" t="s">
         <v>48</v>
@@ -8962,7 +8958,7 @@
         <v>84</v>
       </c>
       <c r="AN18" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO18">
         <v>0</v>
@@ -9100,13 +9096,13 @@
         <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C20" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D20" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E20" t="s">
         <v>151</v>
@@ -9352,13 +9348,13 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C22" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D22" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
@@ -9481,10 +9477,10 @@
         <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>183</v>
+        <v>285</v>
       </c>
       <c r="D23" t="s">
-        <v>184</v>
+        <v>140</v>
       </c>
       <c r="E23" t="s">
         <v>94</v>
@@ -9607,7 +9603,7 @@
         <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D24" t="s">
         <v>152</v>
@@ -9718,7 +9714,7 @@
         <v>89</v>
       </c>
       <c r="AN24" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -9730,7 +9726,7 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C25" t="s">
         <v>182</v>
@@ -9781,10 +9777,10 @@
         <v>103</v>
       </c>
       <c r="S25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="T25" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="U25" t="s">
         <v>27</v>
@@ -9844,7 +9840,7 @@
         <v>84</v>
       </c>
       <c r="AN25" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AO25">
         <v>0</v>
@@ -9856,13 +9852,13 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C26" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D26" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E26" t="s">
         <v>116</v>
@@ -9898,7 +9894,7 @@
         <v>73</v>
       </c>
       <c r="P26" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Q26" t="s">
         <v>113</v>
@@ -9922,7 +9918,7 @@
         <v>27</v>
       </c>
       <c r="X26" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="Y26" t="s">
         <v>136</v>
@@ -9970,7 +9966,7 @@
         <v>91</v>
       </c>
       <c r="AN26" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -9982,13 +9978,13 @@
         <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C27" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D27" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E27" t="s">
         <v>50</v>
@@ -10051,7 +10047,7 @@
         <v>111</v>
       </c>
       <c r="Y27" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Z27">
         <v>25</v>
@@ -10096,7 +10092,7 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -10108,13 +10104,13 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C28" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D28" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E28" t="s">
         <v>116</v>
@@ -10162,10 +10158,10 @@
         <v>74</v>
       </c>
       <c r="T28" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="U28" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="V28" t="s">
         <v>27</v>
@@ -10222,7 +10218,7 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -10234,13 +10230,13 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C29" t="s">
         <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E29" t="s">
         <v>50</v>
@@ -10270,10 +10266,10 @@
         <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="O29" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="P29" t="s">
         <v>25</v>
@@ -10282,10 +10278,10 @@
         <v>137</v>
       </c>
       <c r="R29" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="S29" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="T29" t="s">
         <v>27</v>
@@ -10300,10 +10296,10 @@
         <v>27</v>
       </c>
       <c r="X29" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Y29" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="Z29">
         <v>20</v>
@@ -10348,7 +10344,7 @@
         <v>84</v>
       </c>
       <c r="AN29" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -10360,16 +10356,16 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C30" t="s">
+        <v>260</v>
+      </c>
+      <c r="D30" t="s">
         <v>262</v>
       </c>
-      <c r="D30" t="s">
-        <v>264</v>
-      </c>
       <c r="E30" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F30">
         <v>60</v>
@@ -10396,7 +10392,7 @@
         <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="O30" t="s">
         <v>27</v>
@@ -10426,7 +10422,7 @@
         <v>27</v>
       </c>
       <c r="X30" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Y30" t="s">
         <v>27</v>
@@ -10474,7 +10470,7 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -10486,13 +10482,13 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C31" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D31" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E31" t="s">
         <v>116</v>
@@ -10522,10 +10518,10 @@
         <v>26</v>
       </c>
       <c r="N31" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O31" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P31" t="s">
         <v>138</v>
@@ -10534,7 +10530,7 @@
         <v>110</v>
       </c>
       <c r="R31" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="S31" t="s">
         <v>27</v>
@@ -10543,7 +10539,7 @@
         <v>129</v>
       </c>
       <c r="U31" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -10552,10 +10548,10 @@
         <v>27</v>
       </c>
       <c r="X31" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Y31" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Z31">
         <v>20</v>
@@ -10600,7 +10596,7 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -10612,13 +10608,13 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C32" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D32" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E32" t="s">
         <v>116</v>
@@ -10648,13 +10644,13 @@
         <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="O32" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="P32" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Q32" t="s">
         <v>70</v>
@@ -10678,7 +10674,7 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Y32" t="s">
         <v>27</v>
@@ -10726,7 +10722,7 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -10738,13 +10734,13 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C33" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D33" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E33" t="s">
         <v>50</v>
@@ -10774,40 +10770,40 @@
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="O33" t="s">
+        <v>233</v>
+      </c>
+      <c r="P33" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>220</v>
+      </c>
+      <c r="R33" t="s">
+        <v>27</v>
+      </c>
+      <c r="S33" t="s">
+        <v>27</v>
+      </c>
+      <c r="T33" t="s">
+        <v>27</v>
+      </c>
+      <c r="U33" t="s">
+        <v>27</v>
+      </c>
+      <c r="V33" t="s">
+        <v>27</v>
+      </c>
+      <c r="W33" t="s">
+        <v>27</v>
+      </c>
+      <c r="X33" t="s">
         <v>235</v>
       </c>
-      <c r="P33" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>222</v>
-      </c>
-      <c r="R33" t="s">
-        <v>27</v>
-      </c>
-      <c r="S33" t="s">
-        <v>27</v>
-      </c>
-      <c r="T33" t="s">
-        <v>27</v>
-      </c>
-      <c r="U33" t="s">
-        <v>27</v>
-      </c>
-      <c r="V33" t="s">
-        <v>27</v>
-      </c>
-      <c r="W33" t="s">
-        <v>27</v>
-      </c>
-      <c r="X33" t="s">
-        <v>237</v>
-      </c>
       <c r="Y33" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Z33">
         <v>40</v>
@@ -10852,7 +10848,7 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -10978,7 +10974,7 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -11104,7 +11100,7 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO35">
         <v>1</v>
@@ -11173,7 +11169,7 @@
         <v>98</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
@@ -11275,7 +11271,7 @@
         <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E2" t="s">
         <v>142</v>
@@ -11395,13 +11391,13 @@
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C3" t="s">
         <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E3" t="s">
         <v>142</v>
@@ -11521,13 +11517,13 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C4" t="s">
         <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E4" t="s">
         <v>142</v>
@@ -11647,13 +11643,13 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C5" t="s">
         <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E5" t="s">
         <v>142</v>
@@ -12025,7 +12021,7 @@
         <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C8" t="s">
         <v>169</v>
@@ -12277,7 +12273,7 @@
         <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C10" t="s">
         <v>174</v>
@@ -12391,7 +12387,7 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO10">
         <v>0</v>
@@ -12403,7 +12399,7 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C11" t="s">
         <v>176</v>
@@ -12517,7 +12513,7 @@
         <v>84</v>
       </c>
       <c r="AN11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -12529,7 +12525,7 @@
         <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C12" t="s">
         <v>177</v>
@@ -12643,7 +12639,7 @@
         <v>84</v>
       </c>
       <c r="AN12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -12655,7 +12651,7 @@
         <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C13" t="s">
         <v>178</v>
@@ -12769,7 +12765,7 @@
         <v>84</v>
       </c>
       <c r="AN13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -12781,13 +12777,13 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D14" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E14" t="s">
         <v>142</v>
@@ -12895,7 +12891,7 @@
         <v>84</v>
       </c>
       <c r="AN14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -12907,13 +12903,13 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C15" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D15" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E15" t="s">
         <v>142</v>
@@ -13021,7 +13017,7 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -13033,13 +13029,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C16" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D16" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E16" t="s">
         <v>142</v>
@@ -13147,7 +13143,7 @@
         <v>84</v>
       </c>
       <c r="AN16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -13159,13 +13155,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C17" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D17" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E17" t="s">
         <v>142</v>
@@ -13273,7 +13269,7 @@
         <v>84</v>
       </c>
       <c r="AN17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO17">
         <v>0</v>
@@ -13285,13 +13281,13 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C18" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D18" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E18" t="s">
         <v>142</v>
@@ -13399,7 +13395,7 @@
         <v>84</v>
       </c>
       <c r="AN18" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO18">
         <v>0</v>
@@ -13537,13 +13533,13 @@
         <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C20" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D20" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E20" t="s">
         <v>142</v>
@@ -13789,13 +13785,13 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C22" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D22" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E22" t="s">
         <v>142</v>
@@ -13918,10 +13914,10 @@
         <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>183</v>
+        <v>285</v>
       </c>
       <c r="D23" t="s">
-        <v>184</v>
+        <v>140</v>
       </c>
       <c r="E23" t="s">
         <v>142</v>
@@ -14044,7 +14040,7 @@
         <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D24" t="s">
         <v>152</v>
@@ -14155,7 +14151,7 @@
         <v>89</v>
       </c>
       <c r="AN24" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -14167,7 +14163,7 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C25" t="s">
         <v>182</v>
@@ -14218,10 +14214,10 @@
         <v>103</v>
       </c>
       <c r="S25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="T25" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="U25" t="s">
         <v>27</v>
@@ -14281,7 +14277,7 @@
         <v>84</v>
       </c>
       <c r="AN25" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AO25">
         <v>0</v>
@@ -14293,13 +14289,13 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C26" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D26" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E26" t="s">
         <v>142</v>
@@ -14335,7 +14331,7 @@
         <v>73</v>
       </c>
       <c r="P26" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Q26" t="s">
         <v>113</v>
@@ -14359,7 +14355,7 @@
         <v>27</v>
       </c>
       <c r="X26" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="Y26" t="s">
         <v>136</v>
@@ -14407,7 +14403,7 @@
         <v>91</v>
       </c>
       <c r="AN26" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -14419,13 +14415,13 @@
         <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C27" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D27" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E27" t="s">
         <v>142</v>
@@ -14488,7 +14484,7 @@
         <v>111</v>
       </c>
       <c r="Y27" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Z27">
         <v>25</v>
@@ -14533,7 +14529,7 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -14545,13 +14541,13 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C28" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D28" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E28" t="s">
         <v>142</v>
@@ -14599,10 +14595,10 @@
         <v>74</v>
       </c>
       <c r="T28" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="U28" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="V28" t="s">
         <v>27</v>
@@ -14659,7 +14655,7 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -14671,13 +14667,13 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C29" t="s">
         <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E29" t="s">
         <v>142</v>
@@ -14707,10 +14703,10 @@
         <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="O29" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="P29" t="s">
         <v>25</v>
@@ -14719,10 +14715,10 @@
         <v>137</v>
       </c>
       <c r="R29" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="S29" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="T29" t="s">
         <v>27</v>
@@ -14737,10 +14733,10 @@
         <v>27</v>
       </c>
       <c r="X29" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Y29" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="Z29">
         <v>20</v>
@@ -14785,7 +14781,7 @@
         <v>84</v>
       </c>
       <c r="AN29" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -14797,13 +14793,13 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C30" t="s">
+        <v>260</v>
+      </c>
+      <c r="D30" t="s">
         <v>262</v>
-      </c>
-      <c r="D30" t="s">
-        <v>264</v>
       </c>
       <c r="E30" t="s">
         <v>142</v>
@@ -14833,7 +14829,7 @@
         <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="O30" t="s">
         <v>27</v>
@@ -14863,7 +14859,7 @@
         <v>27</v>
       </c>
       <c r="X30" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Y30" t="s">
         <v>27</v>
@@ -14911,7 +14907,7 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -14923,13 +14919,13 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C31" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D31" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E31" t="s">
         <v>142</v>
@@ -14959,10 +14955,10 @@
         <v>26</v>
       </c>
       <c r="N31" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O31" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P31" t="s">
         <v>138</v>
@@ -14971,7 +14967,7 @@
         <v>110</v>
       </c>
       <c r="R31" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="S31" t="s">
         <v>27</v>
@@ -14980,7 +14976,7 @@
         <v>129</v>
       </c>
       <c r="U31" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -14989,10 +14985,10 @@
         <v>27</v>
       </c>
       <c r="X31" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Y31" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Z31">
         <v>20</v>
@@ -15037,7 +15033,7 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -15049,13 +15045,13 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C32" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D32" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E32" t="s">
         <v>142</v>
@@ -15085,13 +15081,13 @@
         <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="O32" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="P32" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Q32" t="s">
         <v>70</v>
@@ -15115,7 +15111,7 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Y32" t="s">
         <v>27</v>
@@ -15163,7 +15159,7 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -15175,13 +15171,13 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C33" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D33" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E33" t="s">
         <v>142</v>
@@ -15211,40 +15207,40 @@
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="O33" t="s">
+        <v>233</v>
+      </c>
+      <c r="P33" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>220</v>
+      </c>
+      <c r="R33" t="s">
+        <v>27</v>
+      </c>
+      <c r="S33" t="s">
+        <v>27</v>
+      </c>
+      <c r="T33" t="s">
+        <v>27</v>
+      </c>
+      <c r="U33" t="s">
+        <v>27</v>
+      </c>
+      <c r="V33" t="s">
+        <v>27</v>
+      </c>
+      <c r="W33" t="s">
+        <v>27</v>
+      </c>
+      <c r="X33" t="s">
         <v>235</v>
       </c>
-      <c r="P33" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>222</v>
-      </c>
-      <c r="R33" t="s">
-        <v>27</v>
-      </c>
-      <c r="S33" t="s">
-        <v>27</v>
-      </c>
-      <c r="T33" t="s">
-        <v>27</v>
-      </c>
-      <c r="U33" t="s">
-        <v>27</v>
-      </c>
-      <c r="V33" t="s">
-        <v>27</v>
-      </c>
-      <c r="W33" t="s">
-        <v>27</v>
-      </c>
-      <c r="X33" t="s">
-        <v>237</v>
-      </c>
       <c r="Y33" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Z33">
         <v>40</v>
@@ -15289,7 +15285,7 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -15415,7 +15411,7 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -15541,7 +15537,7 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AO35">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA744D9-227D-49A3-A5DB-6115CDAE543A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F113DB-3495-47C0-8747-0BCFE9541510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1230" yWindow="1050" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2730" yWindow="1080" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -1104,13 +1104,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>さんま亭</t>
-    <rPh sb="3" eb="4">
-      <t>テイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ふぐなべ亭</t>
     <rPh sb="4" eb="5">
       <t>テイ</t>
@@ -1704,6 +1697,10 @@
   </si>
   <si>
     <t>Or_EmeraldShop_A1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BARアズール</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2141,7 +2138,7 @@
         <v>98</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
@@ -2981,7 +2978,7 @@
         <v>89</v>
       </c>
       <c r="AN7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AO7">
         <v>0</v>
@@ -3107,7 +3104,7 @@
         <v>84</v>
       </c>
       <c r="AN8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AO8">
         <v>0</v>
@@ -3233,7 +3230,7 @@
         <v>84</v>
       </c>
       <c r="AN9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AO9">
         <v>0</v>
@@ -3359,7 +3356,7 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AO10">
         <v>0</v>
@@ -3485,7 +3482,7 @@
         <v>84</v>
       </c>
       <c r="AN11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -3611,7 +3608,7 @@
         <v>91</v>
       </c>
       <c r="AN12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -3737,7 +3734,7 @@
         <v>87</v>
       </c>
       <c r="AN13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -3863,7 +3860,7 @@
         <v>88</v>
       </c>
       <c r="AN14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -3989,7 +3986,7 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -4115,7 +4112,7 @@
         <v>84</v>
       </c>
       <c r="AN16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -4241,7 +4238,7 @@
         <v>84</v>
       </c>
       <c r="AN17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO17">
         <v>0</v>
@@ -4367,7 +4364,7 @@
         <v>84</v>
       </c>
       <c r="AN18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO18">
         <v>1</v>
@@ -4437,7 +4434,7 @@
         <v>98</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
@@ -5277,7 +5274,7 @@
         <v>89</v>
       </c>
       <c r="AN7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AO7">
         <v>0</v>
@@ -5403,7 +5400,7 @@
         <v>84</v>
       </c>
       <c r="AN8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AO8">
         <v>0</v>
@@ -5529,7 +5526,7 @@
         <v>84</v>
       </c>
       <c r="AN9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AO9">
         <v>0</v>
@@ -5655,7 +5652,7 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AO10">
         <v>0</v>
@@ -5781,7 +5778,7 @@
         <v>84</v>
       </c>
       <c r="AN11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -5907,7 +5904,7 @@
         <v>91</v>
       </c>
       <c r="AN12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -6033,7 +6030,7 @@
         <v>87</v>
       </c>
       <c r="AN13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -6159,7 +6156,7 @@
         <v>88</v>
       </c>
       <c r="AN14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -6285,7 +6282,7 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -6411,7 +6408,7 @@
         <v>84</v>
       </c>
       <c r="AN16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -6537,7 +6534,7 @@
         <v>84</v>
       </c>
       <c r="AN17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO17">
         <v>0</v>
@@ -6663,7 +6660,7 @@
         <v>84</v>
       </c>
       <c r="AN18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO18">
         <v>1</v>
@@ -6732,7 +6729,7 @@
         <v>98</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
@@ -6834,7 +6831,7 @@
         <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
         <v>58</v>
@@ -6954,13 +6951,13 @@
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" t="s">
         <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E3" t="s">
         <v>58</v>
@@ -7080,13 +7077,13 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C4" t="s">
         <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E4" t="s">
         <v>58</v>
@@ -7206,13 +7203,13 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C5" t="s">
         <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E5" t="s">
         <v>58</v>
@@ -7338,7 +7335,7 @@
         <v>156</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E6" t="s">
         <v>58</v>
@@ -7584,13 +7581,13 @@
         <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C8" t="s">
         <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>172</v>
+        <v>285</v>
       </c>
       <c r="E8" t="s">
         <v>58</v>
@@ -7716,7 +7713,7 @@
         <v>170</v>
       </c>
       <c r="D9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E9" t="s">
         <v>58</v>
@@ -7836,10 +7833,10 @@
         <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" t="s">
         <v>157</v>
@@ -7950,7 +7947,7 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO10">
         <v>0</v>
@@ -7962,13 +7959,13 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E11" t="s">
         <v>48</v>
@@ -8076,7 +8073,7 @@
         <v>84</v>
       </c>
       <c r="AN11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -8088,13 +8085,13 @@
         <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
@@ -8202,7 +8199,7 @@
         <v>84</v>
       </c>
       <c r="AN12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -8214,13 +8211,13 @@
         <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E13" t="s">
         <v>48</v>
@@ -8328,7 +8325,7 @@
         <v>84</v>
       </c>
       <c r="AN13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -8340,13 +8337,13 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E14" t="s">
         <v>48</v>
@@ -8454,7 +8451,7 @@
         <v>84</v>
       </c>
       <c r="AN14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -8466,13 +8463,13 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E15" t="s">
         <v>48</v>
@@ -8580,7 +8577,7 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -8592,13 +8589,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E16" t="s">
         <v>48</v>
@@ -8706,7 +8703,7 @@
         <v>84</v>
       </c>
       <c r="AN16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -8718,13 +8715,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C17" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E17" t="s">
         <v>48</v>
@@ -8832,7 +8829,7 @@
         <v>84</v>
       </c>
       <c r="AN17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO17">
         <v>0</v>
@@ -8844,13 +8841,13 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C18" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E18" t="s">
         <v>48</v>
@@ -8958,7 +8955,7 @@
         <v>84</v>
       </c>
       <c r="AN18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO18">
         <v>0</v>
@@ -9096,13 +9093,13 @@
         <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E20" t="s">
         <v>151</v>
@@ -9348,13 +9345,13 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
@@ -9477,7 +9474,7 @@
         <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D23" t="s">
         <v>140</v>
@@ -9603,7 +9600,7 @@
         <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D24" t="s">
         <v>152</v>
@@ -9714,7 +9711,7 @@
         <v>89</v>
       </c>
       <c r="AN24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -9726,10 +9723,10 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D25" t="s">
         <v>153</v>
@@ -9777,10 +9774,10 @@
         <v>103</v>
       </c>
       <c r="S25" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="T25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U25" t="s">
         <v>27</v>
@@ -9840,7 +9837,7 @@
         <v>84</v>
       </c>
       <c r="AN25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AO25">
         <v>0</v>
@@ -9852,13 +9849,13 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E26" t="s">
         <v>116</v>
@@ -9894,7 +9891,7 @@
         <v>73</v>
       </c>
       <c r="P26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q26" t="s">
         <v>113</v>
@@ -9918,7 +9915,7 @@
         <v>27</v>
       </c>
       <c r="X26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y26" t="s">
         <v>136</v>
@@ -9966,7 +9963,7 @@
         <v>91</v>
       </c>
       <c r="AN26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -9978,13 +9975,13 @@
         <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E27" t="s">
         <v>50</v>
@@ -10047,7 +10044,7 @@
         <v>111</v>
       </c>
       <c r="Y27" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Z27">
         <v>25</v>
@@ -10092,7 +10089,7 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -10104,13 +10101,13 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E28" t="s">
         <v>116</v>
@@ -10158,10 +10155,10 @@
         <v>74</v>
       </c>
       <c r="T28" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="U28" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="V28" t="s">
         <v>27</v>
@@ -10218,7 +10215,7 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -10230,13 +10227,13 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C29" t="s">
         <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E29" t="s">
         <v>50</v>
@@ -10266,10 +10263,10 @@
         <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O29" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P29" t="s">
         <v>25</v>
@@ -10278,10 +10275,10 @@
         <v>137</v>
       </c>
       <c r="R29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S29" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="T29" t="s">
         <v>27</v>
@@ -10296,10 +10293,10 @@
         <v>27</v>
       </c>
       <c r="X29" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y29" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Z29">
         <v>20</v>
@@ -10344,7 +10341,7 @@
         <v>84</v>
       </c>
       <c r="AN29" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -10356,16 +10353,16 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C30" t="s">
+        <v>259</v>
+      </c>
+      <c r="D30" t="s">
+        <v>261</v>
+      </c>
+      <c r="E30" t="s">
         <v>260</v>
-      </c>
-      <c r="D30" t="s">
-        <v>262</v>
-      </c>
-      <c r="E30" t="s">
-        <v>261</v>
       </c>
       <c r="F30">
         <v>60</v>
@@ -10392,7 +10389,7 @@
         <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O30" t="s">
         <v>27</v>
@@ -10422,7 +10419,7 @@
         <v>27</v>
       </c>
       <c r="X30" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y30" t="s">
         <v>27</v>
@@ -10470,7 +10467,7 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -10482,13 +10479,13 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C31" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E31" t="s">
         <v>116</v>
@@ -10518,10 +10515,10 @@
         <v>26</v>
       </c>
       <c r="N31" t="s">
+        <v>215</v>
+      </c>
+      <c r="O31" t="s">
         <v>216</v>
-      </c>
-      <c r="O31" t="s">
-        <v>217</v>
       </c>
       <c r="P31" t="s">
         <v>138</v>
@@ -10530,7 +10527,7 @@
         <v>110</v>
       </c>
       <c r="R31" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S31" t="s">
         <v>27</v>
@@ -10539,7 +10536,7 @@
         <v>129</v>
       </c>
       <c r="U31" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -10548,10 +10545,10 @@
         <v>27</v>
       </c>
       <c r="X31" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Y31" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Z31">
         <v>20</v>
@@ -10596,7 +10593,7 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -10608,13 +10605,13 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D32" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E32" t="s">
         <v>116</v>
@@ -10644,13 +10641,13 @@
         <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P32" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q32" t="s">
         <v>70</v>
@@ -10674,7 +10671,7 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y32" t="s">
         <v>27</v>
@@ -10722,7 +10719,7 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -10734,13 +10731,13 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D33" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E33" t="s">
         <v>50</v>
@@ -10770,40 +10767,40 @@
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O33" t="s">
+        <v>232</v>
+      </c>
+      <c r="P33" t="s">
         <v>233</v>
       </c>
-      <c r="P33" t="s">
+      <c r="Q33" t="s">
+        <v>219</v>
+      </c>
+      <c r="R33" t="s">
+        <v>27</v>
+      </c>
+      <c r="S33" t="s">
+        <v>27</v>
+      </c>
+      <c r="T33" t="s">
+        <v>27</v>
+      </c>
+      <c r="U33" t="s">
+        <v>27</v>
+      </c>
+      <c r="V33" t="s">
+        <v>27</v>
+      </c>
+      <c r="W33" t="s">
+        <v>27</v>
+      </c>
+      <c r="X33" t="s">
         <v>234</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="Y33" t="s">
         <v>220</v>
-      </c>
-      <c r="R33" t="s">
-        <v>27</v>
-      </c>
-      <c r="S33" t="s">
-        <v>27</v>
-      </c>
-      <c r="T33" t="s">
-        <v>27</v>
-      </c>
-      <c r="U33" t="s">
-        <v>27</v>
-      </c>
-      <c r="V33" t="s">
-        <v>27</v>
-      </c>
-      <c r="W33" t="s">
-        <v>27</v>
-      </c>
-      <c r="X33" t="s">
-        <v>235</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>221</v>
       </c>
       <c r="Z33">
         <v>40</v>
@@ -10848,7 +10845,7 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -10974,7 +10971,7 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -11100,7 +11097,7 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO35">
         <v>1</v>
@@ -11169,7 +11166,7 @@
         <v>98</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
@@ -11271,7 +11268,7 @@
         <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
         <v>142</v>
@@ -11391,13 +11388,13 @@
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" t="s">
         <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E3" t="s">
         <v>142</v>
@@ -11517,13 +11514,13 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C4" t="s">
         <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E4" t="s">
         <v>142</v>
@@ -11643,13 +11640,13 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C5" t="s">
         <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E5" t="s">
         <v>142</v>
@@ -11775,7 +11772,7 @@
         <v>156</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E6" t="s">
         <v>142</v>
@@ -12021,13 +12018,13 @@
         <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C8" t="s">
         <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>172</v>
+        <v>285</v>
       </c>
       <c r="E8" t="s">
         <v>142</v>
@@ -12153,7 +12150,7 @@
         <v>170</v>
       </c>
       <c r="D9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E9" t="s">
         <v>142</v>
@@ -12273,10 +12270,10 @@
         <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" t="s">
         <v>157</v>
@@ -12387,7 +12384,7 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO10">
         <v>0</v>
@@ -12399,13 +12396,13 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E11" t="s">
         <v>142</v>
@@ -12513,7 +12510,7 @@
         <v>84</v>
       </c>
       <c r="AN11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -12525,13 +12522,13 @@
         <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E12" t="s">
         <v>142</v>
@@ -12639,7 +12636,7 @@
         <v>84</v>
       </c>
       <c r="AN12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -12651,13 +12648,13 @@
         <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E13" t="s">
         <v>142</v>
@@ -12765,7 +12762,7 @@
         <v>84</v>
       </c>
       <c r="AN13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -12777,13 +12774,13 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E14" t="s">
         <v>142</v>
@@ -12891,7 +12888,7 @@
         <v>84</v>
       </c>
       <c r="AN14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -12903,13 +12900,13 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E15" t="s">
         <v>142</v>
@@ -13017,7 +13014,7 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -13029,13 +13026,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E16" t="s">
         <v>142</v>
@@ -13143,7 +13140,7 @@
         <v>84</v>
       </c>
       <c r="AN16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -13155,13 +13152,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C17" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E17" t="s">
         <v>142</v>
@@ -13269,7 +13266,7 @@
         <v>84</v>
       </c>
       <c r="AN17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO17">
         <v>0</v>
@@ -13281,13 +13278,13 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C18" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E18" t="s">
         <v>142</v>
@@ -13395,7 +13392,7 @@
         <v>84</v>
       </c>
       <c r="AN18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO18">
         <v>0</v>
@@ -13533,13 +13530,13 @@
         <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E20" t="s">
         <v>142</v>
@@ -13785,13 +13782,13 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E22" t="s">
         <v>142</v>
@@ -13914,7 +13911,7 @@
         <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D23" t="s">
         <v>140</v>
@@ -14040,7 +14037,7 @@
         <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D24" t="s">
         <v>152</v>
@@ -14151,7 +14148,7 @@
         <v>89</v>
       </c>
       <c r="AN24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -14163,10 +14160,10 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D25" t="s">
         <v>153</v>
@@ -14214,10 +14211,10 @@
         <v>103</v>
       </c>
       <c r="S25" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="T25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U25" t="s">
         <v>27</v>
@@ -14277,7 +14274,7 @@
         <v>84</v>
       </c>
       <c r="AN25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AO25">
         <v>0</v>
@@ -14289,13 +14286,13 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E26" t="s">
         <v>142</v>
@@ -14331,7 +14328,7 @@
         <v>73</v>
       </c>
       <c r="P26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q26" t="s">
         <v>113</v>
@@ -14355,7 +14352,7 @@
         <v>27</v>
       </c>
       <c r="X26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y26" t="s">
         <v>136</v>
@@ -14403,7 +14400,7 @@
         <v>91</v>
       </c>
       <c r="AN26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -14415,13 +14412,13 @@
         <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E27" t="s">
         <v>142</v>
@@ -14484,7 +14481,7 @@
         <v>111</v>
       </c>
       <c r="Y27" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Z27">
         <v>25</v>
@@ -14529,7 +14526,7 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -14541,13 +14538,13 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E28" t="s">
         <v>142</v>
@@ -14595,10 +14592,10 @@
         <v>74</v>
       </c>
       <c r="T28" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="U28" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="V28" t="s">
         <v>27</v>
@@ -14655,7 +14652,7 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -14667,13 +14664,13 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C29" t="s">
         <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E29" t="s">
         <v>142</v>
@@ -14703,10 +14700,10 @@
         <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O29" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P29" t="s">
         <v>25</v>
@@ -14715,10 +14712,10 @@
         <v>137</v>
       </c>
       <c r="R29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S29" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="T29" t="s">
         <v>27</v>
@@ -14733,10 +14730,10 @@
         <v>27</v>
       </c>
       <c r="X29" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y29" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Z29">
         <v>20</v>
@@ -14781,7 +14778,7 @@
         <v>84</v>
       </c>
       <c r="AN29" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -14793,13 +14790,13 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C30" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E30" t="s">
         <v>142</v>
@@ -14829,7 +14826,7 @@
         <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O30" t="s">
         <v>27</v>
@@ -14859,7 +14856,7 @@
         <v>27</v>
       </c>
       <c r="X30" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y30" t="s">
         <v>27</v>
@@ -14907,7 +14904,7 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -14919,13 +14916,13 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C31" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E31" t="s">
         <v>142</v>
@@ -14955,10 +14952,10 @@
         <v>26</v>
       </c>
       <c r="N31" t="s">
+        <v>215</v>
+      </c>
+      <c r="O31" t="s">
         <v>216</v>
-      </c>
-      <c r="O31" t="s">
-        <v>217</v>
       </c>
       <c r="P31" t="s">
         <v>138</v>
@@ -14967,7 +14964,7 @@
         <v>110</v>
       </c>
       <c r="R31" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S31" t="s">
         <v>27</v>
@@ -14976,7 +14973,7 @@
         <v>129</v>
       </c>
       <c r="U31" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -14985,10 +14982,10 @@
         <v>27</v>
       </c>
       <c r="X31" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Y31" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Z31">
         <v>20</v>
@@ -15033,7 +15030,7 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -15045,13 +15042,13 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D32" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E32" t="s">
         <v>142</v>
@@ -15081,13 +15078,13 @@
         <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P32" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q32" t="s">
         <v>70</v>
@@ -15111,7 +15108,7 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y32" t="s">
         <v>27</v>
@@ -15159,7 +15156,7 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -15171,13 +15168,13 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D33" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E33" t="s">
         <v>142</v>
@@ -15207,40 +15204,40 @@
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O33" t="s">
+        <v>232</v>
+      </c>
+      <c r="P33" t="s">
         <v>233</v>
       </c>
-      <c r="P33" t="s">
+      <c r="Q33" t="s">
+        <v>219</v>
+      </c>
+      <c r="R33" t="s">
+        <v>27</v>
+      </c>
+      <c r="S33" t="s">
+        <v>27</v>
+      </c>
+      <c r="T33" t="s">
+        <v>27</v>
+      </c>
+      <c r="U33" t="s">
+        <v>27</v>
+      </c>
+      <c r="V33" t="s">
+        <v>27</v>
+      </c>
+      <c r="W33" t="s">
+        <v>27</v>
+      </c>
+      <c r="X33" t="s">
         <v>234</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="Y33" t="s">
         <v>220</v>
-      </c>
-      <c r="R33" t="s">
-        <v>27</v>
-      </c>
-      <c r="S33" t="s">
-        <v>27</v>
-      </c>
-      <c r="T33" t="s">
-        <v>27</v>
-      </c>
-      <c r="U33" t="s">
-        <v>27</v>
-      </c>
-      <c r="V33" t="s">
-        <v>27</v>
-      </c>
-      <c r="W33" t="s">
-        <v>27</v>
-      </c>
-      <c r="X33" t="s">
-        <v>235</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>221</v>
       </c>
       <c r="Z33">
         <v>40</v>
@@ -15285,7 +15282,7 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -15411,7 +15408,7 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -15537,7 +15534,7 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO35">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F113DB-3495-47C0-8747-0BCFE9541510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D075EA99-489F-4A8B-8108-A9D83A760DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1080" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1650" yWindow="1095" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -1208,16 +1208,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>春の牧場</t>
-    <rPh sb="0" eb="1">
-      <t>ハル</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ボクジョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>place_category</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1701,6 +1691,10 @@
   </si>
   <si>
     <t>BARアズール</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ポンポンファ～ム</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2138,7 +2132,7 @@
         <v>98</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
@@ -4434,7 +4428,7 @@
         <v>98</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
@@ -6729,7 +6723,7 @@
         <v>98</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
@@ -6831,7 +6825,7 @@
         <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E2" t="s">
         <v>58</v>
@@ -6951,13 +6945,13 @@
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C3" t="s">
         <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E3" t="s">
         <v>58</v>
@@ -7077,13 +7071,13 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C4" t="s">
         <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E4" t="s">
         <v>58</v>
@@ -7203,13 +7197,13 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C5" t="s">
         <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E5" t="s">
         <v>58</v>
@@ -7581,13 +7575,13 @@
         <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C8" t="s">
         <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E8" t="s">
         <v>58</v>
@@ -7833,7 +7827,7 @@
         <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C10" t="s">
         <v>173</v>
@@ -7959,7 +7953,7 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C11" t="s">
         <v>175</v>
@@ -8085,7 +8079,7 @@
         <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C12" t="s">
         <v>176</v>
@@ -8211,7 +8205,7 @@
         <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C13" t="s">
         <v>177</v>
@@ -8337,13 +8331,13 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E14" t="s">
         <v>48</v>
@@ -8463,13 +8457,13 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E15" t="s">
         <v>48</v>
@@ -8589,13 +8583,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E16" t="s">
         <v>48</v>
@@ -8715,13 +8709,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E17" t="s">
         <v>48</v>
@@ -8841,13 +8835,13 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D18" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E18" t="s">
         <v>48</v>
@@ -9093,13 +9087,13 @@
         <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E20" t="s">
         <v>151</v>
@@ -9345,13 +9339,13 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C22" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D22" t="s">
-        <v>192</v>
+        <v>285</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
@@ -9474,7 +9468,7 @@
         <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D23" t="s">
         <v>140</v>
@@ -9600,7 +9594,7 @@
         <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D24" t="s">
         <v>152</v>
@@ -9723,7 +9717,7 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C25" t="s">
         <v>181</v>
@@ -9774,7 +9768,7 @@
         <v>103</v>
       </c>
       <c r="S25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T25" t="s">
         <v>191</v>
@@ -9795,7 +9789,7 @@
         <v>83</v>
       </c>
       <c r="Z25">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA25">
         <v>16</v>
@@ -9807,7 +9801,7 @@
         <v>10</v>
       </c>
       <c r="AD25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE25">
         <v>10</v>
@@ -9816,7 +9810,7 @@
         <v>4</v>
       </c>
       <c r="AG25">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AH25">
         <v>0</v>
@@ -9849,13 +9843,13 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E26" t="s">
         <v>116</v>
@@ -9891,7 +9885,7 @@
         <v>73</v>
       </c>
       <c r="P26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q26" t="s">
         <v>113</v>
@@ -9915,7 +9909,7 @@
         <v>27</v>
       </c>
       <c r="X26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y26" t="s">
         <v>136</v>
@@ -9963,7 +9957,7 @@
         <v>91</v>
       </c>
       <c r="AN26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -9975,13 +9969,13 @@
         <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C27" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E27" t="s">
         <v>50</v>
@@ -10044,7 +10038,7 @@
         <v>111</v>
       </c>
       <c r="Y27" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z27">
         <v>25</v>
@@ -10089,7 +10083,7 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -10101,13 +10095,13 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C28" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D28" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E28" t="s">
         <v>116</v>
@@ -10155,10 +10149,10 @@
         <v>74</v>
       </c>
       <c r="T28" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="U28" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V28" t="s">
         <v>27</v>
@@ -10215,7 +10209,7 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -10227,13 +10221,13 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C29" t="s">
         <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E29" t="s">
         <v>50</v>
@@ -10263,10 +10257,10 @@
         <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P29" t="s">
         <v>25</v>
@@ -10275,10 +10269,10 @@
         <v>137</v>
       </c>
       <c r="R29" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="S29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="T29" t="s">
         <v>27</v>
@@ -10293,10 +10287,10 @@
         <v>27</v>
       </c>
       <c r="X29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Y29" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Z29">
         <v>20</v>
@@ -10341,7 +10335,7 @@
         <v>84</v>
       </c>
       <c r="AN29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -10353,16 +10347,16 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C30" t="s">
+        <v>258</v>
+      </c>
+      <c r="D30" t="s">
+        <v>260</v>
+      </c>
+      <c r="E30" t="s">
         <v>259</v>
-      </c>
-      <c r="D30" t="s">
-        <v>261</v>
-      </c>
-      <c r="E30" t="s">
-        <v>260</v>
       </c>
       <c r="F30">
         <v>60</v>
@@ -10389,7 +10383,7 @@
         <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O30" t="s">
         <v>27</v>
@@ -10419,7 +10413,7 @@
         <v>27</v>
       </c>
       <c r="X30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Y30" t="s">
         <v>27</v>
@@ -10467,7 +10461,7 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -10479,13 +10473,13 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C31" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E31" t="s">
         <v>116</v>
@@ -10515,10 +10509,10 @@
         <v>26</v>
       </c>
       <c r="N31" t="s">
+        <v>214</v>
+      </c>
+      <c r="O31" t="s">
         <v>215</v>
-      </c>
-      <c r="O31" t="s">
-        <v>216</v>
       </c>
       <c r="P31" t="s">
         <v>138</v>
@@ -10527,7 +10521,7 @@
         <v>110</v>
       </c>
       <c r="R31" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="S31" t="s">
         <v>27</v>
@@ -10536,7 +10530,7 @@
         <v>129</v>
       </c>
       <c r="U31" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -10545,10 +10539,10 @@
         <v>27</v>
       </c>
       <c r="X31" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Y31" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Z31">
         <v>20</v>
@@ -10593,7 +10587,7 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -10605,13 +10599,13 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D32" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E32" t="s">
         <v>116</v>
@@ -10641,13 +10635,13 @@
         <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O32" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P32" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q32" t="s">
         <v>70</v>
@@ -10671,7 +10665,7 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y32" t="s">
         <v>27</v>
@@ -10719,7 +10713,7 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -10731,13 +10725,13 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C33" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D33" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E33" t="s">
         <v>50</v>
@@ -10767,40 +10761,40 @@
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O33" t="s">
+        <v>231</v>
+      </c>
+      <c r="P33" t="s">
         <v>232</v>
       </c>
-      <c r="P33" t="s">
+      <c r="Q33" t="s">
+        <v>218</v>
+      </c>
+      <c r="R33" t="s">
+        <v>27</v>
+      </c>
+      <c r="S33" t="s">
+        <v>27</v>
+      </c>
+      <c r="T33" t="s">
+        <v>27</v>
+      </c>
+      <c r="U33" t="s">
+        <v>27</v>
+      </c>
+      <c r="V33" t="s">
+        <v>27</v>
+      </c>
+      <c r="W33" t="s">
+        <v>27</v>
+      </c>
+      <c r="X33" t="s">
         <v>233</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="Y33" t="s">
         <v>219</v>
-      </c>
-      <c r="R33" t="s">
-        <v>27</v>
-      </c>
-      <c r="S33" t="s">
-        <v>27</v>
-      </c>
-      <c r="T33" t="s">
-        <v>27</v>
-      </c>
-      <c r="U33" t="s">
-        <v>27</v>
-      </c>
-      <c r="V33" t="s">
-        <v>27</v>
-      </c>
-      <c r="W33" t="s">
-        <v>27</v>
-      </c>
-      <c r="X33" t="s">
-        <v>234</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>220</v>
       </c>
       <c r="Z33">
         <v>40</v>
@@ -10845,7 +10839,7 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -11166,7 +11160,7 @@
         <v>98</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
@@ -11268,7 +11262,7 @@
         <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E2" t="s">
         <v>142</v>
@@ -11388,13 +11382,13 @@
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C3" t="s">
         <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E3" t="s">
         <v>142</v>
@@ -11514,13 +11508,13 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C4" t="s">
         <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E4" t="s">
         <v>142</v>
@@ -11640,13 +11634,13 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C5" t="s">
         <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E5" t="s">
         <v>142</v>
@@ -12018,13 +12012,13 @@
         <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C8" t="s">
         <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E8" t="s">
         <v>142</v>
@@ -12270,7 +12264,7 @@
         <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C10" t="s">
         <v>173</v>
@@ -12396,7 +12390,7 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C11" t="s">
         <v>175</v>
@@ -12522,7 +12516,7 @@
         <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C12" t="s">
         <v>176</v>
@@ -12648,7 +12642,7 @@
         <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C13" t="s">
         <v>177</v>
@@ -12774,13 +12768,13 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E14" t="s">
         <v>142</v>
@@ -12900,13 +12894,13 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E15" t="s">
         <v>142</v>
@@ -13026,13 +13020,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E16" t="s">
         <v>142</v>
@@ -13152,13 +13146,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E17" t="s">
         <v>142</v>
@@ -13278,13 +13272,13 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D18" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E18" t="s">
         <v>142</v>
@@ -13530,13 +13524,13 @@
         <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E20" t="s">
         <v>142</v>
@@ -13782,13 +13776,13 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C22" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D22" t="s">
-        <v>192</v>
+        <v>285</v>
       </c>
       <c r="E22" t="s">
         <v>142</v>
@@ -13911,7 +13905,7 @@
         <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D23" t="s">
         <v>140</v>
@@ -14037,7 +14031,7 @@
         <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D24" t="s">
         <v>152</v>
@@ -14160,7 +14154,7 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C25" t="s">
         <v>181</v>
@@ -14211,7 +14205,7 @@
         <v>103</v>
       </c>
       <c r="S25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T25" t="s">
         <v>191</v>
@@ -14232,7 +14226,7 @@
         <v>83</v>
       </c>
       <c r="Z25">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA25">
         <v>16</v>
@@ -14244,7 +14238,7 @@
         <v>10</v>
       </c>
       <c r="AD25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE25">
         <v>10</v>
@@ -14253,7 +14247,7 @@
         <v>4</v>
       </c>
       <c r="AG25">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AH25">
         <v>0</v>
@@ -14286,13 +14280,13 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E26" t="s">
         <v>142</v>
@@ -14328,7 +14322,7 @@
         <v>73</v>
       </c>
       <c r="P26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q26" t="s">
         <v>113</v>
@@ -14352,7 +14346,7 @@
         <v>27</v>
       </c>
       <c r="X26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y26" t="s">
         <v>136</v>
@@ -14400,7 +14394,7 @@
         <v>91</v>
       </c>
       <c r="AN26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -14412,13 +14406,13 @@
         <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C27" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E27" t="s">
         <v>142</v>
@@ -14481,7 +14475,7 @@
         <v>111</v>
       </c>
       <c r="Y27" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z27">
         <v>25</v>
@@ -14526,7 +14520,7 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -14538,13 +14532,13 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C28" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D28" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E28" t="s">
         <v>142</v>
@@ -14592,10 +14586,10 @@
         <v>74</v>
       </c>
       <c r="T28" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="U28" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V28" t="s">
         <v>27</v>
@@ -14652,7 +14646,7 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -14664,13 +14658,13 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C29" t="s">
         <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E29" t="s">
         <v>142</v>
@@ -14700,10 +14694,10 @@
         <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P29" t="s">
         <v>25</v>
@@ -14712,10 +14706,10 @@
         <v>137</v>
       </c>
       <c r="R29" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="S29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="T29" t="s">
         <v>27</v>
@@ -14730,10 +14724,10 @@
         <v>27</v>
       </c>
       <c r="X29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Y29" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Z29">
         <v>20</v>
@@ -14778,7 +14772,7 @@
         <v>84</v>
       </c>
       <c r="AN29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -14790,13 +14784,13 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D30" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E30" t="s">
         <v>142</v>
@@ -14826,7 +14820,7 @@
         <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O30" t="s">
         <v>27</v>
@@ -14856,7 +14850,7 @@
         <v>27</v>
       </c>
       <c r="X30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Y30" t="s">
         <v>27</v>
@@ -14904,7 +14898,7 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -14916,13 +14910,13 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C31" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E31" t="s">
         <v>142</v>
@@ -14952,10 +14946,10 @@
         <v>26</v>
       </c>
       <c r="N31" t="s">
+        <v>214</v>
+      </c>
+      <c r="O31" t="s">
         <v>215</v>
-      </c>
-      <c r="O31" t="s">
-        <v>216</v>
       </c>
       <c r="P31" t="s">
         <v>138</v>
@@ -14964,7 +14958,7 @@
         <v>110</v>
       </c>
       <c r="R31" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="S31" t="s">
         <v>27</v>
@@ -14973,7 +14967,7 @@
         <v>129</v>
       </c>
       <c r="U31" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -14982,10 +14976,10 @@
         <v>27</v>
       </c>
       <c r="X31" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Y31" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Z31">
         <v>20</v>
@@ -15030,7 +15024,7 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -15042,13 +15036,13 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D32" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E32" t="s">
         <v>142</v>
@@ -15078,13 +15072,13 @@
         <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O32" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P32" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q32" t="s">
         <v>70</v>
@@ -15108,7 +15102,7 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y32" t="s">
         <v>27</v>
@@ -15156,7 +15150,7 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -15168,13 +15162,13 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C33" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D33" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E33" t="s">
         <v>142</v>
@@ -15204,40 +15198,40 @@
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O33" t="s">
+        <v>231</v>
+      </c>
+      <c r="P33" t="s">
         <v>232</v>
       </c>
-      <c r="P33" t="s">
+      <c r="Q33" t="s">
+        <v>218</v>
+      </c>
+      <c r="R33" t="s">
+        <v>27</v>
+      </c>
+      <c r="S33" t="s">
+        <v>27</v>
+      </c>
+      <c r="T33" t="s">
+        <v>27</v>
+      </c>
+      <c r="U33" t="s">
+        <v>27</v>
+      </c>
+      <c r="V33" t="s">
+        <v>27</v>
+      </c>
+      <c r="W33" t="s">
+        <v>27</v>
+      </c>
+      <c r="X33" t="s">
         <v>233</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="Y33" t="s">
         <v>219</v>
-      </c>
-      <c r="R33" t="s">
-        <v>27</v>
-      </c>
-      <c r="S33" t="s">
-        <v>27</v>
-      </c>
-      <c r="T33" t="s">
-        <v>27</v>
-      </c>
-      <c r="U33" t="s">
-        <v>27</v>
-      </c>
-      <c r="V33" t="s">
-        <v>27</v>
-      </c>
-      <c r="W33" t="s">
-        <v>27</v>
-      </c>
-      <c r="X33" t="s">
-        <v>234</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>220</v>
       </c>
       <c r="Z33">
         <v>40</v>
@@ -15282,7 +15276,7 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AO33">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D075EA99-489F-4A8B-8108-A9D83A760DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1B2E90-1B9E-48E2-B6BB-D9E8F795983C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1650" yWindow="1095" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2970" yWindow="1215" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -10797,19 +10797,19 @@
         <v>219</v>
       </c>
       <c r="Z33">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="AA33">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AB33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AC33">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AD33">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE33">
         <v>0</v>
@@ -10827,13 +10827,13 @@
         <v>0</v>
       </c>
       <c r="AJ33">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AK33">
         <v>4</v>
       </c>
       <c r="AL33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM33" t="s">
         <v>84</v>
@@ -15234,19 +15234,19 @@
         <v>219</v>
       </c>
       <c r="Z33">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="AA33">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AB33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AC33">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AD33">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE33">
         <v>0</v>
@@ -15264,13 +15264,13 @@
         <v>0</v>
       </c>
       <c r="AJ33">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AK33">
         <v>4</v>
       </c>
       <c r="AL33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM33" t="s">
         <v>84</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1B2E90-1B9E-48E2-B6BB-D9E8F795983C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3117842F-DD06-4587-9542-7468FF531F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2970" yWindow="1215" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2715" yWindow="1335" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2140" uniqueCount="288">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -1695,6 +1695,17 @@
   </si>
   <si>
     <t>ポンポンファ～ム</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Or_Hiroba_Summer_SweetsHouse</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>イケメンのお店</t>
+    <rPh sb="6" eb="7">
+      <t>ミセ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -6669,7 +6680,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAAE7BC7-74FC-4400-A474-EA5B977D362B}">
-  <dimension ref="A1:AO35"/>
+  <dimension ref="A1:AO36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -7319,7 +7330,7 @@
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A6">
-        <f t="shared" ref="A6:A35" si="0">ROW()-2+100</f>
+        <f t="shared" ref="A6:A36" si="0">ROW()-2+100</f>
         <v>104</v>
       </c>
       <c r="B6" t="s">
@@ -9591,52 +9602,52 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>254</v>
       </c>
       <c r="C24" t="s">
-        <v>194</v>
+        <v>286</v>
       </c>
       <c r="D24" t="s">
-        <v>152</v>
+        <v>287</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M24" t="s">
         <v>26</v>
       </c>
       <c r="N24" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="O24" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P24" t="s">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="Q24" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="R24" t="s">
         <v>27</v>
@@ -9657,25 +9668,25 @@
         <v>27</v>
       </c>
       <c r="X24" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="Y24" t="s">
         <v>27</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA24">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC24">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AD24">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE24">
         <v>0</v>
@@ -9693,19 +9704,19 @@
         <v>0</v>
       </c>
       <c r="AJ24">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AK24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AN24" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -9717,19 +9728,19 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>262</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E25" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="F25">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -9753,25 +9764,25 @@
         <v>26</v>
       </c>
       <c r="N25" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O25" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="P25" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="Q25" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="R25" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="S25" t="s">
-        <v>282</v>
+        <v>27</v>
       </c>
       <c r="T25" t="s">
-        <v>191</v>
+        <v>27</v>
       </c>
       <c r="U25" t="s">
         <v>27</v>
@@ -9783,55 +9794,55 @@
         <v>27</v>
       </c>
       <c r="X25" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="Y25" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="Z25">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="AB25">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AC25">
+        <v>7</v>
+      </c>
+      <c r="AD25">
         <v>10</v>
       </c>
-      <c r="AD25">
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>98</v>
+      </c>
+      <c r="AK25">
         <v>2</v>
       </c>
-      <c r="AE25">
-        <v>10</v>
-      </c>
-      <c r="AF25">
-        <v>4</v>
-      </c>
-      <c r="AG25">
-        <v>26</v>
-      </c>
-      <c r="AH25">
-        <v>0</v>
-      </c>
-      <c r="AI25">
-        <v>0</v>
-      </c>
-      <c r="AJ25">
-        <v>78</v>
-      </c>
-      <c r="AK25">
-        <v>15</v>
-      </c>
       <c r="AL25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AN25" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AO25">
         <v>0</v>
@@ -9843,31 +9854,31 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C26" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D26" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="E26" t="s">
         <v>116</v>
       </c>
       <c r="F26">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -9879,25 +9890,25 @@
         <v>26</v>
       </c>
       <c r="N26" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="O26" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="P26" t="s">
-        <v>224</v>
+        <v>25</v>
       </c>
       <c r="Q26" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="R26" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="S26" t="s">
-        <v>27</v>
+        <v>282</v>
       </c>
       <c r="T26" t="s">
-        <v>27</v>
+        <v>191</v>
       </c>
       <c r="U26" t="s">
         <v>27</v>
@@ -9909,34 +9920,34 @@
         <v>27</v>
       </c>
       <c r="X26" t="s">
-        <v>208</v>
+        <v>33</v>
       </c>
       <c r="Y26" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="Z26">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AA26">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC26">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD26">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AE26">
         <v>10</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AH26">
         <v>0</v>
@@ -9945,19 +9956,19 @@
         <v>0</v>
       </c>
       <c r="AJ26">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AK26">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AL26">
         <v>7</v>
       </c>
       <c r="AM26" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AN26" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -9969,25 +9980,25 @@
         <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C27" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D27" t="s">
-        <v>270</v>
+        <v>195</v>
       </c>
       <c r="E27" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F27">
         <v>30</v>
       </c>
       <c r="G27">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -9999,25 +10010,25 @@
         <v>1</v>
       </c>
       <c r="L27">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M27" t="s">
         <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P27" t="s">
-        <v>108</v>
+        <v>224</v>
       </c>
       <c r="Q27" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="R27" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="S27" t="s">
         <v>27</v>
@@ -10035,25 +10046,25 @@
         <v>27</v>
       </c>
       <c r="X27" t="s">
-        <v>111</v>
+        <v>208</v>
       </c>
       <c r="Y27" t="s">
-        <v>229</v>
+        <v>136</v>
       </c>
       <c r="Z27">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AA27">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB27">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AC27">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AD27">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AE27">
         <v>10</v>
@@ -10071,19 +10082,19 @@
         <v>0</v>
       </c>
       <c r="AJ27">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK27">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AL27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM27" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="AN27" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -10095,25 +10106,25 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="C28" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D28" t="s">
-        <v>197</v>
+        <v>270</v>
       </c>
       <c r="E28" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="F28">
         <v>30</v>
       </c>
       <c r="G28">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -10125,7 +10136,7 @@
         <v>1</v>
       </c>
       <c r="L28">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M28" t="s">
         <v>26</v>
@@ -10134,25 +10145,25 @@
         <v>72</v>
       </c>
       <c r="O28" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="P28" t="s">
         <v>108</v>
       </c>
       <c r="Q28" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="R28" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="S28" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="T28" t="s">
-        <v>222</v>
+        <v>27</v>
       </c>
       <c r="U28" t="s">
-        <v>250</v>
+        <v>27</v>
       </c>
       <c r="V28" t="s">
         <v>27</v>
@@ -10161,55 +10172,55 @@
         <v>27</v>
       </c>
       <c r="X28" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="Y28" t="s">
-        <v>111</v>
+        <v>229</v>
       </c>
       <c r="Z28">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AA28">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="AB28">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AC28">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AD28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE28">
         <v>10</v>
       </c>
       <c r="AF28">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>94</v>
+      </c>
+      <c r="AK28">
+        <v>1</v>
+      </c>
+      <c r="AL28">
         <v>5</v>
-      </c>
-      <c r="AI28">
-        <v>0</v>
-      </c>
-      <c r="AJ28">
-        <v>83</v>
-      </c>
-      <c r="AK28">
-        <v>16</v>
-      </c>
-      <c r="AL28">
-        <v>1</v>
       </c>
       <c r="AM28" t="s">
         <v>84</v>
       </c>
       <c r="AN28" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -10221,25 +10232,25 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="D29" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E29" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F29">
         <v>30</v>
       </c>
       <c r="G29">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H29">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -10251,34 +10262,34 @@
         <v>1</v>
       </c>
       <c r="L29">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M29" t="s">
         <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
       <c r="O29" t="s">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="Q29" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="R29" t="s">
-        <v>223</v>
+        <v>112</v>
       </c>
       <c r="S29" t="s">
-        <v>227</v>
+        <v>74</v>
       </c>
       <c r="T29" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="U29" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="V29" t="s">
         <v>27</v>
@@ -10287,55 +10298,55 @@
         <v>27</v>
       </c>
       <c r="X29" t="s">
-        <v>216</v>
+        <v>127</v>
       </c>
       <c r="Y29" t="s">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="Z29">
         <v>20</v>
       </c>
       <c r="AA29">
+        <v>5</v>
+      </c>
+      <c r="AB29">
         <v>20</v>
       </c>
-      <c r="AB29">
-        <v>17</v>
-      </c>
       <c r="AC29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD29">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE29">
         <v>10</v>
       </c>
       <c r="AF29">
+        <v>13</v>
+      </c>
+      <c r="AG29">
         <v>10</v>
       </c>
-      <c r="AG29">
-        <v>0</v>
-      </c>
       <c r="AH29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI29">
         <v>0</v>
       </c>
       <c r="AJ29">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AK29">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AL29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM29" t="s">
         <v>84</v>
       </c>
       <c r="AN29" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -10347,25 +10358,25 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C30" t="s">
-        <v>258</v>
+        <v>42</v>
       </c>
       <c r="D30" t="s">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="E30" t="s">
-        <v>259</v>
+        <v>50</v>
       </c>
       <c r="F30">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H30">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -10383,22 +10394,22 @@
         <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="O30" t="s">
-        <v>27</v>
+        <v>221</v>
       </c>
       <c r="P30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q30" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="R30" t="s">
-        <v>27</v>
+        <v>223</v>
       </c>
       <c r="S30" t="s">
-        <v>27</v>
+        <v>227</v>
       </c>
       <c r="T30" t="s">
         <v>27</v>
@@ -10413,31 +10424,31 @@
         <v>27</v>
       </c>
       <c r="X30" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="Y30" t="s">
-        <v>27</v>
+        <v>269</v>
       </c>
       <c r="Z30">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB30">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AC30">
         <v>13</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG30">
         <v>0</v>
@@ -10449,19 +10460,19 @@
         <v>0</v>
       </c>
       <c r="AJ30">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="AK30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM30" t="s">
         <v>84</v>
       </c>
       <c r="AN30" t="s">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -10473,25 +10484,25 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C31" t="s">
-        <v>202</v>
+        <v>258</v>
       </c>
       <c r="D31" t="s">
-        <v>198</v>
+        <v>260</v>
       </c>
       <c r="E31" t="s">
-        <v>116</v>
+        <v>259</v>
       </c>
       <c r="F31">
         <v>60</v>
       </c>
       <c r="G31">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -10503,34 +10514,34 @@
         <v>1</v>
       </c>
       <c r="L31">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M31" t="s">
         <v>26</v>
       </c>
       <c r="N31" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="O31" t="s">
-        <v>215</v>
+        <v>27</v>
       </c>
       <c r="P31" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="Q31" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="R31" t="s">
-        <v>257</v>
+        <v>27</v>
       </c>
       <c r="S31" t="s">
         <v>27</v>
       </c>
       <c r="T31" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="U31" t="s">
-        <v>228</v>
+        <v>27</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -10539,55 +10550,55 @@
         <v>27</v>
       </c>
       <c r="X31" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="Y31" t="s">
-        <v>216</v>
+        <v>27</v>
       </c>
       <c r="Z31">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AA31">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB31">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AD31">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI31">
         <v>0</v>
       </c>
       <c r="AJ31">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="AK31">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AL31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AM31" t="s">
         <v>84</v>
       </c>
       <c r="AN31" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -10599,25 +10610,25 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C32" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D32" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E32" t="s">
         <v>116</v>
       </c>
       <c r="F32">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G32">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="H32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -10629,34 +10640,34 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M32" t="s">
         <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="O32" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="P32" t="s">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="Q32" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="R32" t="s">
-        <v>103</v>
+        <v>257</v>
       </c>
       <c r="S32" t="s">
         <v>27</v>
       </c>
       <c r="T32" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="U32" t="s">
-        <v>27</v>
+        <v>228</v>
       </c>
       <c r="V32" t="s">
         <v>27</v>
@@ -10665,55 +10676,55 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="Y32" t="s">
-        <v>27</v>
+        <v>216</v>
       </c>
       <c r="Z32">
         <v>20</v>
       </c>
       <c r="AA32">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AB32">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC32">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AD32">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE32">
         <v>10</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI32">
         <v>0</v>
       </c>
       <c r="AJ32">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AK32">
         <v>10</v>
       </c>
       <c r="AL32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AM32" t="s">
         <v>84</v>
       </c>
       <c r="AN32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -10725,25 +10736,25 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="C33" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D33" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E33" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F33">
         <v>90</v>
       </c>
       <c r="G33">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -10761,19 +10772,19 @@
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="O33" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="P33" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="Q33" t="s">
-        <v>218</v>
+        <v>70</v>
       </c>
       <c r="R33" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="S33" t="s">
         <v>27</v>
@@ -10791,28 +10802,28 @@
         <v>27</v>
       </c>
       <c r="X33" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="Y33" t="s">
-        <v>219</v>
+        <v>27</v>
       </c>
       <c r="Z33">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="AA33">
+        <v>38</v>
+      </c>
+      <c r="AB33">
+        <v>2</v>
+      </c>
+      <c r="AC33">
         <v>13</v>
       </c>
-      <c r="AB33">
-        <v>9</v>
-      </c>
-      <c r="AC33">
-        <v>6</v>
-      </c>
       <c r="AD33">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF33">
         <v>0</v>
@@ -10827,19 +10838,19 @@
         <v>0</v>
       </c>
       <c r="AJ33">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK33">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AL33">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AM33" t="s">
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -10851,52 +10862,52 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>268</v>
       </c>
       <c r="C34" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="E34" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F34">
         <v>90</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M34" t="s">
         <v>26</v>
       </c>
       <c r="N34" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="O34" t="s">
-        <v>27</v>
+        <v>231</v>
       </c>
       <c r="P34" t="s">
-        <v>27</v>
+        <v>232</v>
       </c>
       <c r="Q34" t="s">
-        <v>27</v>
+        <v>218</v>
       </c>
       <c r="R34" t="s">
         <v>27</v>
@@ -10917,25 +10928,25 @@
         <v>27</v>
       </c>
       <c r="X34" t="s">
-        <v>27</v>
+        <v>233</v>
       </c>
       <c r="Y34" t="s">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="Z34">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AA34">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AB34">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AC34">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE34">
         <v>0</v>
@@ -10953,19 +10964,19 @@
         <v>0</v>
       </c>
       <c r="AJ34">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AK34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM34" t="s">
         <v>84</v>
       </c>
       <c r="AN34" t="s">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -10980,10 +10991,10 @@
         <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D35" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E35" t="s">
         <v>48</v>
@@ -11001,7 +11012,7 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -11094,6 +11105,132 @@
         <v>186</v>
       </c>
       <c r="AO35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:41" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>134</v>
+      </c>
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" t="s">
+        <v>160</v>
+      </c>
+      <c r="D36" t="s">
+        <v>161</v>
+      </c>
+      <c r="E36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36">
+        <v>90</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>9999</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>10</v>
+      </c>
+      <c r="M36" t="s">
+        <v>26</v>
+      </c>
+      <c r="N36" t="s">
+        <v>27</v>
+      </c>
+      <c r="O36" t="s">
+        <v>27</v>
+      </c>
+      <c r="P36" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>27</v>
+      </c>
+      <c r="R36" t="s">
+        <v>27</v>
+      </c>
+      <c r="S36" t="s">
+        <v>27</v>
+      </c>
+      <c r="T36" t="s">
+        <v>27</v>
+      </c>
+      <c r="U36" t="s">
+        <v>27</v>
+      </c>
+      <c r="V36" t="s">
+        <v>27</v>
+      </c>
+      <c r="W36" t="s">
+        <v>27</v>
+      </c>
+      <c r="X36" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z36">
+        <v>60</v>
+      </c>
+      <c r="AA36">
+        <v>25</v>
+      </c>
+      <c r="AB36">
+        <v>12</v>
+      </c>
+      <c r="AC36">
+        <v>3</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36">
+        <v>0</v>
+      </c>
+      <c r="AI36">
+        <v>0</v>
+      </c>
+      <c r="AJ36">
+        <v>95</v>
+      </c>
+      <c r="AK36">
+        <v>5</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>186</v>
+      </c>
+      <c r="AO36">
         <v>1</v>
       </c>
     </row>
@@ -11106,7 +11243,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAD14E5B-6BFE-4D20-B771-5A2DB6950621}">
-  <dimension ref="A1:AO35"/>
+  <dimension ref="A1:AO36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -12260,7 +12397,7 @@
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A10">
-        <f t="shared" ref="A10:A35" si="1">ROW()-2+100</f>
+        <f t="shared" ref="A10:A36" si="1">ROW()-2+100</f>
         <v>108</v>
       </c>
       <c r="B10" t="s">
@@ -14028,52 +14165,52 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>254</v>
       </c>
       <c r="C24" t="s">
-        <v>194</v>
+        <v>286</v>
       </c>
       <c r="D24" t="s">
-        <v>152</v>
+        <v>287</v>
       </c>
       <c r="E24" t="s">
         <v>142</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M24" t="s">
         <v>26</v>
       </c>
       <c r="N24" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="O24" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P24" t="s">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="Q24" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="R24" t="s">
         <v>27</v>
@@ -14094,25 +14231,25 @@
         <v>27</v>
       </c>
       <c r="X24" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="Y24" t="s">
         <v>27</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA24">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC24">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AD24">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE24">
         <v>0</v>
@@ -14130,19 +14267,19 @@
         <v>0</v>
       </c>
       <c r="AJ24">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AK24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AN24" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -14154,19 +14291,19 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>262</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E25" t="s">
         <v>142</v>
       </c>
       <c r="F25">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -14190,25 +14327,25 @@
         <v>26</v>
       </c>
       <c r="N25" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O25" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="P25" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="Q25" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="R25" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="S25" t="s">
-        <v>282</v>
+        <v>27</v>
       </c>
       <c r="T25" t="s">
-        <v>191</v>
+        <v>27</v>
       </c>
       <c r="U25" t="s">
         <v>27</v>
@@ -14220,55 +14357,55 @@
         <v>27</v>
       </c>
       <c r="X25" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="Y25" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="Z25">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="AB25">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AC25">
+        <v>7</v>
+      </c>
+      <c r="AD25">
         <v>10</v>
       </c>
-      <c r="AD25">
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>98</v>
+      </c>
+      <c r="AK25">
         <v>2</v>
       </c>
-      <c r="AE25">
-        <v>10</v>
-      </c>
-      <c r="AF25">
-        <v>4</v>
-      </c>
-      <c r="AG25">
-        <v>26</v>
-      </c>
-      <c r="AH25">
-        <v>0</v>
-      </c>
-      <c r="AI25">
-        <v>0</v>
-      </c>
-      <c r="AJ25">
-        <v>78</v>
-      </c>
-      <c r="AK25">
-        <v>15</v>
-      </c>
       <c r="AL25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AN25" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AO25">
         <v>0</v>
@@ -14280,31 +14417,31 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C26" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D26" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="E26" t="s">
         <v>142</v>
       </c>
       <c r="F26">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -14316,25 +14453,25 @@
         <v>26</v>
       </c>
       <c r="N26" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="O26" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="P26" t="s">
-        <v>224</v>
+        <v>25</v>
       </c>
       <c r="Q26" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="R26" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="S26" t="s">
-        <v>27</v>
+        <v>282</v>
       </c>
       <c r="T26" t="s">
-        <v>27</v>
+        <v>191</v>
       </c>
       <c r="U26" t="s">
         <v>27</v>
@@ -14346,34 +14483,34 @@
         <v>27</v>
       </c>
       <c r="X26" t="s">
-        <v>208</v>
+        <v>33</v>
       </c>
       <c r="Y26" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="Z26">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AA26">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC26">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD26">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AE26">
         <v>10</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AH26">
         <v>0</v>
@@ -14382,19 +14519,19 @@
         <v>0</v>
       </c>
       <c r="AJ26">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AK26">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AL26">
         <v>7</v>
       </c>
       <c r="AM26" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AN26" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -14406,13 +14543,13 @@
         <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C27" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D27" t="s">
-        <v>270</v>
+        <v>195</v>
       </c>
       <c r="E27" t="s">
         <v>142</v>
@@ -14421,10 +14558,10 @@
         <v>30</v>
       </c>
       <c r="G27">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -14436,25 +14573,25 @@
         <v>1</v>
       </c>
       <c r="L27">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M27" t="s">
         <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P27" t="s">
-        <v>108</v>
+        <v>224</v>
       </c>
       <c r="Q27" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="R27" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="S27" t="s">
         <v>27</v>
@@ -14472,25 +14609,25 @@
         <v>27</v>
       </c>
       <c r="X27" t="s">
-        <v>111</v>
+        <v>208</v>
       </c>
       <c r="Y27" t="s">
-        <v>229</v>
+        <v>136</v>
       </c>
       <c r="Z27">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AA27">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB27">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AC27">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AD27">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AE27">
         <v>10</v>
@@ -14508,19 +14645,19 @@
         <v>0</v>
       </c>
       <c r="AJ27">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK27">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AL27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM27" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="AN27" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -14532,13 +14669,13 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="C28" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D28" t="s">
-        <v>197</v>
+        <v>270</v>
       </c>
       <c r="E28" t="s">
         <v>142</v>
@@ -14547,10 +14684,10 @@
         <v>30</v>
       </c>
       <c r="G28">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -14562,7 +14699,7 @@
         <v>1</v>
       </c>
       <c r="L28">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M28" t="s">
         <v>26</v>
@@ -14571,25 +14708,25 @@
         <v>72</v>
       </c>
       <c r="O28" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="P28" t="s">
         <v>108</v>
       </c>
       <c r="Q28" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="R28" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="S28" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="T28" t="s">
-        <v>222</v>
+        <v>27</v>
       </c>
       <c r="U28" t="s">
-        <v>250</v>
+        <v>27</v>
       </c>
       <c r="V28" t="s">
         <v>27</v>
@@ -14598,55 +14735,55 @@
         <v>27</v>
       </c>
       <c r="X28" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="Y28" t="s">
-        <v>111</v>
+        <v>229</v>
       </c>
       <c r="Z28">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AA28">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="AB28">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AC28">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AD28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE28">
         <v>10</v>
       </c>
       <c r="AF28">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>94</v>
+      </c>
+      <c r="AK28">
+        <v>1</v>
+      </c>
+      <c r="AL28">
         <v>5</v>
-      </c>
-      <c r="AI28">
-        <v>0</v>
-      </c>
-      <c r="AJ28">
-        <v>83</v>
-      </c>
-      <c r="AK28">
-        <v>16</v>
-      </c>
-      <c r="AL28">
-        <v>1</v>
       </c>
       <c r="AM28" t="s">
         <v>84</v>
       </c>
       <c r="AN28" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -14658,13 +14795,13 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="D29" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E29" t="s">
         <v>142</v>
@@ -14673,10 +14810,10 @@
         <v>30</v>
       </c>
       <c r="G29">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H29">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -14688,34 +14825,34 @@
         <v>1</v>
       </c>
       <c r="L29">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M29" t="s">
         <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
       <c r="O29" t="s">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="Q29" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="R29" t="s">
-        <v>223</v>
+        <v>112</v>
       </c>
       <c r="S29" t="s">
-        <v>227</v>
+        <v>74</v>
       </c>
       <c r="T29" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="U29" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="V29" t="s">
         <v>27</v>
@@ -14724,55 +14861,55 @@
         <v>27</v>
       </c>
       <c r="X29" t="s">
-        <v>216</v>
+        <v>127</v>
       </c>
       <c r="Y29" t="s">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="Z29">
         <v>20</v>
       </c>
       <c r="AA29">
+        <v>5</v>
+      </c>
+      <c r="AB29">
         <v>20</v>
       </c>
-      <c r="AB29">
-        <v>17</v>
-      </c>
       <c r="AC29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD29">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE29">
         <v>10</v>
       </c>
       <c r="AF29">
+        <v>13</v>
+      </c>
+      <c r="AG29">
         <v>10</v>
       </c>
-      <c r="AG29">
-        <v>0</v>
-      </c>
       <c r="AH29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI29">
         <v>0</v>
       </c>
       <c r="AJ29">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AK29">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AL29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM29" t="s">
         <v>84</v>
       </c>
       <c r="AN29" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -14784,25 +14921,25 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C30" t="s">
-        <v>258</v>
+        <v>42</v>
       </c>
       <c r="D30" t="s">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="E30" t="s">
         <v>142</v>
       </c>
       <c r="F30">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H30">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -14820,22 +14957,22 @@
         <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="O30" t="s">
-        <v>27</v>
+        <v>221</v>
       </c>
       <c r="P30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q30" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="R30" t="s">
-        <v>27</v>
+        <v>223</v>
       </c>
       <c r="S30" t="s">
-        <v>27</v>
+        <v>227</v>
       </c>
       <c r="T30" t="s">
         <v>27</v>
@@ -14850,31 +14987,31 @@
         <v>27</v>
       </c>
       <c r="X30" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="Y30" t="s">
-        <v>27</v>
+        <v>269</v>
       </c>
       <c r="Z30">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB30">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AC30">
         <v>13</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG30">
         <v>0</v>
@@ -14886,19 +15023,19 @@
         <v>0</v>
       </c>
       <c r="AJ30">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="AK30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM30" t="s">
         <v>84</v>
       </c>
       <c r="AN30" t="s">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -14910,13 +15047,13 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C31" t="s">
-        <v>202</v>
+        <v>258</v>
       </c>
       <c r="D31" t="s">
-        <v>198</v>
+        <v>260</v>
       </c>
       <c r="E31" t="s">
         <v>142</v>
@@ -14925,10 +15062,10 @@
         <v>60</v>
       </c>
       <c r="G31">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -14940,34 +15077,34 @@
         <v>1</v>
       </c>
       <c r="L31">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M31" t="s">
         <v>26</v>
       </c>
       <c r="N31" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="O31" t="s">
-        <v>215</v>
+        <v>27</v>
       </c>
       <c r="P31" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="Q31" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="R31" t="s">
-        <v>257</v>
+        <v>27</v>
       </c>
       <c r="S31" t="s">
         <v>27</v>
       </c>
       <c r="T31" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="U31" t="s">
-        <v>228</v>
+        <v>27</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -14976,55 +15113,55 @@
         <v>27</v>
       </c>
       <c r="X31" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="Y31" t="s">
-        <v>216</v>
+        <v>27</v>
       </c>
       <c r="Z31">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AA31">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB31">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AD31">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI31">
         <v>0</v>
       </c>
       <c r="AJ31">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="AK31">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AL31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AM31" t="s">
         <v>84</v>
       </c>
       <c r="AN31" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -15036,25 +15173,25 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C32" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D32" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E32" t="s">
         <v>142</v>
       </c>
       <c r="F32">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G32">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="H32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -15066,34 +15203,34 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M32" t="s">
         <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="O32" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="P32" t="s">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="Q32" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="R32" t="s">
-        <v>103</v>
+        <v>257</v>
       </c>
       <c r="S32" t="s">
         <v>27</v>
       </c>
       <c r="T32" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="U32" t="s">
-        <v>27</v>
+        <v>228</v>
       </c>
       <c r="V32" t="s">
         <v>27</v>
@@ -15102,55 +15239,55 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="Y32" t="s">
-        <v>27</v>
+        <v>216</v>
       </c>
       <c r="Z32">
         <v>20</v>
       </c>
       <c r="AA32">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AB32">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC32">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AD32">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE32">
         <v>10</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI32">
         <v>0</v>
       </c>
       <c r="AJ32">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AK32">
         <v>10</v>
       </c>
       <c r="AL32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AM32" t="s">
         <v>84</v>
       </c>
       <c r="AN32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -15162,13 +15299,13 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="C33" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D33" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E33" t="s">
         <v>142</v>
@@ -15177,10 +15314,10 @@
         <v>90</v>
       </c>
       <c r="G33">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -15198,19 +15335,19 @@
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="O33" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="P33" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="Q33" t="s">
-        <v>218</v>
+        <v>70</v>
       </c>
       <c r="R33" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="S33" t="s">
         <v>27</v>
@@ -15228,28 +15365,28 @@
         <v>27</v>
       </c>
       <c r="X33" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="Y33" t="s">
-        <v>219</v>
+        <v>27</v>
       </c>
       <c r="Z33">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="AA33">
+        <v>38</v>
+      </c>
+      <c r="AB33">
+        <v>2</v>
+      </c>
+      <c r="AC33">
         <v>13</v>
       </c>
-      <c r="AB33">
-        <v>9</v>
-      </c>
-      <c r="AC33">
-        <v>6</v>
-      </c>
       <c r="AD33">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF33">
         <v>0</v>
@@ -15264,19 +15401,19 @@
         <v>0</v>
       </c>
       <c r="AJ33">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK33">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AL33">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AM33" t="s">
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -15288,13 +15425,13 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>268</v>
       </c>
       <c r="C34" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="E34" t="s">
         <v>142</v>
@@ -15303,37 +15440,37 @@
         <v>90</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M34" t="s">
         <v>26</v>
       </c>
       <c r="N34" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="O34" t="s">
-        <v>27</v>
+        <v>231</v>
       </c>
       <c r="P34" t="s">
-        <v>27</v>
+        <v>232</v>
       </c>
       <c r="Q34" t="s">
-        <v>27</v>
+        <v>218</v>
       </c>
       <c r="R34" t="s">
         <v>27</v>
@@ -15354,25 +15491,25 @@
         <v>27</v>
       </c>
       <c r="X34" t="s">
-        <v>27</v>
+        <v>233</v>
       </c>
       <c r="Y34" t="s">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="Z34">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AA34">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AB34">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AC34">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE34">
         <v>0</v>
@@ -15390,19 +15527,19 @@
         <v>0</v>
       </c>
       <c r="AJ34">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AK34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM34" t="s">
         <v>84</v>
       </c>
       <c r="AN34" t="s">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -15417,10 +15554,10 @@
         <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D35" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E35" t="s">
         <v>142</v>
@@ -15438,7 +15575,7 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -15531,6 +15668,132 @@
         <v>186</v>
       </c>
       <c r="AO35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:41" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <f t="shared" si="1"/>
+        <v>134</v>
+      </c>
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" t="s">
+        <v>160</v>
+      </c>
+      <c r="D36" t="s">
+        <v>161</v>
+      </c>
+      <c r="E36" t="s">
+        <v>142</v>
+      </c>
+      <c r="F36">
+        <v>90</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>9999</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>10</v>
+      </c>
+      <c r="M36" t="s">
+        <v>26</v>
+      </c>
+      <c r="N36" t="s">
+        <v>27</v>
+      </c>
+      <c r="O36" t="s">
+        <v>27</v>
+      </c>
+      <c r="P36" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>27</v>
+      </c>
+      <c r="R36" t="s">
+        <v>27</v>
+      </c>
+      <c r="S36" t="s">
+        <v>27</v>
+      </c>
+      <c r="T36" t="s">
+        <v>27</v>
+      </c>
+      <c r="U36" t="s">
+        <v>27</v>
+      </c>
+      <c r="V36" t="s">
+        <v>27</v>
+      </c>
+      <c r="W36" t="s">
+        <v>27</v>
+      </c>
+      <c r="X36" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z36">
+        <v>60</v>
+      </c>
+      <c r="AA36">
+        <v>25</v>
+      </c>
+      <c r="AB36">
+        <v>12</v>
+      </c>
+      <c r="AC36">
+        <v>3</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36">
+        <v>0</v>
+      </c>
+      <c r="AI36">
+        <v>0</v>
+      </c>
+      <c r="AJ36">
+        <v>95</v>
+      </c>
+      <c r="AK36">
+        <v>5</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>186</v>
+      </c>
+      <c r="AO36">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3117842F-DD06-4587-9542-7468FF531F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80F7463-D170-42D3-83A6-E612B689305B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2715" yWindow="1335" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2805" yWindow="735" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2140" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2140" uniqueCount="291">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -1706,6 +1706,18 @@
     <rPh sb="6" eb="7">
       <t>ミセ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>autumn_enter_mini_icon</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>spring_enter_mini_icon</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>oldhouse_blue_mini_icon</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -8342,7 +8354,7 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>210</v>
+        <v>289</v>
       </c>
       <c r="C14" t="s">
         <v>241</v>
@@ -8594,7 +8606,7 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>210</v>
+        <v>288</v>
       </c>
       <c r="C16" t="s">
         <v>246</v>
@@ -9602,7 +9614,7 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="C24" t="s">
         <v>286</v>
@@ -12905,7 +12917,7 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>210</v>
+        <v>289</v>
       </c>
       <c r="C14" t="s">
         <v>241</v>
@@ -13157,7 +13169,7 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>210</v>
+        <v>288</v>
       </c>
       <c r="C16" t="s">
         <v>246</v>
@@ -14165,7 +14177,7 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="C24" t="s">
         <v>286</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80F7463-D170-42D3-83A6-E612B689305B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68C6BCD-7803-4C92-B0A4-C925AC85F38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2805" yWindow="735" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68C6BCD-7803-4C92-B0A4-C925AC85F38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A0EEB7-E57C-4677-8AA9-5F91A1CDEC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2140" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="293">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -1718,6 +1718,14 @@
   </si>
   <si>
     <t>oldhouse_blue_mini_icon</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Or_Hiroba_Summer_SodaIsland</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ソーダアイランド</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -6692,7 +6700,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAAE7BC7-74FC-4400-A474-EA5B977D362B}">
-  <dimension ref="A1:AO36"/>
+  <dimension ref="A1:AO37"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -7342,7 +7350,7 @@
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A6">
-        <f t="shared" ref="A6:A36" si="0">ROW()-2+100</f>
+        <f t="shared" ref="A6:A37" si="0">ROW()-2+100</f>
         <v>104</v>
       </c>
       <c r="B6" t="s">
@@ -8504,7 +8512,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -8606,13 +8614,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="C16" t="s">
-        <v>246</v>
+        <v>291</v>
       </c>
       <c r="D16" t="s">
-        <v>243</v>
+        <v>292</v>
       </c>
       <c r="E16" t="s">
         <v>48</v>
@@ -8636,7 +8644,7 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M16" t="s">
         <v>26</v>
@@ -8732,13 +8740,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="C17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E17" t="s">
         <v>48</v>
@@ -8762,7 +8770,7 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M17" t="s">
         <v>26</v>
@@ -8858,19 +8866,19 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="C18" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D18" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E18" t="s">
         <v>48</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -8888,7 +8896,7 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M18" t="s">
         <v>26</v>
@@ -8984,19 +8992,19 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>275</v>
       </c>
       <c r="C19" t="s">
-        <v>150</v>
+        <v>249</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>248</v>
       </c>
       <c r="E19" t="s">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -9008,7 +9016,7 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -9056,16 +9064,16 @@
         <v>27</v>
       </c>
       <c r="Z19">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AA19">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AB19">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AC19">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -9095,10 +9103,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="AN19" t="s">
-        <v>27</v>
+        <v>186</v>
       </c>
       <c r="AO19">
         <v>0</v>
@@ -9110,19 +9118,19 @@
         <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>253</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>239</v>
+        <v>150</v>
       </c>
       <c r="D20" t="s">
-        <v>238</v>
+        <v>149</v>
       </c>
       <c r="E20" t="s">
         <v>151</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -9236,19 +9244,19 @@
         <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>253</v>
       </c>
       <c r="C21" t="s">
-        <v>167</v>
+        <v>239</v>
       </c>
       <c r="D21" t="s">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="E21" t="s">
         <v>151</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -9260,7 +9268,7 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -9362,19 +9370,19 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>256</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>166</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>151</v>
       </c>
       <c r="F22">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -9386,7 +9394,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -9434,16 +9442,16 @@
         <v>27</v>
       </c>
       <c r="Z22">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA22">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB22">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AC22">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AD22">
         <v>0</v>
@@ -9488,19 +9496,19 @@
         <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>256</v>
       </c>
       <c r="C23" t="s">
-        <v>283</v>
+        <v>193</v>
       </c>
       <c r="D23" t="s">
-        <v>140</v>
+        <v>285</v>
       </c>
       <c r="E23" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="F23">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -9560,16 +9568,16 @@
         <v>27</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AA23">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AB23">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AC23">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AD23">
         <v>0</v>
@@ -9614,19 +9622,19 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>290</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>140</v>
       </c>
       <c r="E24" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -9644,7 +9652,7 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M24" t="s">
         <v>26</v>
@@ -9686,16 +9694,16 @@
         <v>27</v>
       </c>
       <c r="Z24">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA24">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB24">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AC24">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AD24">
         <v>0</v>
@@ -9725,10 +9733,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AN24" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -9740,52 +9748,52 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>290</v>
       </c>
       <c r="C25" t="s">
-        <v>194</v>
+        <v>286</v>
       </c>
       <c r="D25" t="s">
-        <v>152</v>
+        <v>287</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M25" t="s">
         <v>26</v>
       </c>
       <c r="N25" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="O25" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P25" t="s">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="Q25" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="R25" t="s">
         <v>27</v>
@@ -9806,25 +9814,25 @@
         <v>27</v>
       </c>
       <c r="X25" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="Y25" t="s">
         <v>27</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA25">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AD25">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE25">
         <v>0</v>
@@ -9842,19 +9850,19 @@
         <v>0</v>
       </c>
       <c r="AJ25">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AK25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AN25" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AO25">
         <v>0</v>
@@ -9866,19 +9874,19 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>262</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E26" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="F26">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -9902,25 +9910,25 @@
         <v>26</v>
       </c>
       <c r="N26" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O26" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="P26" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="Q26" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="R26" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="S26" t="s">
-        <v>282</v>
+        <v>27</v>
       </c>
       <c r="T26" t="s">
-        <v>191</v>
+        <v>27</v>
       </c>
       <c r="U26" t="s">
         <v>27</v>
@@ -9932,55 +9940,55 @@
         <v>27</v>
       </c>
       <c r="X26" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="Y26" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="Z26">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="AB26">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AC26">
+        <v>7</v>
+      </c>
+      <c r="AD26">
         <v>10</v>
       </c>
-      <c r="AD26">
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>98</v>
+      </c>
+      <c r="AK26">
         <v>2</v>
       </c>
-      <c r="AE26">
-        <v>10</v>
-      </c>
-      <c r="AF26">
-        <v>4</v>
-      </c>
-      <c r="AG26">
-        <v>26</v>
-      </c>
-      <c r="AH26">
-        <v>0</v>
-      </c>
-      <c r="AI26">
-        <v>0</v>
-      </c>
-      <c r="AJ26">
-        <v>78</v>
-      </c>
-      <c r="AK26">
-        <v>15</v>
-      </c>
       <c r="AL26">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AN26" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -9992,31 +10000,31 @@
         <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C27" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D27" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="E27" t="s">
         <v>116</v>
       </c>
       <c r="F27">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -10028,25 +10036,25 @@
         <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="O27" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="P27" t="s">
-        <v>224</v>
+        <v>25</v>
       </c>
       <c r="Q27" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="R27" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="S27" t="s">
-        <v>27</v>
+        <v>282</v>
       </c>
       <c r="T27" t="s">
-        <v>27</v>
+        <v>191</v>
       </c>
       <c r="U27" t="s">
         <v>27</v>
@@ -10058,34 +10066,34 @@
         <v>27</v>
       </c>
       <c r="X27" t="s">
-        <v>208</v>
+        <v>33</v>
       </c>
       <c r="Y27" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="Z27">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AA27">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AB27">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC27">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD27">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AE27">
         <v>10</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AH27">
         <v>0</v>
@@ -10094,19 +10102,19 @@
         <v>0</v>
       </c>
       <c r="AJ27">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AK27">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AL27">
         <v>7</v>
       </c>
       <c r="AM27" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AN27" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -10118,25 +10126,25 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C28" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D28" t="s">
-        <v>270</v>
+        <v>195</v>
       </c>
       <c r="E28" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F28">
         <v>30</v>
       </c>
       <c r="G28">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -10148,25 +10156,25 @@
         <v>1</v>
       </c>
       <c r="L28">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M28" t="s">
         <v>26</v>
       </c>
       <c r="N28" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P28" t="s">
-        <v>108</v>
+        <v>224</v>
       </c>
       <c r="Q28" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="R28" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="S28" t="s">
         <v>27</v>
@@ -10184,25 +10192,25 @@
         <v>27</v>
       </c>
       <c r="X28" t="s">
-        <v>111</v>
+        <v>208</v>
       </c>
       <c r="Y28" t="s">
-        <v>229</v>
+        <v>136</v>
       </c>
       <c r="Z28">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AA28">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB28">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AC28">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AD28">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AE28">
         <v>10</v>
@@ -10220,19 +10228,19 @@
         <v>0</v>
       </c>
       <c r="AJ28">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK28">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AL28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM28" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="AN28" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -10244,25 +10252,25 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="C29" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D29" t="s">
-        <v>197</v>
+        <v>270</v>
       </c>
       <c r="E29" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="F29">
         <v>30</v>
       </c>
       <c r="G29">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -10274,7 +10282,7 @@
         <v>1</v>
       </c>
       <c r="L29">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M29" t="s">
         <v>26</v>
@@ -10283,25 +10291,25 @@
         <v>72</v>
       </c>
       <c r="O29" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="P29" t="s">
         <v>108</v>
       </c>
       <c r="Q29" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="R29" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="S29" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="T29" t="s">
-        <v>222</v>
+        <v>27</v>
       </c>
       <c r="U29" t="s">
-        <v>250</v>
+        <v>27</v>
       </c>
       <c r="V29" t="s">
         <v>27</v>
@@ -10310,55 +10318,55 @@
         <v>27</v>
       </c>
       <c r="X29" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="Y29" t="s">
-        <v>111</v>
+        <v>229</v>
       </c>
       <c r="Z29">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AA29">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="AB29">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AC29">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AD29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE29">
         <v>10</v>
       </c>
       <c r="AF29">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>94</v>
+      </c>
+      <c r="AK29">
+        <v>1</v>
+      </c>
+      <c r="AL29">
         <v>5</v>
-      </c>
-      <c r="AI29">
-        <v>0</v>
-      </c>
-      <c r="AJ29">
-        <v>83</v>
-      </c>
-      <c r="AK29">
-        <v>16</v>
-      </c>
-      <c r="AL29">
-        <v>1</v>
       </c>
       <c r="AM29" t="s">
         <v>84</v>
       </c>
       <c r="AN29" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -10370,25 +10378,25 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="D30" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E30" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F30">
         <v>30</v>
       </c>
       <c r="G30">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H30">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -10400,34 +10408,34 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M30" t="s">
         <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
       <c r="O30" t="s">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="P30" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="Q30" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="R30" t="s">
-        <v>223</v>
+        <v>112</v>
       </c>
       <c r="S30" t="s">
-        <v>227</v>
+        <v>74</v>
       </c>
       <c r="T30" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="U30" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="V30" t="s">
         <v>27</v>
@@ -10436,55 +10444,55 @@
         <v>27</v>
       </c>
       <c r="X30" t="s">
-        <v>216</v>
+        <v>127</v>
       </c>
       <c r="Y30" t="s">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="Z30">
         <v>20</v>
       </c>
       <c r="AA30">
+        <v>5</v>
+      </c>
+      <c r="AB30">
         <v>20</v>
       </c>
-      <c r="AB30">
-        <v>17</v>
-      </c>
       <c r="AC30">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD30">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE30">
         <v>10</v>
       </c>
       <c r="AF30">
+        <v>13</v>
+      </c>
+      <c r="AG30">
         <v>10</v>
       </c>
-      <c r="AG30">
-        <v>0</v>
-      </c>
       <c r="AH30">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI30">
         <v>0</v>
       </c>
       <c r="AJ30">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AK30">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AL30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM30" t="s">
         <v>84</v>
       </c>
       <c r="AN30" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -10496,25 +10504,25 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C31" t="s">
-        <v>258</v>
+        <v>42</v>
       </c>
       <c r="D31" t="s">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="E31" t="s">
-        <v>259</v>
+        <v>50</v>
       </c>
       <c r="F31">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -10532,22 +10540,22 @@
         <v>26</v>
       </c>
       <c r="N31" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="O31" t="s">
-        <v>27</v>
+        <v>221</v>
       </c>
       <c r="P31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q31" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="R31" t="s">
-        <v>27</v>
+        <v>223</v>
       </c>
       <c r="S31" t="s">
-        <v>27</v>
+        <v>227</v>
       </c>
       <c r="T31" t="s">
         <v>27</v>
@@ -10562,31 +10570,31 @@
         <v>27</v>
       </c>
       <c r="X31" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="Y31" t="s">
-        <v>27</v>
+        <v>269</v>
       </c>
       <c r="Z31">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB31">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AC31">
         <v>13</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG31">
         <v>0</v>
@@ -10598,19 +10606,19 @@
         <v>0</v>
       </c>
       <c r="AJ31">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="AK31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM31" t="s">
         <v>84</v>
       </c>
       <c r="AN31" t="s">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -10622,25 +10630,25 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C32" t="s">
-        <v>202</v>
+        <v>258</v>
       </c>
       <c r="D32" t="s">
-        <v>198</v>
+        <v>260</v>
       </c>
       <c r="E32" t="s">
-        <v>116</v>
+        <v>259</v>
       </c>
       <c r="F32">
         <v>60</v>
       </c>
       <c r="G32">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -10652,34 +10660,34 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M32" t="s">
         <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="O32" t="s">
-        <v>215</v>
+        <v>27</v>
       </c>
       <c r="P32" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="Q32" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="R32" t="s">
-        <v>257</v>
+        <v>27</v>
       </c>
       <c r="S32" t="s">
         <v>27</v>
       </c>
       <c r="T32" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="U32" t="s">
-        <v>228</v>
+        <v>27</v>
       </c>
       <c r="V32" t="s">
         <v>27</v>
@@ -10688,55 +10696,55 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="Y32" t="s">
-        <v>216</v>
+        <v>27</v>
       </c>
       <c r="Z32">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AA32">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AD32">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI32">
         <v>0</v>
       </c>
       <c r="AJ32">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="AK32">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AL32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AM32" t="s">
         <v>84</v>
       </c>
       <c r="AN32" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -10748,25 +10756,25 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C33" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D33" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E33" t="s">
         <v>116</v>
       </c>
       <c r="F33">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G33">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="H33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -10778,34 +10786,34 @@
         <v>1</v>
       </c>
       <c r="L33">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M33" t="s">
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="O33" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="P33" t="s">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="Q33" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="R33" t="s">
-        <v>103</v>
+        <v>257</v>
       </c>
       <c r="S33" t="s">
         <v>27</v>
       </c>
       <c r="T33" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="U33" t="s">
-        <v>27</v>
+        <v>228</v>
       </c>
       <c r="V33" t="s">
         <v>27</v>
@@ -10814,55 +10822,55 @@
         <v>27</v>
       </c>
       <c r="X33" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="Y33" t="s">
-        <v>27</v>
+        <v>216</v>
       </c>
       <c r="Z33">
         <v>20</v>
       </c>
       <c r="AA33">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AB33">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC33">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AD33">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE33">
         <v>10</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI33">
         <v>0</v>
       </c>
       <c r="AJ33">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AK33">
         <v>10</v>
       </c>
       <c r="AL33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AM33" t="s">
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -10874,25 +10882,25 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="C34" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D34" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E34" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F34">
         <v>90</v>
       </c>
       <c r="G34">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -10910,19 +10918,19 @@
         <v>26</v>
       </c>
       <c r="N34" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="O34" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="P34" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="Q34" t="s">
-        <v>218</v>
+        <v>70</v>
       </c>
       <c r="R34" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="S34" t="s">
         <v>27</v>
@@ -10940,28 +10948,28 @@
         <v>27</v>
       </c>
       <c r="X34" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="Y34" t="s">
-        <v>219</v>
+        <v>27</v>
       </c>
       <c r="Z34">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="AA34">
+        <v>38</v>
+      </c>
+      <c r="AB34">
+        <v>2</v>
+      </c>
+      <c r="AC34">
         <v>13</v>
       </c>
-      <c r="AB34">
-        <v>9</v>
-      </c>
-      <c r="AC34">
-        <v>6</v>
-      </c>
       <c r="AD34">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF34">
         <v>0</v>
@@ -10976,19 +10984,19 @@
         <v>0</v>
       </c>
       <c r="AJ34">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK34">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AL34">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AM34" t="s">
         <v>84</v>
       </c>
       <c r="AN34" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -11000,52 +11008,52 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>268</v>
       </c>
       <c r="C35" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="E35" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F35">
         <v>90</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M35" t="s">
         <v>26</v>
       </c>
       <c r="N35" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="O35" t="s">
-        <v>27</v>
+        <v>231</v>
       </c>
       <c r="P35" t="s">
-        <v>27</v>
+        <v>232</v>
       </c>
       <c r="Q35" t="s">
-        <v>27</v>
+        <v>218</v>
       </c>
       <c r="R35" t="s">
         <v>27</v>
@@ -11066,25 +11074,25 @@
         <v>27</v>
       </c>
       <c r="X35" t="s">
-        <v>27</v>
+        <v>233</v>
       </c>
       <c r="Y35" t="s">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="Z35">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AA35">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AB35">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AC35">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE35">
         <v>0</v>
@@ -11102,19 +11110,19 @@
         <v>0</v>
       </c>
       <c r="AJ35">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AK35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM35" t="s">
         <v>84</v>
       </c>
       <c r="AN35" t="s">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="AO35">
         <v>0</v>
@@ -11129,10 +11137,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D36" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s">
         <v>48</v>
@@ -11150,7 +11158,7 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -11243,6 +11251,132 @@
         <v>186</v>
       </c>
       <c r="AO36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:41" x14ac:dyDescent="0.4">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>135</v>
+      </c>
+      <c r="B37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" t="s">
+        <v>160</v>
+      </c>
+      <c r="D37" t="s">
+        <v>161</v>
+      </c>
+      <c r="E37" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37">
+        <v>90</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>9999</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>10</v>
+      </c>
+      <c r="M37" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" t="s">
+        <v>27</v>
+      </c>
+      <c r="O37" t="s">
+        <v>27</v>
+      </c>
+      <c r="P37" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>27</v>
+      </c>
+      <c r="R37" t="s">
+        <v>27</v>
+      </c>
+      <c r="S37" t="s">
+        <v>27</v>
+      </c>
+      <c r="T37" t="s">
+        <v>27</v>
+      </c>
+      <c r="U37" t="s">
+        <v>27</v>
+      </c>
+      <c r="V37" t="s">
+        <v>27</v>
+      </c>
+      <c r="W37" t="s">
+        <v>27</v>
+      </c>
+      <c r="X37" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z37">
+        <v>60</v>
+      </c>
+      <c r="AA37">
+        <v>25</v>
+      </c>
+      <c r="AB37">
+        <v>12</v>
+      </c>
+      <c r="AC37">
+        <v>3</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37">
+        <v>0</v>
+      </c>
+      <c r="AI37">
+        <v>0</v>
+      </c>
+      <c r="AJ37">
+        <v>95</v>
+      </c>
+      <c r="AK37">
+        <v>5</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>186</v>
+      </c>
+      <c r="AO37">
         <v>1</v>
       </c>
     </row>
@@ -11255,7 +11389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAD14E5B-6BFE-4D20-B771-5A2DB6950621}">
-  <dimension ref="A1:AO36"/>
+  <dimension ref="A1:AO37"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -12409,7 +12543,7 @@
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A10">
-        <f t="shared" ref="A10:A36" si="1">ROW()-2+100</f>
+        <f t="shared" ref="A10:A37" si="1">ROW()-2+100</f>
         <v>108</v>
       </c>
       <c r="B10" t="s">
@@ -13067,7 +13201,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -13169,13 +13303,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="C16" t="s">
-        <v>246</v>
+        <v>291</v>
       </c>
       <c r="D16" t="s">
-        <v>243</v>
+        <v>292</v>
       </c>
       <c r="E16" t="s">
         <v>142</v>
@@ -13199,7 +13333,7 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M16" t="s">
         <v>26</v>
@@ -13295,13 +13429,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="C17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E17" t="s">
         <v>142</v>
@@ -13325,7 +13459,7 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M17" t="s">
         <v>26</v>
@@ -13421,19 +13555,19 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="C18" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D18" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E18" t="s">
         <v>142</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -13451,7 +13585,7 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M18" t="s">
         <v>26</v>
@@ -13547,19 +13681,19 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>275</v>
       </c>
       <c r="C19" t="s">
-        <v>150</v>
+        <v>249</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>248</v>
       </c>
       <c r="E19" t="s">
         <v>142</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -13571,7 +13705,7 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -13619,16 +13753,16 @@
         <v>27</v>
       </c>
       <c r="Z19">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AA19">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AB19">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AC19">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -13658,10 +13792,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="AN19" t="s">
-        <v>27</v>
+        <v>186</v>
       </c>
       <c r="AO19">
         <v>0</v>
@@ -13673,19 +13807,19 @@
         <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>253</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>239</v>
+        <v>150</v>
       </c>
       <c r="D20" t="s">
-        <v>238</v>
+        <v>149</v>
       </c>
       <c r="E20" t="s">
         <v>142</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -13799,19 +13933,19 @@
         <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>253</v>
       </c>
       <c r="C21" t="s">
-        <v>167</v>
+        <v>239</v>
       </c>
       <c r="D21" t="s">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="E21" t="s">
         <v>142</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -13823,7 +13957,7 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -13925,19 +14059,19 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>256</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>166</v>
       </c>
       <c r="E22" t="s">
         <v>142</v>
       </c>
       <c r="F22">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -13949,7 +14083,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -13997,16 +14131,16 @@
         <v>27</v>
       </c>
       <c r="Z22">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA22">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB22">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AC22">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AD22">
         <v>0</v>
@@ -14051,19 +14185,19 @@
         <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>256</v>
       </c>
       <c r="C23" t="s">
-        <v>283</v>
+        <v>193</v>
       </c>
       <c r="D23" t="s">
-        <v>140</v>
+        <v>285</v>
       </c>
       <c r="E23" t="s">
         <v>142</v>
       </c>
       <c r="F23">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -14123,16 +14257,16 @@
         <v>27</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AA23">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AB23">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AC23">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AD23">
         <v>0</v>
@@ -14177,19 +14311,19 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>290</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>140</v>
       </c>
       <c r="E24" t="s">
         <v>142</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -14207,7 +14341,7 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M24" t="s">
         <v>26</v>
@@ -14249,16 +14383,16 @@
         <v>27</v>
       </c>
       <c r="Z24">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA24">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB24">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AC24">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AD24">
         <v>0</v>
@@ -14288,10 +14422,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AN24" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -14303,52 +14437,52 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>290</v>
       </c>
       <c r="C25" t="s">
-        <v>194</v>
+        <v>286</v>
       </c>
       <c r="D25" t="s">
-        <v>152</v>
+        <v>287</v>
       </c>
       <c r="E25" t="s">
         <v>142</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M25" t="s">
         <v>26</v>
       </c>
       <c r="N25" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="O25" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P25" t="s">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="Q25" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="R25" t="s">
         <v>27</v>
@@ -14369,25 +14503,25 @@
         <v>27</v>
       </c>
       <c r="X25" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="Y25" t="s">
         <v>27</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA25">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AD25">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE25">
         <v>0</v>
@@ -14405,19 +14539,19 @@
         <v>0</v>
       </c>
       <c r="AJ25">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AK25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AN25" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AO25">
         <v>0</v>
@@ -14429,19 +14563,19 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>262</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E26" t="s">
         <v>142</v>
       </c>
       <c r="F26">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -14465,25 +14599,25 @@
         <v>26</v>
       </c>
       <c r="N26" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O26" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="P26" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="Q26" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="R26" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="S26" t="s">
-        <v>282</v>
+        <v>27</v>
       </c>
       <c r="T26" t="s">
-        <v>191</v>
+        <v>27</v>
       </c>
       <c r="U26" t="s">
         <v>27</v>
@@ -14495,55 +14629,55 @@
         <v>27</v>
       </c>
       <c r="X26" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="Y26" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="Z26">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="AB26">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AC26">
+        <v>7</v>
+      </c>
+      <c r="AD26">
         <v>10</v>
       </c>
-      <c r="AD26">
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>98</v>
+      </c>
+      <c r="AK26">
         <v>2</v>
       </c>
-      <c r="AE26">
-        <v>10</v>
-      </c>
-      <c r="AF26">
-        <v>4</v>
-      </c>
-      <c r="AG26">
-        <v>26</v>
-      </c>
-      <c r="AH26">
-        <v>0</v>
-      </c>
-      <c r="AI26">
-        <v>0</v>
-      </c>
-      <c r="AJ26">
-        <v>78</v>
-      </c>
-      <c r="AK26">
-        <v>15</v>
-      </c>
       <c r="AL26">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AN26" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -14555,31 +14689,31 @@
         <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C27" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D27" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="E27" t="s">
         <v>142</v>
       </c>
       <c r="F27">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -14591,25 +14725,25 @@
         <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="O27" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="P27" t="s">
-        <v>224</v>
+        <v>25</v>
       </c>
       <c r="Q27" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="R27" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="S27" t="s">
-        <v>27</v>
+        <v>282</v>
       </c>
       <c r="T27" t="s">
-        <v>27</v>
+        <v>191</v>
       </c>
       <c r="U27" t="s">
         <v>27</v>
@@ -14621,34 +14755,34 @@
         <v>27</v>
       </c>
       <c r="X27" t="s">
-        <v>208</v>
+        <v>33</v>
       </c>
       <c r="Y27" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="Z27">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AA27">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AB27">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC27">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD27">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AE27">
         <v>10</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AH27">
         <v>0</v>
@@ -14657,19 +14791,19 @@
         <v>0</v>
       </c>
       <c r="AJ27">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AK27">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AL27">
         <v>7</v>
       </c>
       <c r="AM27" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AN27" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -14681,13 +14815,13 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C28" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D28" t="s">
-        <v>270</v>
+        <v>195</v>
       </c>
       <c r="E28" t="s">
         <v>142</v>
@@ -14696,10 +14830,10 @@
         <v>30</v>
       </c>
       <c r="G28">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -14711,25 +14845,25 @@
         <v>1</v>
       </c>
       <c r="L28">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M28" t="s">
         <v>26</v>
       </c>
       <c r="N28" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P28" t="s">
-        <v>108</v>
+        <v>224</v>
       </c>
       <c r="Q28" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="R28" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="S28" t="s">
         <v>27</v>
@@ -14747,25 +14881,25 @@
         <v>27</v>
       </c>
       <c r="X28" t="s">
-        <v>111</v>
+        <v>208</v>
       </c>
       <c r="Y28" t="s">
-        <v>229</v>
+        <v>136</v>
       </c>
       <c r="Z28">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AA28">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB28">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AC28">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AD28">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AE28">
         <v>10</v>
@@ -14783,19 +14917,19 @@
         <v>0</v>
       </c>
       <c r="AJ28">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK28">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AL28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM28" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="AN28" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -14807,13 +14941,13 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="C29" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D29" t="s">
-        <v>197</v>
+        <v>270</v>
       </c>
       <c r="E29" t="s">
         <v>142</v>
@@ -14822,10 +14956,10 @@
         <v>30</v>
       </c>
       <c r="G29">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -14837,7 +14971,7 @@
         <v>1</v>
       </c>
       <c r="L29">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M29" t="s">
         <v>26</v>
@@ -14846,25 +14980,25 @@
         <v>72</v>
       </c>
       <c r="O29" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="P29" t="s">
         <v>108</v>
       </c>
       <c r="Q29" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="R29" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="S29" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="T29" t="s">
-        <v>222</v>
+        <v>27</v>
       </c>
       <c r="U29" t="s">
-        <v>250</v>
+        <v>27</v>
       </c>
       <c r="V29" t="s">
         <v>27</v>
@@ -14873,55 +15007,55 @@
         <v>27</v>
       </c>
       <c r="X29" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="Y29" t="s">
-        <v>111</v>
+        <v>229</v>
       </c>
       <c r="Z29">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AA29">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="AB29">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AC29">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AD29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE29">
         <v>10</v>
       </c>
       <c r="AF29">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>94</v>
+      </c>
+      <c r="AK29">
+        <v>1</v>
+      </c>
+      <c r="AL29">
         <v>5</v>
-      </c>
-      <c r="AI29">
-        <v>0</v>
-      </c>
-      <c r="AJ29">
-        <v>83</v>
-      </c>
-      <c r="AK29">
-        <v>16</v>
-      </c>
-      <c r="AL29">
-        <v>1</v>
       </c>
       <c r="AM29" t="s">
         <v>84</v>
       </c>
       <c r="AN29" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -14933,13 +15067,13 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="D30" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E30" t="s">
         <v>142</v>
@@ -14948,10 +15082,10 @@
         <v>30</v>
       </c>
       <c r="G30">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H30">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -14963,34 +15097,34 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M30" t="s">
         <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
       <c r="O30" t="s">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="P30" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="Q30" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="R30" t="s">
-        <v>223</v>
+        <v>112</v>
       </c>
       <c r="S30" t="s">
-        <v>227</v>
+        <v>74</v>
       </c>
       <c r="T30" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="U30" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="V30" t="s">
         <v>27</v>
@@ -14999,55 +15133,55 @@
         <v>27</v>
       </c>
       <c r="X30" t="s">
-        <v>216</v>
+        <v>127</v>
       </c>
       <c r="Y30" t="s">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="Z30">
         <v>20</v>
       </c>
       <c r="AA30">
+        <v>5</v>
+      </c>
+      <c r="AB30">
         <v>20</v>
       </c>
-      <c r="AB30">
-        <v>17</v>
-      </c>
       <c r="AC30">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD30">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE30">
         <v>10</v>
       </c>
       <c r="AF30">
+        <v>13</v>
+      </c>
+      <c r="AG30">
         <v>10</v>
       </c>
-      <c r="AG30">
-        <v>0</v>
-      </c>
       <c r="AH30">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI30">
         <v>0</v>
       </c>
       <c r="AJ30">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AK30">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AL30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM30" t="s">
         <v>84</v>
       </c>
       <c r="AN30" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -15059,25 +15193,25 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C31" t="s">
-        <v>258</v>
+        <v>42</v>
       </c>
       <c r="D31" t="s">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="E31" t="s">
         <v>142</v>
       </c>
       <c r="F31">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -15095,22 +15229,22 @@
         <v>26</v>
       </c>
       <c r="N31" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="O31" t="s">
-        <v>27</v>
+        <v>221</v>
       </c>
       <c r="P31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q31" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="R31" t="s">
-        <v>27</v>
+        <v>223</v>
       </c>
       <c r="S31" t="s">
-        <v>27</v>
+        <v>227</v>
       </c>
       <c r="T31" t="s">
         <v>27</v>
@@ -15125,31 +15259,31 @@
         <v>27</v>
       </c>
       <c r="X31" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="Y31" t="s">
-        <v>27</v>
+        <v>269</v>
       </c>
       <c r="Z31">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB31">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AC31">
         <v>13</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG31">
         <v>0</v>
@@ -15161,19 +15295,19 @@
         <v>0</v>
       </c>
       <c r="AJ31">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="AK31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM31" t="s">
         <v>84</v>
       </c>
       <c r="AN31" t="s">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -15185,13 +15319,13 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C32" t="s">
-        <v>202</v>
+        <v>258</v>
       </c>
       <c r="D32" t="s">
-        <v>198</v>
+        <v>260</v>
       </c>
       <c r="E32" t="s">
         <v>142</v>
@@ -15200,10 +15334,10 @@
         <v>60</v>
       </c>
       <c r="G32">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -15215,34 +15349,34 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M32" t="s">
         <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="O32" t="s">
-        <v>215</v>
+        <v>27</v>
       </c>
       <c r="P32" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="Q32" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="R32" t="s">
-        <v>257</v>
+        <v>27</v>
       </c>
       <c r="S32" t="s">
         <v>27</v>
       </c>
       <c r="T32" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="U32" t="s">
-        <v>228</v>
+        <v>27</v>
       </c>
       <c r="V32" t="s">
         <v>27</v>
@@ -15251,55 +15385,55 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="Y32" t="s">
-        <v>216</v>
+        <v>27</v>
       </c>
       <c r="Z32">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AA32">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AD32">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI32">
         <v>0</v>
       </c>
       <c r="AJ32">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="AK32">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AL32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AM32" t="s">
         <v>84</v>
       </c>
       <c r="AN32" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -15311,25 +15445,25 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C33" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D33" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E33" t="s">
         <v>142</v>
       </c>
       <c r="F33">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G33">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="H33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -15341,34 +15475,34 @@
         <v>1</v>
       </c>
       <c r="L33">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M33" t="s">
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="O33" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="P33" t="s">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="Q33" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="R33" t="s">
-        <v>103</v>
+        <v>257</v>
       </c>
       <c r="S33" t="s">
         <v>27</v>
       </c>
       <c r="T33" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="U33" t="s">
-        <v>27</v>
+        <v>228</v>
       </c>
       <c r="V33" t="s">
         <v>27</v>
@@ -15377,55 +15511,55 @@
         <v>27</v>
       </c>
       <c r="X33" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="Y33" t="s">
-        <v>27</v>
+        <v>216</v>
       </c>
       <c r="Z33">
         <v>20</v>
       </c>
       <c r="AA33">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AB33">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC33">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AD33">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE33">
         <v>10</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI33">
         <v>0</v>
       </c>
       <c r="AJ33">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AK33">
         <v>10</v>
       </c>
       <c r="AL33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AM33" t="s">
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -15437,13 +15571,13 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="C34" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D34" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E34" t="s">
         <v>142</v>
@@ -15452,10 +15586,10 @@
         <v>90</v>
       </c>
       <c r="G34">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -15473,19 +15607,19 @@
         <v>26</v>
       </c>
       <c r="N34" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="O34" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="P34" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="Q34" t="s">
-        <v>218</v>
+        <v>70</v>
       </c>
       <c r="R34" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="S34" t="s">
         <v>27</v>
@@ -15503,28 +15637,28 @@
         <v>27</v>
       </c>
       <c r="X34" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="Y34" t="s">
-        <v>219</v>
+        <v>27</v>
       </c>
       <c r="Z34">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="AA34">
+        <v>38</v>
+      </c>
+      <c r="AB34">
+        <v>2</v>
+      </c>
+      <c r="AC34">
         <v>13</v>
       </c>
-      <c r="AB34">
-        <v>9</v>
-      </c>
-      <c r="AC34">
-        <v>6</v>
-      </c>
       <c r="AD34">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF34">
         <v>0</v>
@@ -15539,19 +15673,19 @@
         <v>0</v>
       </c>
       <c r="AJ34">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK34">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AL34">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AM34" t="s">
         <v>84</v>
       </c>
       <c r="AN34" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -15563,13 +15697,13 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>268</v>
       </c>
       <c r="C35" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="E35" t="s">
         <v>142</v>
@@ -15578,37 +15712,37 @@
         <v>90</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M35" t="s">
         <v>26</v>
       </c>
       <c r="N35" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="O35" t="s">
-        <v>27</v>
+        <v>231</v>
       </c>
       <c r="P35" t="s">
-        <v>27</v>
+        <v>232</v>
       </c>
       <c r="Q35" t="s">
-        <v>27</v>
+        <v>218</v>
       </c>
       <c r="R35" t="s">
         <v>27</v>
@@ -15629,25 +15763,25 @@
         <v>27</v>
       </c>
       <c r="X35" t="s">
-        <v>27</v>
+        <v>233</v>
       </c>
       <c r="Y35" t="s">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="Z35">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AA35">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AB35">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AC35">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE35">
         <v>0</v>
@@ -15665,19 +15799,19 @@
         <v>0</v>
       </c>
       <c r="AJ35">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AK35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM35" t="s">
         <v>84</v>
       </c>
       <c r="AN35" t="s">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="AO35">
         <v>0</v>
@@ -15692,10 +15826,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D36" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s">
         <v>142</v>
@@ -15713,7 +15847,7 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -15806,6 +15940,132 @@
         <v>186</v>
       </c>
       <c r="AO36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:41" x14ac:dyDescent="0.4">
+      <c r="A37">
+        <f t="shared" si="1"/>
+        <v>135</v>
+      </c>
+      <c r="B37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" t="s">
+        <v>160</v>
+      </c>
+      <c r="D37" t="s">
+        <v>161</v>
+      </c>
+      <c r="E37" t="s">
+        <v>142</v>
+      </c>
+      <c r="F37">
+        <v>90</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>9999</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>10</v>
+      </c>
+      <c r="M37" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" t="s">
+        <v>27</v>
+      </c>
+      <c r="O37" t="s">
+        <v>27</v>
+      </c>
+      <c r="P37" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>27</v>
+      </c>
+      <c r="R37" t="s">
+        <v>27</v>
+      </c>
+      <c r="S37" t="s">
+        <v>27</v>
+      </c>
+      <c r="T37" t="s">
+        <v>27</v>
+      </c>
+      <c r="U37" t="s">
+        <v>27</v>
+      </c>
+      <c r="V37" t="s">
+        <v>27</v>
+      </c>
+      <c r="W37" t="s">
+        <v>27</v>
+      </c>
+      <c r="X37" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z37">
+        <v>60</v>
+      </c>
+      <c r="AA37">
+        <v>25</v>
+      </c>
+      <c r="AB37">
+        <v>12</v>
+      </c>
+      <c r="AC37">
+        <v>3</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37">
+        <v>0</v>
+      </c>
+      <c r="AI37">
+        <v>0</v>
+      </c>
+      <c r="AJ37">
+        <v>95</v>
+      </c>
+      <c r="AK37">
+        <v>5</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>186</v>
+      </c>
+      <c r="AO37">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A0EEB7-E57C-4677-8AA9-5F91A1CDEC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A3FD98-51BA-48A0-B514-62AA191D6188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1560" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="295">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -1726,6 +1726,23 @@
   </si>
   <si>
     <t>ソーダアイランド</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Or_Hiroba1_Roten</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>春の露店通り</t>
+    <rPh sb="0" eb="1">
+      <t>ハル</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ロテン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ドオ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -6700,7 +6717,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAAE7BC7-74FC-4400-A474-EA5B977D362B}">
-  <dimension ref="A1:AO37"/>
+  <dimension ref="A1:AO38"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -7350,7 +7367,7 @@
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A6">
-        <f t="shared" ref="A6:A37" si="0">ROW()-2+100</f>
+        <f t="shared" ref="A6:A38" si="0">ROW()-2+100</f>
         <v>104</v>
       </c>
       <c r="B6" t="s">
@@ -7882,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -8008,7 +8025,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -8134,7 +8151,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -8260,7 +8277,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -8386,7 +8403,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -8764,7 +8781,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -8890,7 +8907,7 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -9244,19 +9261,19 @@
         <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>253</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>239</v>
+        <v>293</v>
       </c>
       <c r="D21" t="s">
-        <v>238</v>
+        <v>294</v>
       </c>
       <c r="E21" t="s">
         <v>151</v>
       </c>
       <c r="F21">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -9370,19 +9387,19 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>253</v>
       </c>
       <c r="C22" t="s">
-        <v>167</v>
+        <v>239</v>
       </c>
       <c r="D22" t="s">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="E22" t="s">
         <v>151</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -9394,7 +9411,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -9496,19 +9513,19 @@
         <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>256</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>166</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>151</v>
       </c>
       <c r="F23">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -9520,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -9568,16 +9585,16 @@
         <v>27</v>
       </c>
       <c r="Z23">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA23">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB23">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AC23">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AD23">
         <v>0</v>
@@ -9622,19 +9639,19 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>256</v>
       </c>
       <c r="C24" t="s">
-        <v>283</v>
+        <v>193</v>
       </c>
       <c r="D24" t="s">
-        <v>140</v>
+        <v>285</v>
       </c>
       <c r="E24" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="F24">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -9694,16 +9711,16 @@
         <v>27</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AA24">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AB24">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AC24">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AD24">
         <v>0</v>
@@ -9748,19 +9765,19 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>290</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>140</v>
       </c>
       <c r="E25" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -9778,7 +9795,7 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M25" t="s">
         <v>26</v>
@@ -9820,16 +9837,16 @@
         <v>27</v>
       </c>
       <c r="Z25">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA25">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB25">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AC25">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AD25">
         <v>0</v>
@@ -9859,10 +9876,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AN25" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="AO25">
         <v>0</v>
@@ -9874,52 +9891,52 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>290</v>
       </c>
       <c r="C26" t="s">
-        <v>194</v>
+        <v>286</v>
       </c>
       <c r="D26" t="s">
-        <v>152</v>
+        <v>287</v>
       </c>
       <c r="E26" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M26" t="s">
         <v>26</v>
       </c>
       <c r="N26" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="O26" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P26" t="s">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="Q26" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="R26" t="s">
         <v>27</v>
@@ -9940,25 +9957,25 @@
         <v>27</v>
       </c>
       <c r="X26" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="Y26" t="s">
         <v>27</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA26">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC26">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE26">
         <v>0</v>
@@ -9976,19 +9993,19 @@
         <v>0</v>
       </c>
       <c r="AJ26">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AK26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AN26" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -10000,19 +10017,19 @@
         <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>262</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E27" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="F27">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -10036,25 +10053,25 @@
         <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O27" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="P27" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="Q27" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="R27" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="S27" t="s">
-        <v>282</v>
+        <v>27</v>
       </c>
       <c r="T27" t="s">
-        <v>191</v>
+        <v>27</v>
       </c>
       <c r="U27" t="s">
         <v>27</v>
@@ -10066,55 +10083,55 @@
         <v>27</v>
       </c>
       <c r="X27" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="Y27" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="Z27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="AB27">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AC27">
+        <v>7</v>
+      </c>
+      <c r="AD27">
         <v>10</v>
       </c>
-      <c r="AD27">
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <v>98</v>
+      </c>
+      <c r="AK27">
         <v>2</v>
       </c>
-      <c r="AE27">
-        <v>10</v>
-      </c>
-      <c r="AF27">
-        <v>4</v>
-      </c>
-      <c r="AG27">
-        <v>26</v>
-      </c>
-      <c r="AH27">
-        <v>0</v>
-      </c>
-      <c r="AI27">
-        <v>0</v>
-      </c>
-      <c r="AJ27">
-        <v>78</v>
-      </c>
-      <c r="AK27">
-        <v>15</v>
-      </c>
       <c r="AL27">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AN27" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -10126,31 +10143,31 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C28" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D28" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="E28" t="s">
         <v>116</v>
       </c>
       <c r="F28">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -10162,25 +10179,25 @@
         <v>26</v>
       </c>
       <c r="N28" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="O28" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="P28" t="s">
-        <v>224</v>
+        <v>25</v>
       </c>
       <c r="Q28" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="R28" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="S28" t="s">
-        <v>27</v>
+        <v>282</v>
       </c>
       <c r="T28" t="s">
-        <v>27</v>
+        <v>191</v>
       </c>
       <c r="U28" t="s">
         <v>27</v>
@@ -10192,34 +10209,34 @@
         <v>27</v>
       </c>
       <c r="X28" t="s">
-        <v>208</v>
+        <v>33</v>
       </c>
       <c r="Y28" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="Z28">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AA28">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AB28">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC28">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD28">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AE28">
         <v>10</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AH28">
         <v>0</v>
@@ -10228,19 +10245,19 @@
         <v>0</v>
       </c>
       <c r="AJ28">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AK28">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AL28">
         <v>7</v>
       </c>
       <c r="AM28" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AN28" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -10252,25 +10269,25 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C29" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D29" t="s">
-        <v>270</v>
+        <v>195</v>
       </c>
       <c r="E29" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F29">
         <v>30</v>
       </c>
       <c r="G29">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -10282,25 +10299,25 @@
         <v>1</v>
       </c>
       <c r="L29">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M29" t="s">
         <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P29" t="s">
-        <v>108</v>
+        <v>224</v>
       </c>
       <c r="Q29" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="R29" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="S29" t="s">
         <v>27</v>
@@ -10318,25 +10335,25 @@
         <v>27</v>
       </c>
       <c r="X29" t="s">
-        <v>111</v>
+        <v>208</v>
       </c>
       <c r="Y29" t="s">
-        <v>229</v>
+        <v>136</v>
       </c>
       <c r="Z29">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AA29">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB29">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AC29">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AD29">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AE29">
         <v>10</v>
@@ -10354,19 +10371,19 @@
         <v>0</v>
       </c>
       <c r="AJ29">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK29">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AL29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM29" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="AN29" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -10378,25 +10395,25 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="C30" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D30" t="s">
-        <v>197</v>
+        <v>270</v>
       </c>
       <c r="E30" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="F30">
         <v>30</v>
       </c>
       <c r="G30">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -10408,7 +10425,7 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M30" t="s">
         <v>26</v>
@@ -10417,25 +10434,25 @@
         <v>72</v>
       </c>
       <c r="O30" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="P30" t="s">
         <v>108</v>
       </c>
       <c r="Q30" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="R30" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="S30" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="T30" t="s">
-        <v>222</v>
+        <v>27</v>
       </c>
       <c r="U30" t="s">
-        <v>250</v>
+        <v>27</v>
       </c>
       <c r="V30" t="s">
         <v>27</v>
@@ -10444,55 +10461,55 @@
         <v>27</v>
       </c>
       <c r="X30" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="Y30" t="s">
-        <v>111</v>
+        <v>229</v>
       </c>
       <c r="Z30">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AA30">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="AB30">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AC30">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AD30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE30">
         <v>10</v>
       </c>
       <c r="AF30">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <v>94</v>
+      </c>
+      <c r="AK30">
+        <v>1</v>
+      </c>
+      <c r="AL30">
         <v>5</v>
-      </c>
-      <c r="AI30">
-        <v>0</v>
-      </c>
-      <c r="AJ30">
-        <v>83</v>
-      </c>
-      <c r="AK30">
-        <v>16</v>
-      </c>
-      <c r="AL30">
-        <v>1</v>
       </c>
       <c r="AM30" t="s">
         <v>84</v>
       </c>
       <c r="AN30" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -10504,25 +10521,25 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="D31" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E31" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F31">
         <v>30</v>
       </c>
       <c r="G31">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -10540,28 +10557,28 @@
         <v>26</v>
       </c>
       <c r="N31" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
       <c r="O31" t="s">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="P31" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="Q31" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="R31" t="s">
-        <v>223</v>
+        <v>112</v>
       </c>
       <c r="S31" t="s">
-        <v>227</v>
+        <v>74</v>
       </c>
       <c r="T31" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="U31" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -10570,55 +10587,55 @@
         <v>27</v>
       </c>
       <c r="X31" t="s">
-        <v>216</v>
+        <v>127</v>
       </c>
       <c r="Y31" t="s">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="Z31">
         <v>20</v>
       </c>
       <c r="AA31">
+        <v>5</v>
+      </c>
+      <c r="AB31">
         <v>20</v>
       </c>
-      <c r="AB31">
-        <v>17</v>
-      </c>
       <c r="AC31">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE31">
         <v>10</v>
       </c>
       <c r="AF31">
+        <v>13</v>
+      </c>
+      <c r="AG31">
         <v>10</v>
       </c>
-      <c r="AG31">
-        <v>0</v>
-      </c>
       <c r="AH31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI31">
         <v>0</v>
       </c>
       <c r="AJ31">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AK31">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AL31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM31" t="s">
         <v>84</v>
       </c>
       <c r="AN31" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -10630,25 +10647,25 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C32" t="s">
-        <v>258</v>
+        <v>42</v>
       </c>
       <c r="D32" t="s">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="E32" t="s">
-        <v>259</v>
+        <v>50</v>
       </c>
       <c r="F32">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H32">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -10666,22 +10683,22 @@
         <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="O32" t="s">
-        <v>27</v>
+        <v>221</v>
       </c>
       <c r="P32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q32" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="R32" t="s">
-        <v>27</v>
+        <v>223</v>
       </c>
       <c r="S32" t="s">
-        <v>27</v>
+        <v>227</v>
       </c>
       <c r="T32" t="s">
         <v>27</v>
@@ -10696,31 +10713,31 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="Y32" t="s">
-        <v>27</v>
+        <v>269</v>
       </c>
       <c r="Z32">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB32">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AC32">
         <v>13</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG32">
         <v>0</v>
@@ -10732,19 +10749,19 @@
         <v>0</v>
       </c>
       <c r="AJ32">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="AK32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM32" t="s">
         <v>84</v>
       </c>
       <c r="AN32" t="s">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -10756,25 +10773,25 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C33" t="s">
-        <v>202</v>
+        <v>258</v>
       </c>
       <c r="D33" t="s">
-        <v>198</v>
+        <v>260</v>
       </c>
       <c r="E33" t="s">
-        <v>116</v>
+        <v>259</v>
       </c>
       <c r="F33">
         <v>60</v>
       </c>
       <c r="G33">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -10786,34 +10803,34 @@
         <v>1</v>
       </c>
       <c r="L33">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M33" t="s">
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="O33" t="s">
-        <v>215</v>
+        <v>27</v>
       </c>
       <c r="P33" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="Q33" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="R33" t="s">
-        <v>257</v>
+        <v>27</v>
       </c>
       <c r="S33" t="s">
         <v>27</v>
       </c>
       <c r="T33" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="U33" t="s">
-        <v>228</v>
+        <v>27</v>
       </c>
       <c r="V33" t="s">
         <v>27</v>
@@ -10822,55 +10839,55 @@
         <v>27</v>
       </c>
       <c r="X33" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="Y33" t="s">
-        <v>216</v>
+        <v>27</v>
       </c>
       <c r="Z33">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AA33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB33">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AC33">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AD33">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH33">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI33">
         <v>0</v>
       </c>
       <c r="AJ33">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="AK33">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AL33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AM33" t="s">
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -10882,25 +10899,25 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D34" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E34" t="s">
         <v>116</v>
       </c>
       <c r="F34">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G34">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="H34">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -10912,34 +10929,34 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M34" t="s">
         <v>26</v>
       </c>
       <c r="N34" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="O34" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="P34" t="s">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="Q34" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="R34" t="s">
-        <v>103</v>
+        <v>257</v>
       </c>
       <c r="S34" t="s">
         <v>27</v>
       </c>
       <c r="T34" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="U34" t="s">
-        <v>27</v>
+        <v>228</v>
       </c>
       <c r="V34" t="s">
         <v>27</v>
@@ -10948,55 +10965,55 @@
         <v>27</v>
       </c>
       <c r="X34" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="Y34" t="s">
-        <v>27</v>
+        <v>216</v>
       </c>
       <c r="Z34">
         <v>20</v>
       </c>
       <c r="AA34">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AB34">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC34">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AD34">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE34">
         <v>10</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI34">
         <v>0</v>
       </c>
       <c r="AJ34">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AK34">
         <v>10</v>
       </c>
       <c r="AL34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AM34" t="s">
         <v>84</v>
       </c>
       <c r="AN34" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -11008,25 +11025,25 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="C35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D35" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E35" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F35">
         <v>90</v>
       </c>
       <c r="G35">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="H35">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -11044,19 +11061,19 @@
         <v>26</v>
       </c>
       <c r="N35" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="O35" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="P35" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="Q35" t="s">
-        <v>218</v>
+        <v>70</v>
       </c>
       <c r="R35" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="S35" t="s">
         <v>27</v>
@@ -11074,28 +11091,28 @@
         <v>27</v>
       </c>
       <c r="X35" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="Y35" t="s">
-        <v>219</v>
+        <v>27</v>
       </c>
       <c r="Z35">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="AA35">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="AB35">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AC35">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AD35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF35">
         <v>0</v>
@@ -11110,19 +11127,19 @@
         <v>0</v>
       </c>
       <c r="AJ35">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK35">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AL35">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AM35" t="s">
         <v>84</v>
       </c>
       <c r="AN35" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AO35">
         <v>0</v>
@@ -11134,52 +11151,52 @@
         <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>268</v>
       </c>
       <c r="C36" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="E36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F36">
         <v>90</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M36" t="s">
         <v>26</v>
       </c>
       <c r="N36" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="O36" t="s">
-        <v>27</v>
+        <v>231</v>
       </c>
       <c r="P36" t="s">
-        <v>27</v>
+        <v>232</v>
       </c>
       <c r="Q36" t="s">
-        <v>27</v>
+        <v>218</v>
       </c>
       <c r="R36" t="s">
         <v>27</v>
@@ -11200,25 +11217,25 @@
         <v>27</v>
       </c>
       <c r="X36" t="s">
-        <v>27</v>
+        <v>233</v>
       </c>
       <c r="Y36" t="s">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="Z36">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AA36">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AB36">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AC36">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE36">
         <v>0</v>
@@ -11236,19 +11253,19 @@
         <v>0</v>
       </c>
       <c r="AJ36">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AK36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM36" t="s">
         <v>84</v>
       </c>
       <c r="AN36" t="s">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="AO36">
         <v>0</v>
@@ -11263,10 +11280,10 @@
         <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D37" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E37" t="s">
         <v>48</v>
@@ -11284,7 +11301,7 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -11377,6 +11394,132 @@
         <v>186</v>
       </c>
       <c r="AO37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:41" x14ac:dyDescent="0.4">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>136</v>
+      </c>
+      <c r="B38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" t="s">
+        <v>160</v>
+      </c>
+      <c r="D38" t="s">
+        <v>161</v>
+      </c>
+      <c r="E38" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38">
+        <v>90</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>9999</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>10</v>
+      </c>
+      <c r="M38" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" t="s">
+        <v>27</v>
+      </c>
+      <c r="P38" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>27</v>
+      </c>
+      <c r="R38" t="s">
+        <v>27</v>
+      </c>
+      <c r="S38" t="s">
+        <v>27</v>
+      </c>
+      <c r="T38" t="s">
+        <v>27</v>
+      </c>
+      <c r="U38" t="s">
+        <v>27</v>
+      </c>
+      <c r="V38" t="s">
+        <v>27</v>
+      </c>
+      <c r="W38" t="s">
+        <v>27</v>
+      </c>
+      <c r="X38" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z38">
+        <v>60</v>
+      </c>
+      <c r="AA38">
+        <v>25</v>
+      </c>
+      <c r="AB38">
+        <v>12</v>
+      </c>
+      <c r="AC38">
+        <v>3</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38">
+        <v>0</v>
+      </c>
+      <c r="AI38">
+        <v>0</v>
+      </c>
+      <c r="AJ38">
+        <v>95</v>
+      </c>
+      <c r="AK38">
+        <v>5</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>186</v>
+      </c>
+      <c r="AO38">
         <v>1</v>
       </c>
     </row>
@@ -11389,7 +11532,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAD14E5B-6BFE-4D20-B771-5A2DB6950621}">
-  <dimension ref="A1:AO37"/>
+  <dimension ref="A1:AO38"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -12543,7 +12686,7 @@
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A10">
-        <f t="shared" ref="A10:A37" si="1">ROW()-2+100</f>
+        <f t="shared" ref="A10:A38" si="1">ROW()-2+100</f>
         <v>108</v>
       </c>
       <c r="B10" t="s">
@@ -12571,7 +12714,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -12697,7 +12840,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -12823,7 +12966,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -12949,7 +13092,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -13075,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -13453,7 +13596,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -13579,7 +13722,7 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -13933,19 +14076,19 @@
         <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>253</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>239</v>
+        <v>293</v>
       </c>
       <c r="D21" t="s">
-        <v>238</v>
+        <v>294</v>
       </c>
       <c r="E21" t="s">
         <v>142</v>
       </c>
       <c r="F21">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -14059,19 +14202,19 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>253</v>
       </c>
       <c r="C22" t="s">
-        <v>167</v>
+        <v>239</v>
       </c>
       <c r="D22" t="s">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="E22" t="s">
         <v>142</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -14083,7 +14226,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -14185,19 +14328,19 @@
         <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>256</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>166</v>
       </c>
       <c r="E23" t="s">
         <v>142</v>
       </c>
       <c r="F23">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -14209,7 +14352,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -14257,16 +14400,16 @@
         <v>27</v>
       </c>
       <c r="Z23">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA23">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB23">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AC23">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AD23">
         <v>0</v>
@@ -14311,19 +14454,19 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>256</v>
       </c>
       <c r="C24" t="s">
-        <v>283</v>
+        <v>193</v>
       </c>
       <c r="D24" t="s">
-        <v>140</v>
+        <v>285</v>
       </c>
       <c r="E24" t="s">
         <v>142</v>
       </c>
       <c r="F24">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -14383,16 +14526,16 @@
         <v>27</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AA24">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AB24">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AC24">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AD24">
         <v>0</v>
@@ -14437,19 +14580,19 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>290</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>140</v>
       </c>
       <c r="E25" t="s">
         <v>142</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -14467,7 +14610,7 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M25" t="s">
         <v>26</v>
@@ -14509,16 +14652,16 @@
         <v>27</v>
       </c>
       <c r="Z25">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA25">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB25">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AC25">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AD25">
         <v>0</v>
@@ -14548,10 +14691,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AN25" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="AO25">
         <v>0</v>
@@ -14563,52 +14706,52 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>290</v>
       </c>
       <c r="C26" t="s">
-        <v>194</v>
+        <v>286</v>
       </c>
       <c r="D26" t="s">
-        <v>152</v>
+        <v>287</v>
       </c>
       <c r="E26" t="s">
         <v>142</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M26" t="s">
         <v>26</v>
       </c>
       <c r="N26" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="O26" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P26" t="s">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="Q26" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="R26" t="s">
         <v>27</v>
@@ -14629,25 +14772,25 @@
         <v>27</v>
       </c>
       <c r="X26" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="Y26" t="s">
         <v>27</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA26">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC26">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE26">
         <v>0</v>
@@ -14665,19 +14808,19 @@
         <v>0</v>
       </c>
       <c r="AJ26">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AK26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AN26" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -14689,19 +14832,19 @@
         <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>262</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E27" t="s">
         <v>142</v>
       </c>
       <c r="F27">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -14725,25 +14868,25 @@
         <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O27" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="P27" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="Q27" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="R27" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="S27" t="s">
-        <v>282</v>
+        <v>27</v>
       </c>
       <c r="T27" t="s">
-        <v>191</v>
+        <v>27</v>
       </c>
       <c r="U27" t="s">
         <v>27</v>
@@ -14755,55 +14898,55 @@
         <v>27</v>
       </c>
       <c r="X27" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="Y27" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="Z27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="AB27">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AC27">
+        <v>7</v>
+      </c>
+      <c r="AD27">
         <v>10</v>
       </c>
-      <c r="AD27">
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <v>98</v>
+      </c>
+      <c r="AK27">
         <v>2</v>
       </c>
-      <c r="AE27">
-        <v>10</v>
-      </c>
-      <c r="AF27">
-        <v>4</v>
-      </c>
-      <c r="AG27">
-        <v>26</v>
-      </c>
-      <c r="AH27">
-        <v>0</v>
-      </c>
-      <c r="AI27">
-        <v>0</v>
-      </c>
-      <c r="AJ27">
-        <v>78</v>
-      </c>
-      <c r="AK27">
-        <v>15</v>
-      </c>
       <c r="AL27">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AN27" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -14815,31 +14958,31 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C28" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D28" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="E28" t="s">
         <v>142</v>
       </c>
       <c r="F28">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -14851,25 +14994,25 @@
         <v>26</v>
       </c>
       <c r="N28" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="O28" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="P28" t="s">
-        <v>224</v>
+        <v>25</v>
       </c>
       <c r="Q28" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="R28" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="S28" t="s">
-        <v>27</v>
+        <v>282</v>
       </c>
       <c r="T28" t="s">
-        <v>27</v>
+        <v>191</v>
       </c>
       <c r="U28" t="s">
         <v>27</v>
@@ -14881,34 +15024,34 @@
         <v>27</v>
       </c>
       <c r="X28" t="s">
-        <v>208</v>
+        <v>33</v>
       </c>
       <c r="Y28" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="Z28">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AA28">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AB28">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC28">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD28">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AE28">
         <v>10</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AH28">
         <v>0</v>
@@ -14917,19 +15060,19 @@
         <v>0</v>
       </c>
       <c r="AJ28">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AK28">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AL28">
         <v>7</v>
       </c>
       <c r="AM28" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AN28" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -14941,13 +15084,13 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C29" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D29" t="s">
-        <v>270</v>
+        <v>195</v>
       </c>
       <c r="E29" t="s">
         <v>142</v>
@@ -14956,10 +15099,10 @@
         <v>30</v>
       </c>
       <c r="G29">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -14971,25 +15114,25 @@
         <v>1</v>
       </c>
       <c r="L29">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M29" t="s">
         <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P29" t="s">
-        <v>108</v>
+        <v>224</v>
       </c>
       <c r="Q29" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="R29" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="S29" t="s">
         <v>27</v>
@@ -15007,25 +15150,25 @@
         <v>27</v>
       </c>
       <c r="X29" t="s">
-        <v>111</v>
+        <v>208</v>
       </c>
       <c r="Y29" t="s">
-        <v>229</v>
+        <v>136</v>
       </c>
       <c r="Z29">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AA29">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB29">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AC29">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AD29">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AE29">
         <v>10</v>
@@ -15043,19 +15186,19 @@
         <v>0</v>
       </c>
       <c r="AJ29">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK29">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AL29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM29" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="AN29" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -15067,13 +15210,13 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="C30" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D30" t="s">
-        <v>197</v>
+        <v>270</v>
       </c>
       <c r="E30" t="s">
         <v>142</v>
@@ -15082,10 +15225,10 @@
         <v>30</v>
       </c>
       <c r="G30">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -15097,7 +15240,7 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M30" t="s">
         <v>26</v>
@@ -15106,25 +15249,25 @@
         <v>72</v>
       </c>
       <c r="O30" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="P30" t="s">
         <v>108</v>
       </c>
       <c r="Q30" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="R30" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="S30" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="T30" t="s">
-        <v>222</v>
+        <v>27</v>
       </c>
       <c r="U30" t="s">
-        <v>250</v>
+        <v>27</v>
       </c>
       <c r="V30" t="s">
         <v>27</v>
@@ -15133,55 +15276,55 @@
         <v>27</v>
       </c>
       <c r="X30" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="Y30" t="s">
-        <v>111</v>
+        <v>229</v>
       </c>
       <c r="Z30">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AA30">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="AB30">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AC30">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AD30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE30">
         <v>10</v>
       </c>
       <c r="AF30">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <v>94</v>
+      </c>
+      <c r="AK30">
+        <v>1</v>
+      </c>
+      <c r="AL30">
         <v>5</v>
-      </c>
-      <c r="AI30">
-        <v>0</v>
-      </c>
-      <c r="AJ30">
-        <v>83</v>
-      </c>
-      <c r="AK30">
-        <v>16</v>
-      </c>
-      <c r="AL30">
-        <v>1</v>
       </c>
       <c r="AM30" t="s">
         <v>84</v>
       </c>
       <c r="AN30" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -15193,13 +15336,13 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="D31" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E31" t="s">
         <v>142</v>
@@ -15208,10 +15351,10 @@
         <v>30</v>
       </c>
       <c r="G31">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -15229,28 +15372,28 @@
         <v>26</v>
       </c>
       <c r="N31" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
       <c r="O31" t="s">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="P31" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="Q31" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="R31" t="s">
-        <v>223</v>
+        <v>112</v>
       </c>
       <c r="S31" t="s">
-        <v>227</v>
+        <v>74</v>
       </c>
       <c r="T31" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="U31" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -15259,55 +15402,55 @@
         <v>27</v>
       </c>
       <c r="X31" t="s">
-        <v>216</v>
+        <v>127</v>
       </c>
       <c r="Y31" t="s">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="Z31">
         <v>20</v>
       </c>
       <c r="AA31">
+        <v>5</v>
+      </c>
+      <c r="AB31">
         <v>20</v>
       </c>
-      <c r="AB31">
-        <v>17</v>
-      </c>
       <c r="AC31">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE31">
         <v>10</v>
       </c>
       <c r="AF31">
+        <v>13</v>
+      </c>
+      <c r="AG31">
         <v>10</v>
       </c>
-      <c r="AG31">
-        <v>0</v>
-      </c>
       <c r="AH31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI31">
         <v>0</v>
       </c>
       <c r="AJ31">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AK31">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AL31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM31" t="s">
         <v>84</v>
       </c>
       <c r="AN31" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -15319,25 +15462,25 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C32" t="s">
-        <v>258</v>
+        <v>42</v>
       </c>
       <c r="D32" t="s">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="E32" t="s">
         <v>142</v>
       </c>
       <c r="F32">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H32">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -15355,22 +15498,22 @@
         <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="O32" t="s">
-        <v>27</v>
+        <v>221</v>
       </c>
       <c r="P32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q32" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="R32" t="s">
-        <v>27</v>
+        <v>223</v>
       </c>
       <c r="S32" t="s">
-        <v>27</v>
+        <v>227</v>
       </c>
       <c r="T32" t="s">
         <v>27</v>
@@ -15385,31 +15528,31 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="Y32" t="s">
-        <v>27</v>
+        <v>269</v>
       </c>
       <c r="Z32">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB32">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AC32">
         <v>13</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG32">
         <v>0</v>
@@ -15421,19 +15564,19 @@
         <v>0</v>
       </c>
       <c r="AJ32">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="AK32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM32" t="s">
         <v>84</v>
       </c>
       <c r="AN32" t="s">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -15445,13 +15588,13 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C33" t="s">
-        <v>202</v>
+        <v>258</v>
       </c>
       <c r="D33" t="s">
-        <v>198</v>
+        <v>260</v>
       </c>
       <c r="E33" t="s">
         <v>142</v>
@@ -15460,10 +15603,10 @@
         <v>60</v>
       </c>
       <c r="G33">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -15475,34 +15618,34 @@
         <v>1</v>
       </c>
       <c r="L33">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M33" t="s">
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="O33" t="s">
-        <v>215</v>
+        <v>27</v>
       </c>
       <c r="P33" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="Q33" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="R33" t="s">
-        <v>257</v>
+        <v>27</v>
       </c>
       <c r="S33" t="s">
         <v>27</v>
       </c>
       <c r="T33" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="U33" t="s">
-        <v>228</v>
+        <v>27</v>
       </c>
       <c r="V33" t="s">
         <v>27</v>
@@ -15511,55 +15654,55 @@
         <v>27</v>
       </c>
       <c r="X33" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="Y33" t="s">
-        <v>216</v>
+        <v>27</v>
       </c>
       <c r="Z33">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AA33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB33">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AC33">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AD33">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH33">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI33">
         <v>0</v>
       </c>
       <c r="AJ33">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="AK33">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AL33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AM33" t="s">
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -15571,25 +15714,25 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D34" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E34" t="s">
         <v>142</v>
       </c>
       <c r="F34">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G34">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="H34">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -15601,34 +15744,34 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M34" t="s">
         <v>26</v>
       </c>
       <c r="N34" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="O34" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="P34" t="s">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="Q34" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="R34" t="s">
-        <v>103</v>
+        <v>257</v>
       </c>
       <c r="S34" t="s">
         <v>27</v>
       </c>
       <c r="T34" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="U34" t="s">
-        <v>27</v>
+        <v>228</v>
       </c>
       <c r="V34" t="s">
         <v>27</v>
@@ -15637,55 +15780,55 @@
         <v>27</v>
       </c>
       <c r="X34" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="Y34" t="s">
-        <v>27</v>
+        <v>216</v>
       </c>
       <c r="Z34">
         <v>20</v>
       </c>
       <c r="AA34">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AB34">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC34">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AD34">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE34">
         <v>10</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI34">
         <v>0</v>
       </c>
       <c r="AJ34">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AK34">
         <v>10</v>
       </c>
       <c r="AL34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AM34" t="s">
         <v>84</v>
       </c>
       <c r="AN34" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -15697,13 +15840,13 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="C35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D35" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E35" t="s">
         <v>142</v>
@@ -15712,10 +15855,10 @@
         <v>90</v>
       </c>
       <c r="G35">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="H35">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -15733,19 +15876,19 @@
         <v>26</v>
       </c>
       <c r="N35" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="O35" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="P35" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="Q35" t="s">
-        <v>218</v>
+        <v>70</v>
       </c>
       <c r="R35" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="S35" t="s">
         <v>27</v>
@@ -15763,28 +15906,28 @@
         <v>27</v>
       </c>
       <c r="X35" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="Y35" t="s">
-        <v>219</v>
+        <v>27</v>
       </c>
       <c r="Z35">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="AA35">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="AB35">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AC35">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AD35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF35">
         <v>0</v>
@@ -15799,19 +15942,19 @@
         <v>0</v>
       </c>
       <c r="AJ35">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK35">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AL35">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AM35" t="s">
         <v>84</v>
       </c>
       <c r="AN35" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AO35">
         <v>0</v>
@@ -15823,13 +15966,13 @@
         <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>268</v>
       </c>
       <c r="C36" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="E36" t="s">
         <v>142</v>
@@ -15838,37 +15981,37 @@
         <v>90</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M36" t="s">
         <v>26</v>
       </c>
       <c r="N36" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="O36" t="s">
-        <v>27</v>
+        <v>231</v>
       </c>
       <c r="P36" t="s">
-        <v>27</v>
+        <v>232</v>
       </c>
       <c r="Q36" t="s">
-        <v>27</v>
+        <v>218</v>
       </c>
       <c r="R36" t="s">
         <v>27</v>
@@ -15889,25 +16032,25 @@
         <v>27</v>
       </c>
       <c r="X36" t="s">
-        <v>27</v>
+        <v>233</v>
       </c>
       <c r="Y36" t="s">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="Z36">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AA36">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AB36">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AC36">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE36">
         <v>0</v>
@@ -15925,19 +16068,19 @@
         <v>0</v>
       </c>
       <c r="AJ36">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AK36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM36" t="s">
         <v>84</v>
       </c>
       <c r="AN36" t="s">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="AO36">
         <v>0</v>
@@ -15952,10 +16095,10 @@
         <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D37" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E37" t="s">
         <v>142</v>
@@ -15973,7 +16116,7 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -16066,6 +16209,132 @@
         <v>186</v>
       </c>
       <c r="AO37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:41" x14ac:dyDescent="0.4">
+      <c r="A38">
+        <f t="shared" si="1"/>
+        <v>136</v>
+      </c>
+      <c r="B38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" t="s">
+        <v>160</v>
+      </c>
+      <c r="D38" t="s">
+        <v>161</v>
+      </c>
+      <c r="E38" t="s">
+        <v>142</v>
+      </c>
+      <c r="F38">
+        <v>90</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>9999</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>10</v>
+      </c>
+      <c r="M38" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" t="s">
+        <v>27</v>
+      </c>
+      <c r="P38" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>27</v>
+      </c>
+      <c r="R38" t="s">
+        <v>27</v>
+      </c>
+      <c r="S38" t="s">
+        <v>27</v>
+      </c>
+      <c r="T38" t="s">
+        <v>27</v>
+      </c>
+      <c r="U38" t="s">
+        <v>27</v>
+      </c>
+      <c r="V38" t="s">
+        <v>27</v>
+      </c>
+      <c r="W38" t="s">
+        <v>27</v>
+      </c>
+      <c r="X38" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z38">
+        <v>60</v>
+      </c>
+      <c r="AA38">
+        <v>25</v>
+      </c>
+      <c r="AB38">
+        <v>12</v>
+      </c>
+      <c r="AC38">
+        <v>3</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38">
+        <v>0</v>
+      </c>
+      <c r="AI38">
+        <v>0</v>
+      </c>
+      <c r="AJ38">
+        <v>95</v>
+      </c>
+      <c r="AK38">
+        <v>5</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>186</v>
+      </c>
+      <c r="AO38">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A3FD98-51BA-48A0-B514-62AA191D6188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7837FD11-A2C9-415D-9A61-04369C6D5174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
@@ -10092,10 +10092,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AC27">
         <v>7</v>
@@ -10320,7 +10320,7 @@
         <v>128</v>
       </c>
       <c r="S29" t="s">
-        <v>27</v>
+        <v>127</v>
       </c>
       <c r="T29" t="s">
         <v>27</v>
@@ -10341,7 +10341,7 @@
         <v>136</v>
       </c>
       <c r="Z29">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AA29">
         <v>30</v>
@@ -10359,7 +10359,7 @@
         <v>10</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG29">
         <v>0</v>
@@ -10587,7 +10587,7 @@
         <v>27</v>
       </c>
       <c r="X31" t="s">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="Y31" t="s">
         <v>111</v>
@@ -14907,10 +14907,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AC27">
         <v>7</v>
@@ -15135,7 +15135,7 @@
         <v>128</v>
       </c>
       <c r="S29" t="s">
-        <v>27</v>
+        <v>127</v>
       </c>
       <c r="T29" t="s">
         <v>27</v>
@@ -15156,7 +15156,7 @@
         <v>136</v>
       </c>
       <c r="Z29">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AA29">
         <v>30</v>
@@ -15174,7 +15174,7 @@
         <v>10</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG29">
         <v>0</v>
@@ -15402,7 +15402,7 @@
         <v>27</v>
       </c>
       <c r="X31" t="s">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="Y31" t="s">
         <v>111</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7837FD11-A2C9-415D-9A61-04369C6D5174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7CD361-1965-4967-95A8-5030E94A96C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2460" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="294">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -1331,10 +1331,6 @@
   </si>
   <si>
     <t>apricot</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>melon</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -6993,13 +6989,13 @@
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C3" t="s">
         <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E3" t="s">
         <v>58</v>
@@ -7119,13 +7115,13 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C4" t="s">
         <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E4" t="s">
         <v>58</v>
@@ -7245,13 +7241,13 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C5" t="s">
         <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E5" t="s">
         <v>58</v>
@@ -7623,13 +7619,13 @@
         <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C8" t="s">
         <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E8" t="s">
         <v>58</v>
@@ -8001,7 +7997,7 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C11" t="s">
         <v>175</v>
@@ -8127,7 +8123,7 @@
         <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C12" t="s">
         <v>176</v>
@@ -8253,7 +8249,7 @@
         <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C13" t="s">
         <v>177</v>
@@ -8379,13 +8375,13 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E14" t="s">
         <v>48</v>
@@ -8505,13 +8501,13 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E15" t="s">
         <v>48</v>
@@ -8631,13 +8627,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" t="s">
+        <v>290</v>
+      </c>
+      <c r="D16" t="s">
         <v>291</v>
-      </c>
-      <c r="D16" t="s">
-        <v>292</v>
       </c>
       <c r="E16" t="s">
         <v>48</v>
@@ -8757,13 +8753,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E17" t="s">
         <v>48</v>
@@ -8883,13 +8879,13 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C18" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E18" t="s">
         <v>48</v>
@@ -9009,13 +9005,13 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E19" t="s">
         <v>48</v>
@@ -9264,10 +9260,10 @@
         <v>122</v>
       </c>
       <c r="C21" t="s">
+        <v>292</v>
+      </c>
+      <c r="D21" t="s">
         <v>293</v>
-      </c>
-      <c r="D21" t="s">
-        <v>294</v>
       </c>
       <c r="E21" t="s">
         <v>151</v>
@@ -9387,13 +9383,13 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E22" t="s">
         <v>151</v>
@@ -9639,13 +9635,13 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C24" t="s">
         <v>193</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
@@ -9768,7 +9764,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D25" t="s">
         <v>140</v>
@@ -9891,13 +9887,13 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C26" t="s">
+        <v>285</v>
+      </c>
+      <c r="D26" t="s">
         <v>286</v>
-      </c>
-      <c r="D26" t="s">
-        <v>287</v>
       </c>
       <c r="E26" t="s">
         <v>48</v>
@@ -10143,7 +10139,7 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C28" t="s">
         <v>181</v>
@@ -10194,7 +10190,7 @@
         <v>103</v>
       </c>
       <c r="S28" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="T28" t="s">
         <v>191</v>
@@ -10269,7 +10265,7 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C29" t="s">
         <v>196</v>
@@ -10311,7 +10307,7 @@
         <v>73</v>
       </c>
       <c r="P29" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q29" t="s">
         <v>113</v>
@@ -10395,13 +10391,13 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C30" t="s">
         <v>205</v>
       </c>
       <c r="D30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E30" t="s">
         <v>50</v>
@@ -10464,7 +10460,7 @@
         <v>111</v>
       </c>
       <c r="Y30" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Z30">
         <v>25</v>
@@ -10509,7 +10505,7 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -10521,7 +10517,7 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C31" t="s">
         <v>209</v>
@@ -10575,10 +10571,10 @@
         <v>74</v>
       </c>
       <c r="T31" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U31" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -10635,7 +10631,7 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -10647,7 +10643,7 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C32" t="s">
         <v>42</v>
@@ -10686,7 +10682,7 @@
         <v>212</v>
       </c>
       <c r="O32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P32" t="s">
         <v>25</v>
@@ -10695,10 +10691,10 @@
         <v>137</v>
       </c>
       <c r="R32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="S32" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="T32" t="s">
         <v>27</v>
@@ -10713,10 +10709,10 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Y32" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Z32">
         <v>20</v>
@@ -10761,7 +10757,7 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -10773,16 +10769,16 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C33" t="s">
+        <v>257</v>
+      </c>
+      <c r="D33" t="s">
+        <v>259</v>
+      </c>
+      <c r="E33" t="s">
         <v>258</v>
-      </c>
-      <c r="D33" t="s">
-        <v>260</v>
-      </c>
-      <c r="E33" t="s">
-        <v>259</v>
       </c>
       <c r="F33">
         <v>60</v>
@@ -10809,7 +10805,7 @@
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O33" t="s">
         <v>27</v>
@@ -10839,7 +10835,7 @@
         <v>27</v>
       </c>
       <c r="X33" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Y33" t="s">
         <v>27</v>
@@ -10887,7 +10883,7 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -10899,7 +10895,7 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C34" t="s">
         <v>202</v>
@@ -10947,7 +10943,7 @@
         <v>110</v>
       </c>
       <c r="R34" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="S34" t="s">
         <v>27</v>
@@ -10956,7 +10952,7 @@
         <v>129</v>
       </c>
       <c r="U34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="V34" t="s">
         <v>27</v>
@@ -10965,10 +10961,10 @@
         <v>27</v>
       </c>
       <c r="X34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y34" t="s">
-        <v>216</v>
+        <v>80</v>
       </c>
       <c r="Z34">
         <v>20</v>
@@ -11013,7 +11009,7 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -11025,7 +11021,7 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C35" t="s">
         <v>203</v>
@@ -11061,13 +11057,13 @@
         <v>26</v>
       </c>
       <c r="N35" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O35" t="s">
         <v>211</v>
       </c>
       <c r="P35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q35" t="s">
         <v>70</v>
@@ -11139,7 +11135,7 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AO35">
         <v>0</v>
@@ -11151,7 +11147,7 @@
         <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C36" t="s">
         <v>204</v>
@@ -11190,37 +11186,37 @@
         <v>213</v>
       </c>
       <c r="O36" t="s">
+        <v>230</v>
+      </c>
+      <c r="P36" t="s">
         <v>231</v>
       </c>
-      <c r="P36" t="s">
+      <c r="Q36" t="s">
+        <v>217</v>
+      </c>
+      <c r="R36" t="s">
+        <v>27</v>
+      </c>
+      <c r="S36" t="s">
+        <v>27</v>
+      </c>
+      <c r="T36" t="s">
+        <v>27</v>
+      </c>
+      <c r="U36" t="s">
+        <v>27</v>
+      </c>
+      <c r="V36" t="s">
+        <v>27</v>
+      </c>
+      <c r="W36" t="s">
+        <v>27</v>
+      </c>
+      <c r="X36" t="s">
         <v>232</v>
       </c>
-      <c r="Q36" t="s">
+      <c r="Y36" t="s">
         <v>218</v>
-      </c>
-      <c r="R36" t="s">
-        <v>27</v>
-      </c>
-      <c r="S36" t="s">
-        <v>27</v>
-      </c>
-      <c r="T36" t="s">
-        <v>27</v>
-      </c>
-      <c r="U36" t="s">
-        <v>27</v>
-      </c>
-      <c r="V36" t="s">
-        <v>27</v>
-      </c>
-      <c r="W36" t="s">
-        <v>27</v>
-      </c>
-      <c r="X36" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>219</v>
       </c>
       <c r="Z36">
         <v>68</v>
@@ -11265,7 +11261,7 @@
         <v>84</v>
       </c>
       <c r="AN36" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AO36">
         <v>0</v>
@@ -11808,13 +11804,13 @@
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C3" t="s">
         <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E3" t="s">
         <v>142</v>
@@ -11934,13 +11930,13 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C4" t="s">
         <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E4" t="s">
         <v>142</v>
@@ -12060,13 +12056,13 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C5" t="s">
         <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E5" t="s">
         <v>142</v>
@@ -12438,13 +12434,13 @@
         <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C8" t="s">
         <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E8" t="s">
         <v>142</v>
@@ -12816,7 +12812,7 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C11" t="s">
         <v>175</v>
@@ -12942,7 +12938,7 @@
         <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C12" t="s">
         <v>176</v>
@@ -13068,7 +13064,7 @@
         <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C13" t="s">
         <v>177</v>
@@ -13194,13 +13190,13 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E14" t="s">
         <v>142</v>
@@ -13320,13 +13316,13 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E15" t="s">
         <v>142</v>
@@ -13446,13 +13442,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" t="s">
+        <v>290</v>
+      </c>
+      <c r="D16" t="s">
         <v>291</v>
-      </c>
-      <c r="D16" t="s">
-        <v>292</v>
       </c>
       <c r="E16" t="s">
         <v>142</v>
@@ -13572,13 +13568,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E17" t="s">
         <v>142</v>
@@ -13698,13 +13694,13 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C18" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E18" t="s">
         <v>142</v>
@@ -13824,13 +13820,13 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E19" t="s">
         <v>142</v>
@@ -14079,10 +14075,10 @@
         <v>122</v>
       </c>
       <c r="C21" t="s">
+        <v>292</v>
+      </c>
+      <c r="D21" t="s">
         <v>293</v>
-      </c>
-      <c r="D21" t="s">
-        <v>294</v>
       </c>
       <c r="E21" t="s">
         <v>142</v>
@@ -14202,13 +14198,13 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E22" t="s">
         <v>142</v>
@@ -14454,13 +14450,13 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C24" t="s">
         <v>193</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E24" t="s">
         <v>142</v>
@@ -14583,7 +14579,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D25" t="s">
         <v>140</v>
@@ -14706,13 +14702,13 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C26" t="s">
+        <v>285</v>
+      </c>
+      <c r="D26" t="s">
         <v>286</v>
-      </c>
-      <c r="D26" t="s">
-        <v>287</v>
       </c>
       <c r="E26" t="s">
         <v>142</v>
@@ -14958,7 +14954,7 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C28" t="s">
         <v>181</v>
@@ -15009,7 +15005,7 @@
         <v>103</v>
       </c>
       <c r="S28" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="T28" t="s">
         <v>191</v>
@@ -15084,7 +15080,7 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C29" t="s">
         <v>196</v>
@@ -15126,7 +15122,7 @@
         <v>73</v>
       </c>
       <c r="P29" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q29" t="s">
         <v>113</v>
@@ -15210,13 +15206,13 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C30" t="s">
         <v>205</v>
       </c>
       <c r="D30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E30" t="s">
         <v>142</v>
@@ -15279,7 +15275,7 @@
         <v>111</v>
       </c>
       <c r="Y30" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Z30">
         <v>25</v>
@@ -15324,7 +15320,7 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -15336,7 +15332,7 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C31" t="s">
         <v>209</v>
@@ -15390,10 +15386,10 @@
         <v>74</v>
       </c>
       <c r="T31" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U31" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -15450,7 +15446,7 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -15462,7 +15458,7 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C32" t="s">
         <v>42</v>
@@ -15501,7 +15497,7 @@
         <v>212</v>
       </c>
       <c r="O32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P32" t="s">
         <v>25</v>
@@ -15510,10 +15506,10 @@
         <v>137</v>
       </c>
       <c r="R32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="S32" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="T32" t="s">
         <v>27</v>
@@ -15528,10 +15524,10 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Y32" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Z32">
         <v>20</v>
@@ -15576,7 +15572,7 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -15588,13 +15584,13 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D33" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E33" t="s">
         <v>142</v>
@@ -15624,7 +15620,7 @@
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O33" t="s">
         <v>27</v>
@@ -15654,7 +15650,7 @@
         <v>27</v>
       </c>
       <c r="X33" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Y33" t="s">
         <v>27</v>
@@ -15702,7 +15698,7 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -15714,7 +15710,7 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C34" t="s">
         <v>202</v>
@@ -15762,7 +15758,7 @@
         <v>110</v>
       </c>
       <c r="R34" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="S34" t="s">
         <v>27</v>
@@ -15771,7 +15767,7 @@
         <v>129</v>
       </c>
       <c r="U34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="V34" t="s">
         <v>27</v>
@@ -15780,10 +15776,10 @@
         <v>27</v>
       </c>
       <c r="X34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y34" t="s">
-        <v>216</v>
+        <v>80</v>
       </c>
       <c r="Z34">
         <v>20</v>
@@ -15828,7 +15824,7 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -15840,7 +15836,7 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C35" t="s">
         <v>203</v>
@@ -15876,13 +15872,13 @@
         <v>26</v>
       </c>
       <c r="N35" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O35" t="s">
         <v>211</v>
       </c>
       <c r="P35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q35" t="s">
         <v>70</v>
@@ -15954,7 +15950,7 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AO35">
         <v>0</v>
@@ -15966,7 +15962,7 @@
         <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C36" t="s">
         <v>204</v>
@@ -16005,37 +16001,37 @@
         <v>213</v>
       </c>
       <c r="O36" t="s">
+        <v>230</v>
+      </c>
+      <c r="P36" t="s">
         <v>231</v>
       </c>
-      <c r="P36" t="s">
+      <c r="Q36" t="s">
+        <v>217</v>
+      </c>
+      <c r="R36" t="s">
+        <v>27</v>
+      </c>
+      <c r="S36" t="s">
+        <v>27</v>
+      </c>
+      <c r="T36" t="s">
+        <v>27</v>
+      </c>
+      <c r="U36" t="s">
+        <v>27</v>
+      </c>
+      <c r="V36" t="s">
+        <v>27</v>
+      </c>
+      <c r="W36" t="s">
+        <v>27</v>
+      </c>
+      <c r="X36" t="s">
         <v>232</v>
       </c>
-      <c r="Q36" t="s">
+      <c r="Y36" t="s">
         <v>218</v>
-      </c>
-      <c r="R36" t="s">
-        <v>27</v>
-      </c>
-      <c r="S36" t="s">
-        <v>27</v>
-      </c>
-      <c r="T36" t="s">
-        <v>27</v>
-      </c>
-      <c r="U36" t="s">
-        <v>27</v>
-      </c>
-      <c r="V36" t="s">
-        <v>27</v>
-      </c>
-      <c r="W36" t="s">
-        <v>27</v>
-      </c>
-      <c r="X36" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>219</v>
       </c>
       <c r="Z36">
         <v>68</v>
@@ -16080,7 +16076,7 @@
         <v>84</v>
       </c>
       <c r="AN36" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AO36">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7CD361-1965-4967-95A8-5030E94A96C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99DF578C-6879-43B3-9FA8-D79167B1E498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2640" yWindow="1350" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99DF578C-6879-43B3-9FA8-D79167B1E498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEBF008-DD45-4B66-94DC-F5835F7E1878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="1350" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2085" yWindow="690" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -1432,16 +1432,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>春エリア入口</t>
-    <rPh sb="0" eb="1">
-      <t>ハル</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>イリグチ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Or_HirobaEnter_A1</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1738,6 +1728,13 @@
     </rPh>
     <rPh sb="4" eb="5">
       <t>ドオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お花畑</t>
+    <rPh sb="1" eb="3">
+      <t>ハナバタケ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -6989,13 +6986,13 @@
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C3" t="s">
         <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E3" t="s">
         <v>58</v>
@@ -7115,13 +7112,13 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C4" t="s">
         <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E4" t="s">
         <v>58</v>
@@ -7241,13 +7238,13 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C5" t="s">
         <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E5" t="s">
         <v>58</v>
@@ -7619,13 +7616,13 @@
         <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C8" t="s">
         <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E8" t="s">
         <v>58</v>
@@ -7997,7 +7994,7 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C11" t="s">
         <v>175</v>
@@ -8123,7 +8120,7 @@
         <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C12" t="s">
         <v>176</v>
@@ -8249,7 +8246,7 @@
         <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C13" t="s">
         <v>177</v>
@@ -8375,13 +8372,13 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D14" t="s">
-        <v>239</v>
+        <v>293</v>
       </c>
       <c r="E14" t="s">
         <v>48</v>
@@ -8399,7 +8396,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -8501,13 +8498,13 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E15" t="s">
         <v>48</v>
@@ -8627,13 +8624,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C16" t="s">
+        <v>289</v>
+      </c>
+      <c r="D16" t="s">
         <v>290</v>
-      </c>
-      <c r="D16" t="s">
-        <v>291</v>
       </c>
       <c r="E16" t="s">
         <v>48</v>
@@ -8753,13 +8750,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E17" t="s">
         <v>48</v>
@@ -8879,13 +8876,13 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C18" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E18" t="s">
         <v>48</v>
@@ -9005,13 +9002,13 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E19" t="s">
         <v>48</v>
@@ -9260,10 +9257,10 @@
         <v>122</v>
       </c>
       <c r="C21" t="s">
+        <v>291</v>
+      </c>
+      <c r="D21" t="s">
         <v>292</v>
-      </c>
-      <c r="D21" t="s">
-        <v>293</v>
       </c>
       <c r="E21" t="s">
         <v>151</v>
@@ -9383,7 +9380,7 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C22" t="s">
         <v>238</v>
@@ -9635,13 +9632,13 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C24" t="s">
         <v>193</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
@@ -9764,7 +9761,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D25" t="s">
         <v>140</v>
@@ -9887,13 +9884,13 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C26" t="s">
+        <v>284</v>
+      </c>
+      <c r="D26" t="s">
         <v>285</v>
-      </c>
-      <c r="D26" t="s">
-        <v>286</v>
       </c>
       <c r="E26" t="s">
         <v>48</v>
@@ -10139,7 +10136,7 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C28" t="s">
         <v>181</v>
@@ -10190,7 +10187,7 @@
         <v>103</v>
       </c>
       <c r="S28" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="T28" t="s">
         <v>191</v>
@@ -10265,7 +10262,7 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C29" t="s">
         <v>196</v>
@@ -10391,13 +10388,13 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C30" t="s">
         <v>205</v>
       </c>
       <c r="D30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E30" t="s">
         <v>50</v>
@@ -10517,7 +10514,7 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C31" t="s">
         <v>209</v>
@@ -10574,7 +10571,7 @@
         <v>221</v>
       </c>
       <c r="U31" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -10643,7 +10640,7 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C32" t="s">
         <v>42</v>
@@ -10712,7 +10709,7 @@
         <v>218</v>
       </c>
       <c r="Y32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Z32">
         <v>20</v>
@@ -10769,16 +10766,16 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C33" t="s">
+        <v>256</v>
+      </c>
+      <c r="D33" t="s">
+        <v>258</v>
+      </c>
+      <c r="E33" t="s">
         <v>257</v>
-      </c>
-      <c r="D33" t="s">
-        <v>259</v>
-      </c>
-      <c r="E33" t="s">
-        <v>258</v>
       </c>
       <c r="F33">
         <v>60</v>
@@ -10883,7 +10880,7 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -10895,7 +10892,7 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C34" t="s">
         <v>202</v>
@@ -10943,7 +10940,7 @@
         <v>110</v>
       </c>
       <c r="R34" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S34" t="s">
         <v>27</v>
@@ -11021,7 +11018,7 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C35" t="s">
         <v>203</v>
@@ -11147,7 +11144,7 @@
         <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C36" t="s">
         <v>204</v>
@@ -11804,13 +11801,13 @@
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C3" t="s">
         <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E3" t="s">
         <v>142</v>
@@ -11930,13 +11927,13 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C4" t="s">
         <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E4" t="s">
         <v>142</v>
@@ -12056,13 +12053,13 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C5" t="s">
         <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E5" t="s">
         <v>142</v>
@@ -12434,13 +12431,13 @@
         <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C8" t="s">
         <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E8" t="s">
         <v>142</v>
@@ -12812,7 +12809,7 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C11" t="s">
         <v>175</v>
@@ -12938,7 +12935,7 @@
         <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C12" t="s">
         <v>176</v>
@@ -13064,7 +13061,7 @@
         <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C13" t="s">
         <v>177</v>
@@ -13190,13 +13187,13 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D14" t="s">
-        <v>239</v>
+        <v>293</v>
       </c>
       <c r="E14" t="s">
         <v>142</v>
@@ -13214,7 +13211,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -13316,13 +13313,13 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E15" t="s">
         <v>142</v>
@@ -13442,13 +13439,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C16" t="s">
+        <v>289</v>
+      </c>
+      <c r="D16" t="s">
         <v>290</v>
-      </c>
-      <c r="D16" t="s">
-        <v>291</v>
       </c>
       <c r="E16" t="s">
         <v>142</v>
@@ -13568,13 +13565,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E17" t="s">
         <v>142</v>
@@ -13694,13 +13691,13 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C18" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E18" t="s">
         <v>142</v>
@@ -13820,13 +13817,13 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E19" t="s">
         <v>142</v>
@@ -14075,10 +14072,10 @@
         <v>122</v>
       </c>
       <c r="C21" t="s">
+        <v>291</v>
+      </c>
+      <c r="D21" t="s">
         <v>292</v>
-      </c>
-      <c r="D21" t="s">
-        <v>293</v>
       </c>
       <c r="E21" t="s">
         <v>142</v>
@@ -14198,7 +14195,7 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C22" t="s">
         <v>238</v>
@@ -14450,13 +14447,13 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C24" t="s">
         <v>193</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E24" t="s">
         <v>142</v>
@@ -14579,7 +14576,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D25" t="s">
         <v>140</v>
@@ -14702,13 +14699,13 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C26" t="s">
+        <v>284</v>
+      </c>
+      <c r="D26" t="s">
         <v>285</v>
-      </c>
-      <c r="D26" t="s">
-        <v>286</v>
       </c>
       <c r="E26" t="s">
         <v>142</v>
@@ -14954,7 +14951,7 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C28" t="s">
         <v>181</v>
@@ -15005,7 +15002,7 @@
         <v>103</v>
       </c>
       <c r="S28" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="T28" t="s">
         <v>191</v>
@@ -15080,7 +15077,7 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C29" t="s">
         <v>196</v>
@@ -15206,13 +15203,13 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C30" t="s">
         <v>205</v>
       </c>
       <c r="D30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E30" t="s">
         <v>142</v>
@@ -15332,7 +15329,7 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C31" t="s">
         <v>209</v>
@@ -15389,7 +15386,7 @@
         <v>221</v>
       </c>
       <c r="U31" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -15458,7 +15455,7 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C32" t="s">
         <v>42</v>
@@ -15527,7 +15524,7 @@
         <v>218</v>
       </c>
       <c r="Y32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Z32">
         <v>20</v>
@@ -15584,13 +15581,13 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E33" t="s">
         <v>142</v>
@@ -15698,7 +15695,7 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -15710,7 +15707,7 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C34" t="s">
         <v>202</v>
@@ -15758,7 +15755,7 @@
         <v>110</v>
       </c>
       <c r="R34" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S34" t="s">
         <v>27</v>
@@ -15836,7 +15833,7 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C35" t="s">
         <v>203</v>
@@ -15962,7 +15959,7 @@
         <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C36" t="s">
         <v>204</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEBF008-DD45-4B66-94DC-F5835F7E1878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF9D765-C63A-4690-85C6-84272A8035FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2085" yWindow="690" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2430" yWindow="1035" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF9D765-C63A-4690-85C6-84272A8035FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA13C44-0480-490D-8617-C8E38650C996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2430" yWindow="1035" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -10658,7 +10658,7 @@
         <v>300</v>
       </c>
       <c r="H32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -15473,7 +15473,7 @@
         <v>300</v>
       </c>
       <c r="H32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I32">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA13C44-0480-490D-8617-C8E38650C996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C09D09-B8A8-412C-A2C2-FB950B032115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2685" yWindow="1095" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -8774,7 +8774,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -13589,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K17">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C09D09-B8A8-412C-A2C2-FB950B032115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C74759A-11A2-47E9-B4C3-488E7A159F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="1095" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1185" yWindow="735" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -10718,13 +10718,13 @@
         <v>20</v>
       </c>
       <c r="AB32">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AC32">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AD32">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE32">
         <v>10</v>
@@ -15533,13 +15533,13 @@
         <v>20</v>
       </c>
       <c r="AB32">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AC32">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AD32">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE32">
         <v>10</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C74759A-11A2-47E9-B4C3-488E7A159F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFEB629-BED1-44C3-B5A1-F636D4217A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="735" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1530" yWindow="900" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFEB629-BED1-44C3-B5A1-F636D4217A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF3D73A-145C-40BF-8D58-ECF6D17270B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="900" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1950" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -7892,7 +7892,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -8018,7 +8018,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -8144,7 +8144,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -8270,7 +8270,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -12707,7 +12707,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -12833,7 +12833,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -12959,7 +12959,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -13085,7 +13085,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K13">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF3D73A-145C-40BF-8D58-ECF6D17270B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDF4FB8-382B-49A6-B379-D27E009B8311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2355" yWindow="1155" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="293">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -1395,10 +1395,6 @@
   </si>
   <si>
     <t>grape_kihu</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>diamond_2</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -6986,13 +6982,13 @@
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C3" t="s">
         <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E3" t="s">
         <v>58</v>
@@ -7112,13 +7108,13 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C4" t="s">
         <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E4" t="s">
         <v>58</v>
@@ -7238,13 +7234,13 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C5" t="s">
         <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E5" t="s">
         <v>58</v>
@@ -7616,13 +7612,13 @@
         <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C8" t="s">
         <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E8" t="s">
         <v>58</v>
@@ -7994,7 +7990,7 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C11" t="s">
         <v>175</v>
@@ -8120,7 +8116,7 @@
         <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C12" t="s">
         <v>176</v>
@@ -8246,7 +8242,7 @@
         <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C13" t="s">
         <v>177</v>
@@ -8372,13 +8368,13 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E14" t="s">
         <v>48</v>
@@ -8498,13 +8494,13 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E15" t="s">
         <v>48</v>
@@ -8624,13 +8620,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D16" t="s">
         <v>289</v>
-      </c>
-      <c r="D16" t="s">
-        <v>290</v>
       </c>
       <c r="E16" t="s">
         <v>48</v>
@@ -8750,13 +8746,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E17" t="s">
         <v>48</v>
@@ -8876,13 +8872,13 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C18" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E18" t="s">
         <v>48</v>
@@ -9002,13 +8998,13 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E19" t="s">
         <v>48</v>
@@ -9257,10 +9253,10 @@
         <v>122</v>
       </c>
       <c r="C21" t="s">
+        <v>290</v>
+      </c>
+      <c r="D21" t="s">
         <v>291</v>
-      </c>
-      <c r="D21" t="s">
-        <v>292</v>
       </c>
       <c r="E21" t="s">
         <v>151</v>
@@ -9380,13 +9376,13 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E22" t="s">
         <v>151</v>
@@ -9632,13 +9628,13 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C24" t="s">
         <v>193</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
@@ -9761,7 +9757,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D25" t="s">
         <v>140</v>
@@ -9884,13 +9880,13 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C26" t="s">
+        <v>283</v>
+      </c>
+      <c r="D26" t="s">
         <v>284</v>
-      </c>
-      <c r="D26" t="s">
-        <v>285</v>
       </c>
       <c r="E26" t="s">
         <v>48</v>
@@ -10136,7 +10132,7 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C28" t="s">
         <v>181</v>
@@ -10187,7 +10183,7 @@
         <v>103</v>
       </c>
       <c r="S28" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="T28" t="s">
         <v>191</v>
@@ -10262,7 +10258,7 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C29" t="s">
         <v>196</v>
@@ -10388,13 +10384,13 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C30" t="s">
         <v>205</v>
       </c>
       <c r="D30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E30" t="s">
         <v>50</v>
@@ -10502,7 +10498,7 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -10514,7 +10510,7 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C31" t="s">
         <v>209</v>
@@ -10571,7 +10567,7 @@
         <v>221</v>
       </c>
       <c r="U31" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -10640,7 +10636,7 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C32" t="s">
         <v>42</v>
@@ -10709,7 +10705,7 @@
         <v>218</v>
       </c>
       <c r="Y32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Z32">
         <v>20</v>
@@ -10766,16 +10762,16 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C33" t="s">
+        <v>255</v>
+      </c>
+      <c r="D33" t="s">
+        <v>257</v>
+      </c>
+      <c r="E33" t="s">
         <v>256</v>
-      </c>
-      <c r="D33" t="s">
-        <v>258</v>
-      </c>
-      <c r="E33" t="s">
-        <v>257</v>
       </c>
       <c r="F33">
         <v>60</v>
@@ -10880,7 +10876,7 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -10892,7 +10888,7 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C34" t="s">
         <v>202</v>
@@ -10940,7 +10936,7 @@
         <v>110</v>
       </c>
       <c r="R34" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="S34" t="s">
         <v>27</v>
@@ -11006,7 +11002,7 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -11018,7 +11014,7 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C35" t="s">
         <v>203</v>
@@ -11132,7 +11128,7 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AO35">
         <v>0</v>
@@ -11144,7 +11140,7 @@
         <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C36" t="s">
         <v>204</v>
@@ -11210,7 +11206,7 @@
         <v>27</v>
       </c>
       <c r="X36" t="s">
-        <v>232</v>
+        <v>33</v>
       </c>
       <c r="Y36" t="s">
         <v>218</v>
@@ -11258,7 +11254,7 @@
         <v>84</v>
       </c>
       <c r="AN36" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AO36">
         <v>0</v>
@@ -11801,13 +11797,13 @@
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C3" t="s">
         <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E3" t="s">
         <v>142</v>
@@ -11927,13 +11923,13 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C4" t="s">
         <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E4" t="s">
         <v>142</v>
@@ -12053,13 +12049,13 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C5" t="s">
         <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E5" t="s">
         <v>142</v>
@@ -12431,13 +12427,13 @@
         <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C8" t="s">
         <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E8" t="s">
         <v>142</v>
@@ -12809,7 +12805,7 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C11" t="s">
         <v>175</v>
@@ -12935,7 +12931,7 @@
         <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C12" t="s">
         <v>176</v>
@@ -13061,7 +13057,7 @@
         <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C13" t="s">
         <v>177</v>
@@ -13187,13 +13183,13 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E14" t="s">
         <v>142</v>
@@ -13313,13 +13309,13 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E15" t="s">
         <v>142</v>
@@ -13439,13 +13435,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D16" t="s">
         <v>289</v>
-      </c>
-      <c r="D16" t="s">
-        <v>290</v>
       </c>
       <c r="E16" t="s">
         <v>142</v>
@@ -13565,13 +13561,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E17" t="s">
         <v>142</v>
@@ -13691,13 +13687,13 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C18" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E18" t="s">
         <v>142</v>
@@ -13817,13 +13813,13 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E19" t="s">
         <v>142</v>
@@ -14072,10 +14068,10 @@
         <v>122</v>
       </c>
       <c r="C21" t="s">
+        <v>290</v>
+      </c>
+      <c r="D21" t="s">
         <v>291</v>
-      </c>
-      <c r="D21" t="s">
-        <v>292</v>
       </c>
       <c r="E21" t="s">
         <v>142</v>
@@ -14195,13 +14191,13 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E22" t="s">
         <v>142</v>
@@ -14447,13 +14443,13 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C24" t="s">
         <v>193</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E24" t="s">
         <v>142</v>
@@ -14576,7 +14572,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D25" t="s">
         <v>140</v>
@@ -14699,13 +14695,13 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C26" t="s">
+        <v>283</v>
+      </c>
+      <c r="D26" t="s">
         <v>284</v>
-      </c>
-      <c r="D26" t="s">
-        <v>285</v>
       </c>
       <c r="E26" t="s">
         <v>142</v>
@@ -14951,7 +14947,7 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C28" t="s">
         <v>181</v>
@@ -15002,7 +14998,7 @@
         <v>103</v>
       </c>
       <c r="S28" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="T28" t="s">
         <v>191</v>
@@ -15077,7 +15073,7 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C29" t="s">
         <v>196</v>
@@ -15203,13 +15199,13 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C30" t="s">
         <v>205</v>
       </c>
       <c r="D30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E30" t="s">
         <v>142</v>
@@ -15317,7 +15313,7 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -15329,7 +15325,7 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C31" t="s">
         <v>209</v>
@@ -15386,7 +15382,7 @@
         <v>221</v>
       </c>
       <c r="U31" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -15455,7 +15451,7 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C32" t="s">
         <v>42</v>
@@ -15524,7 +15520,7 @@
         <v>218</v>
       </c>
       <c r="Y32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Z32">
         <v>20</v>
@@ -15581,13 +15577,13 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C33" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E33" t="s">
         <v>142</v>
@@ -15695,7 +15691,7 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -15707,7 +15703,7 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C34" t="s">
         <v>202</v>
@@ -15755,7 +15751,7 @@
         <v>110</v>
       </c>
       <c r="R34" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="S34" t="s">
         <v>27</v>
@@ -15821,7 +15817,7 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -15833,7 +15829,7 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C35" t="s">
         <v>203</v>
@@ -15947,7 +15943,7 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AO35">
         <v>0</v>
@@ -15959,7 +15955,7 @@
         <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C36" t="s">
         <v>204</v>
@@ -16025,7 +16021,7 @@
         <v>27</v>
       </c>
       <c r="X36" t="s">
-        <v>232</v>
+        <v>33</v>
       </c>
       <c r="Y36" t="s">
         <v>218</v>
@@ -16073,7 +16069,7 @@
         <v>84</v>
       </c>
       <c r="AN36" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AO36">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDF4FB8-382B-49A6-B379-D27E009B8311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D976AC-23E5-45D4-A02C-A6AA649B8F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2355" yWindow="1155" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3120" yWindow="1245" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D976AC-23E5-45D4-A02C-A6AA649B8F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D1AD49-9E85-4A2D-945B-B3A4AFE0503A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1245" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2070" yWindow="1455" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -10312,7 +10312,7 @@
         <v>127</v>
       </c>
       <c r="T29" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="U29" t="s">
         <v>27</v>
@@ -10330,7 +10330,7 @@
         <v>136</v>
       </c>
       <c r="Z29">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AA29">
         <v>30</v>
@@ -10351,7 +10351,7 @@
         <v>8</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH29">
         <v>0</v>
@@ -10906,7 +10906,7 @@
         <v>300</v>
       </c>
       <c r="H34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -15127,7 +15127,7 @@
         <v>127</v>
       </c>
       <c r="T29" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="U29" t="s">
         <v>27</v>
@@ -15145,7 +15145,7 @@
         <v>136</v>
       </c>
       <c r="Z29">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AA29">
         <v>30</v>
@@ -15166,7 +15166,7 @@
         <v>8</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH29">
         <v>0</v>
@@ -15721,7 +15721,7 @@
         <v>300</v>
       </c>
       <c r="H34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I34">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D1AD49-9E85-4A2D-945B-B3A4AFE0503A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8350225-F0C3-4956-BD3D-80CBB44F76A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="1455" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1410" yWindow="1410" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -10780,7 +10780,7 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -10837,13 +10837,13 @@
         <v>65</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AB33">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AD33">
         <v>0</v>
@@ -15595,7 +15595,7 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -15652,13 +15652,13 @@
         <v>65</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AB33">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AD33">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8350225-F0C3-4956-BD3D-80CBB44F76A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37813CC7-5BBB-41B4-825C-7E96585A9A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1410" yWindow="1410" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37813CC7-5BBB-41B4-825C-7E96585A9A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBEEBC3-CE24-44AD-A419-A6FE05BCDE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2340" yWindow="1140" windowWidth="25560" windowHeight="14355" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -7864,16 +7864,16 @@
         <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="C10" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>282</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F10">
         <v>20</v>
@@ -7975,10 +7975,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AN10" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="AO10">
         <v>0</v>
@@ -7990,19 +7990,19 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>269</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="D11" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="F11">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -8020,7 +8020,7 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M11" t="s">
         <v>26</v>
@@ -8062,16 +8062,16 @@
         <v>27</v>
       </c>
       <c r="Z11">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB11">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AC11">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -8101,10 +8101,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AN11" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -8116,19 +8116,19 @@
         <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="C12" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D12" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
       </c>
       <c r="F12">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -8146,7 +8146,7 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M12" t="s">
         <v>26</v>
@@ -8242,19 +8242,19 @@
         <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E13" t="s">
         <v>48</v>
       </c>
       <c r="F13">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -8272,7 +8272,7 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="M13" t="s">
         <v>26</v>
@@ -8368,19 +8368,19 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="C14" t="s">
-        <v>238</v>
+        <v>176</v>
       </c>
       <c r="D14" t="s">
-        <v>292</v>
+        <v>179</v>
       </c>
       <c r="E14" t="s">
         <v>48</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -8398,7 +8398,7 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M14" t="s">
         <v>26</v>
@@ -8494,19 +8494,19 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="C15" t="s">
-        <v>242</v>
+        <v>177</v>
       </c>
       <c r="D15" t="s">
-        <v>239</v>
+        <v>180</v>
       </c>
       <c r="E15" t="s">
         <v>48</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -8518,13 +8518,13 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M15" t="s">
         <v>26</v>
@@ -8620,13 +8620,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="C16" t="s">
-        <v>288</v>
+        <v>238</v>
       </c>
       <c r="D16" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E16" t="s">
         <v>48</v>
@@ -8650,7 +8650,7 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M16" t="s">
         <v>26</v>
@@ -8746,13 +8746,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="C17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D17" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E17" t="s">
         <v>48</v>
@@ -8770,13 +8770,13 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M17" t="s">
         <v>26</v>
@@ -8872,13 +8872,13 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C18" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="D18" t="s">
-        <v>241</v>
+        <v>289</v>
       </c>
       <c r="E18" t="s">
         <v>48</v>
@@ -8896,13 +8896,13 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="M18" t="s">
         <v>26</v>
@@ -8998,19 +8998,19 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C19" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D19" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E19" t="s">
         <v>48</v>
       </c>
       <c r="F19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -9028,7 +9028,7 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M19" t="s">
         <v>26</v>
@@ -9124,16 +9124,16 @@
         <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
+        <v>252</v>
       </c>
       <c r="C20" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>241</v>
       </c>
       <c r="E20" t="s">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="F20">
         <v>10</v>
@@ -9148,13 +9148,13 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M20" t="s">
         <v>26</v>
@@ -9196,16 +9196,16 @@
         <v>27</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AA20">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AB20">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AC20">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -9235,10 +9235,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="AN20" t="s">
-        <v>27</v>
+        <v>186</v>
       </c>
       <c r="AO20">
         <v>0</v>
@@ -9250,19 +9250,19 @@
         <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>272</v>
       </c>
       <c r="C21" t="s">
-        <v>290</v>
+        <v>246</v>
       </c>
       <c r="D21" t="s">
-        <v>291</v>
+        <v>245</v>
       </c>
       <c r="E21" t="s">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -9322,16 +9322,16 @@
         <v>27</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AA21">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AB21">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AC21">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -9361,10 +9361,10 @@
         <v>0</v>
       </c>
       <c r="AM21" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="AN21" t="s">
-        <v>27</v>
+        <v>186</v>
       </c>
       <c r="AO21">
         <v>0</v>
@@ -9376,19 +9376,19 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>250</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>237</v>
+        <v>150</v>
       </c>
       <c r="D22" t="s">
-        <v>236</v>
+        <v>149</v>
       </c>
       <c r="E22" t="s">
         <v>151</v>
       </c>
       <c r="F22">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -9505,16 +9505,16 @@
         <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>167</v>
+        <v>290</v>
       </c>
       <c r="D23" t="s">
-        <v>166</v>
+        <v>291</v>
       </c>
       <c r="E23" t="s">
         <v>151</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -9526,7 +9526,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -9628,16 +9628,16 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C24" t="s">
-        <v>193</v>
+        <v>237</v>
       </c>
       <c r="D24" t="s">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>151</v>
       </c>
       <c r="F24">
         <v>20</v>
@@ -9700,16 +9700,16 @@
         <v>27</v>
       </c>
       <c r="Z24">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA24">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB24">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AC24">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AD24">
         <v>0</v>
@@ -9754,19 +9754,19 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
-        <v>280</v>
+        <v>167</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="E25" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="F25">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -12679,13 +12679,13 @@
         <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="C10" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>282</v>
       </c>
       <c r="E10" t="s">
         <v>142</v>
@@ -12790,10 +12790,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AN10" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="AO10">
         <v>0</v>
@@ -12805,19 +12805,19 @@
         <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>269</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="D11" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
         <v>142</v>
       </c>
       <c r="F11">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -12835,7 +12835,7 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M11" t="s">
         <v>26</v>
@@ -12877,16 +12877,16 @@
         <v>27</v>
       </c>
       <c r="Z11">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB11">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AC11">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -12916,10 +12916,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AN11" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -12931,19 +12931,19 @@
         <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="C12" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D12" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="E12" t="s">
         <v>142</v>
       </c>
       <c r="F12">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -12961,7 +12961,7 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M12" t="s">
         <v>26</v>
@@ -13057,19 +13057,19 @@
         <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E13" t="s">
         <v>142</v>
       </c>
       <c r="F13">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -13087,7 +13087,7 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="M13" t="s">
         <v>26</v>
@@ -13183,19 +13183,19 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="C14" t="s">
-        <v>238</v>
+        <v>176</v>
       </c>
       <c r="D14" t="s">
-        <v>292</v>
+        <v>179</v>
       </c>
       <c r="E14" t="s">
         <v>142</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -13213,7 +13213,7 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M14" t="s">
         <v>26</v>
@@ -13309,19 +13309,19 @@
         <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="C15" t="s">
-        <v>242</v>
+        <v>177</v>
       </c>
       <c r="D15" t="s">
-        <v>239</v>
+        <v>180</v>
       </c>
       <c r="E15" t="s">
         <v>142</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -13333,13 +13333,13 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M15" t="s">
         <v>26</v>
@@ -13435,13 +13435,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="C16" t="s">
-        <v>288</v>
+        <v>238</v>
       </c>
       <c r="D16" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E16" t="s">
         <v>142</v>
@@ -13465,7 +13465,7 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M16" t="s">
         <v>26</v>
@@ -13561,13 +13561,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="C17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D17" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E17" t="s">
         <v>142</v>
@@ -13585,13 +13585,13 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M17" t="s">
         <v>26</v>
@@ -13687,13 +13687,13 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C18" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="D18" t="s">
-        <v>241</v>
+        <v>289</v>
       </c>
       <c r="E18" t="s">
         <v>142</v>
@@ -13711,13 +13711,13 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="M18" t="s">
         <v>26</v>
@@ -13813,19 +13813,19 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C19" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D19" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E19" t="s">
         <v>142</v>
       </c>
       <c r="F19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -13843,7 +13843,7 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M19" t="s">
         <v>26</v>
@@ -13939,13 +13939,13 @@
         <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
+        <v>252</v>
       </c>
       <c r="C20" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>241</v>
       </c>
       <c r="E20" t="s">
         <v>142</v>
@@ -13963,13 +13963,13 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M20" t="s">
         <v>26</v>
@@ -14011,16 +14011,16 @@
         <v>27</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AA20">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AB20">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AC20">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -14050,10 +14050,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="AN20" t="s">
-        <v>27</v>
+        <v>186</v>
       </c>
       <c r="AO20">
         <v>0</v>
@@ -14065,19 +14065,19 @@
         <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>272</v>
       </c>
       <c r="C21" t="s">
-        <v>290</v>
+        <v>246</v>
       </c>
       <c r="D21" t="s">
-        <v>291</v>
+        <v>245</v>
       </c>
       <c r="E21" t="s">
         <v>142</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -14137,16 +14137,16 @@
         <v>27</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AA21">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AB21">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AC21">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -14176,10 +14176,10 @@
         <v>0</v>
       </c>
       <c r="AM21" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="AN21" t="s">
-        <v>27</v>
+        <v>186</v>
       </c>
       <c r="AO21">
         <v>0</v>
@@ -14191,19 +14191,19 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>250</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>237</v>
+        <v>150</v>
       </c>
       <c r="D22" t="s">
-        <v>236</v>
+        <v>149</v>
       </c>
       <c r="E22" t="s">
         <v>142</v>
       </c>
       <c r="F22">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -14320,16 +14320,16 @@
         <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>167</v>
+        <v>290</v>
       </c>
       <c r="D23" t="s">
-        <v>166</v>
+        <v>291</v>
       </c>
       <c r="E23" t="s">
         <v>142</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -14341,7 +14341,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -14443,13 +14443,13 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C24" t="s">
-        <v>193</v>
+        <v>237</v>
       </c>
       <c r="D24" t="s">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="E24" t="s">
         <v>142</v>
@@ -14515,16 +14515,16 @@
         <v>27</v>
       </c>
       <c r="Z24">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA24">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB24">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AC24">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AD24">
         <v>0</v>
@@ -14569,19 +14569,19 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
-        <v>280</v>
+        <v>167</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="E25" t="s">
         <v>142</v>
       </c>
       <c r="F25">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -14593,7 +14593,7 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBEEBC3-CE24-44AD-A419-A6FE05BCDE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9BB3B95-13DF-4286-8272-32E79ACF6FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1140" windowWidth="25560" windowHeight="14355" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3015" yWindow="885" windowWidth="25560" windowHeight="14355" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="294">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -1732,6 +1732,10 @@
     <rPh sb="1" eb="3">
       <t>ハナバタケ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>roten_mini_icon</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -9502,7 +9506,7 @@
         <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>293</v>
       </c>
       <c r="C23" t="s">
         <v>290</v>
@@ -14317,7 +14321,7 @@
         <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>293</v>
       </c>
       <c r="C23" t="s">
         <v>290</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9BB3B95-13DF-4286-8272-32E79ACF6FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F21C0C-83AC-4654-8036-5FAA671E801D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3015" yWindow="885" windowWidth="25560" windowHeight="14355" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2595" yWindow="885" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="296">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -1736,6 +1736,17 @@
   </si>
   <si>
     <t>roten_mini_icon</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Or_Hiroba1_HotSpring</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>温泉「ヘルシーメルシー」</t>
+    <rPh sb="0" eb="2">
+      <t>オンセン</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -6710,7 +6721,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAAE7BC7-74FC-4400-A474-EA5B977D362B}">
-  <dimension ref="A1:AO38"/>
+  <dimension ref="A1:AO39"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -7360,7 +7371,7 @@
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A6">
-        <f t="shared" ref="A6:A38" si="0">ROW()-2+100</f>
+        <f t="shared" ref="A6:A39" si="0">ROW()-2+100</f>
         <v>104</v>
       </c>
       <c r="B6" t="s">
@@ -9632,19 +9643,19 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C24" t="s">
-        <v>237</v>
+        <v>294</v>
       </c>
       <c r="D24" t="s">
-        <v>236</v>
+        <v>295</v>
       </c>
       <c r="E24" t="s">
         <v>151</v>
       </c>
       <c r="F24">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -9662,7 +9673,7 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M24" t="s">
         <v>26</v>
@@ -9758,19 +9769,19 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>250</v>
       </c>
       <c r="C25" t="s">
-        <v>167</v>
+        <v>237</v>
       </c>
       <c r="D25" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="E25" t="s">
         <v>151</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -9782,7 +9793,7 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -9884,37 +9895,37 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>287</v>
+        <v>122</v>
       </c>
       <c r="C26" t="s">
-        <v>283</v>
+        <v>167</v>
       </c>
       <c r="D26" t="s">
-        <v>284</v>
+        <v>166</v>
       </c>
       <c r="E26" t="s">
-        <v>48</v>
+        <v>151</v>
       </c>
       <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
         <v>10</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>9999</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>20</v>
       </c>
       <c r="M26" t="s">
         <v>26</v>
@@ -9956,16 +9967,16 @@
         <v>27</v>
       </c>
       <c r="Z26">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA26">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB26">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AC26">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -9995,10 +10006,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AN26" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -10010,52 +10021,52 @@
         <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>287</v>
       </c>
       <c r="C27" t="s">
-        <v>194</v>
+        <v>283</v>
       </c>
       <c r="D27" t="s">
-        <v>152</v>
+        <v>284</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M27" t="s">
         <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="O27" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P27" t="s">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="Q27" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="R27" t="s">
         <v>27</v>
@@ -10076,25 +10087,25 @@
         <v>27</v>
       </c>
       <c r="X27" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="Y27" t="s">
         <v>27</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA27">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="AB27">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AD27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE27">
         <v>0</v>
@@ -10112,19 +10123,19 @@
         <v>0</v>
       </c>
       <c r="AJ27">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AK27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AN27" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -10136,19 +10147,19 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>259</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D28" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E28" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="F28">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -10172,25 +10183,25 @@
         <v>26</v>
       </c>
       <c r="N28" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O28" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="P28" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="Q28" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="R28" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="S28" t="s">
-        <v>279</v>
+        <v>27</v>
       </c>
       <c r="T28" t="s">
-        <v>191</v>
+        <v>27</v>
       </c>
       <c r="U28" t="s">
         <v>27</v>
@@ -10202,55 +10213,55 @@
         <v>27</v>
       </c>
       <c r="X28" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="Y28" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>68</v>
+      </c>
+      <c r="AB28">
         <v>15</v>
       </c>
-      <c r="AA28">
-        <v>16</v>
-      </c>
-      <c r="AB28">
-        <v>17</v>
-      </c>
       <c r="AC28">
+        <v>7</v>
+      </c>
+      <c r="AD28">
         <v>10</v>
       </c>
-      <c r="AD28">
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>98</v>
+      </c>
+      <c r="AK28">
         <v>2</v>
       </c>
-      <c r="AE28">
-        <v>10</v>
-      </c>
-      <c r="AF28">
-        <v>4</v>
-      </c>
-      <c r="AG28">
-        <v>26</v>
-      </c>
-      <c r="AH28">
-        <v>0</v>
-      </c>
-      <c r="AI28">
-        <v>0</v>
-      </c>
-      <c r="AJ28">
-        <v>78</v>
-      </c>
-      <c r="AK28">
-        <v>15</v>
-      </c>
       <c r="AL28">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AN28" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -10262,31 +10273,31 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C29" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D29" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="E29" t="s">
         <v>116</v>
       </c>
       <c r="F29">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -10298,25 +10309,25 @@
         <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="O29" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="P29" t="s">
-        <v>223</v>
+        <v>25</v>
       </c>
       <c r="Q29" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="R29" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="S29" t="s">
-        <v>127</v>
+        <v>279</v>
       </c>
       <c r="T29" t="s">
-        <v>99</v>
+        <v>191</v>
       </c>
       <c r="U29" t="s">
         <v>27</v>
@@ -10328,34 +10339,34 @@
         <v>27</v>
       </c>
       <c r="X29" t="s">
-        <v>208</v>
+        <v>33</v>
       </c>
       <c r="Y29" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="Z29">
         <v>15</v>
       </c>
       <c r="AA29">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AB29">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC29">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD29">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AE29">
         <v>10</v>
       </c>
       <c r="AF29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG29">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="AH29">
         <v>0</v>
@@ -10364,19 +10375,19 @@
         <v>0</v>
       </c>
       <c r="AJ29">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AK29">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AL29">
         <v>7</v>
       </c>
       <c r="AM29" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AN29" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -10388,25 +10399,25 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C30" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D30" t="s">
-        <v>267</v>
+        <v>195</v>
       </c>
       <c r="E30" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F30">
         <v>30</v>
       </c>
       <c r="G30">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -10418,32 +10429,32 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M30" t="s">
         <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P30" t="s">
-        <v>108</v>
+        <v>223</v>
       </c>
       <c r="Q30" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="R30" t="s">
+        <v>128</v>
+      </c>
+      <c r="S30" t="s">
+        <v>127</v>
+      </c>
+      <c r="T30" t="s">
         <v>99</v>
       </c>
-      <c r="S30" t="s">
-        <v>27</v>
-      </c>
-      <c r="T30" t="s">
-        <v>27</v>
-      </c>
       <c r="U30" t="s">
         <v>27</v>
       </c>
@@ -10454,34 +10465,34 @@
         <v>27</v>
       </c>
       <c r="X30" t="s">
-        <v>111</v>
+        <v>208</v>
       </c>
       <c r="Y30" t="s">
-        <v>228</v>
+        <v>136</v>
       </c>
       <c r="Z30">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AA30">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB30">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AC30">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AD30">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AE30">
         <v>10</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH30">
         <v>0</v>
@@ -10490,19 +10501,19 @@
         <v>0</v>
       </c>
       <c r="AJ30">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK30">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AL30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM30" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="AN30" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -10514,25 +10525,25 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="C31" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D31" t="s">
-        <v>197</v>
+        <v>267</v>
       </c>
       <c r="E31" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="F31">
         <v>30</v>
       </c>
       <c r="G31">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -10544,7 +10555,7 @@
         <v>1</v>
       </c>
       <c r="L31">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M31" t="s">
         <v>26</v>
@@ -10553,25 +10564,25 @@
         <v>72</v>
       </c>
       <c r="O31" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="P31" t="s">
         <v>108</v>
       </c>
       <c r="Q31" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="R31" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="S31" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="T31" t="s">
-        <v>221</v>
+        <v>27</v>
       </c>
       <c r="U31" t="s">
-        <v>247</v>
+        <v>27</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -10580,55 +10591,55 @@
         <v>27</v>
       </c>
       <c r="X31" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="Y31" t="s">
-        <v>111</v>
+        <v>228</v>
       </c>
       <c r="Z31">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AA31">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="AB31">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AC31">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AD31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE31">
         <v>10</v>
       </c>
       <c r="AF31">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>94</v>
+      </c>
+      <c r="AK31">
+        <v>1</v>
+      </c>
+      <c r="AL31">
         <v>5</v>
-      </c>
-      <c r="AI31">
-        <v>0</v>
-      </c>
-      <c r="AJ31">
-        <v>83</v>
-      </c>
-      <c r="AK31">
-        <v>16</v>
-      </c>
-      <c r="AL31">
-        <v>1</v>
       </c>
       <c r="AM31" t="s">
         <v>84</v>
       </c>
       <c r="AN31" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -10640,25 +10651,25 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="D32" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F32">
         <v>30</v>
       </c>
       <c r="G32">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -10676,28 +10687,28 @@
         <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
       <c r="O32" t="s">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="Q32" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="R32" t="s">
-        <v>222</v>
+        <v>112</v>
       </c>
       <c r="S32" t="s">
-        <v>226</v>
+        <v>74</v>
       </c>
       <c r="T32" t="s">
-        <v>27</v>
+        <v>221</v>
       </c>
       <c r="U32" t="s">
-        <v>27</v>
+        <v>247</v>
       </c>
       <c r="V32" t="s">
         <v>27</v>
@@ -10706,22 +10717,22 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>218</v>
+        <v>72</v>
       </c>
       <c r="Y32" t="s">
-        <v>266</v>
+        <v>111</v>
       </c>
       <c r="Z32">
         <v>20</v>
       </c>
       <c r="AA32">
+        <v>5</v>
+      </c>
+      <c r="AB32">
         <v>20</v>
       </c>
-      <c r="AB32">
-        <v>25</v>
-      </c>
       <c r="AC32">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD32">
         <v>5</v>
@@ -10730,31 +10741,31 @@
         <v>10</v>
       </c>
       <c r="AF32">
+        <v>13</v>
+      </c>
+      <c r="AG32">
         <v>10</v>
       </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
       <c r="AH32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI32">
         <v>0</v>
       </c>
       <c r="AJ32">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AK32">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AL32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM32" t="s">
         <v>84</v>
       </c>
       <c r="AN32" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -10766,25 +10777,25 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>255</v>
+        <v>42</v>
       </c>
       <c r="D33" t="s">
-        <v>257</v>
+        <v>201</v>
       </c>
       <c r="E33" t="s">
-        <v>256</v>
+        <v>50</v>
       </c>
       <c r="F33">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -10802,22 +10813,22 @@
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="O33" t="s">
-        <v>27</v>
+        <v>220</v>
       </c>
       <c r="P33" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q33" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="R33" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="S33" t="s">
-        <v>27</v>
+        <v>226</v>
       </c>
       <c r="T33" t="s">
         <v>27</v>
@@ -10832,31 +10843,31 @@
         <v>27</v>
       </c>
       <c r="X33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Y33" t="s">
-        <v>27</v>
+        <v>266</v>
       </c>
       <c r="Z33">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AA33">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG33">
         <v>0</v>
@@ -10868,19 +10879,19 @@
         <v>0</v>
       </c>
       <c r="AJ33">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="AK33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM33" t="s">
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>258</v>
+        <v>224</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -10892,25 +10903,25 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C34" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="D34" t="s">
-        <v>198</v>
+        <v>257</v>
       </c>
       <c r="E34" t="s">
-        <v>116</v>
+        <v>256</v>
       </c>
       <c r="F34">
         <v>60</v>
       </c>
       <c r="G34">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -10922,34 +10933,34 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M34" t="s">
         <v>26</v>
       </c>
       <c r="N34" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="O34" t="s">
-        <v>215</v>
+        <v>27</v>
       </c>
       <c r="P34" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="Q34" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="R34" t="s">
-        <v>254</v>
+        <v>27</v>
       </c>
       <c r="S34" t="s">
         <v>27</v>
       </c>
       <c r="T34" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="U34" t="s">
-        <v>227</v>
+        <v>27</v>
       </c>
       <c r="V34" t="s">
         <v>27</v>
@@ -10958,55 +10969,55 @@
         <v>27</v>
       </c>
       <c r="X34" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="Y34" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="Z34">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AA34">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AB34">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH34">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI34">
         <v>0</v>
       </c>
       <c r="AJ34">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="AK34">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AL34">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AM34" t="s">
         <v>84</v>
       </c>
       <c r="AN34" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -11018,25 +11029,25 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C35" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D35" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E35" t="s">
         <v>116</v>
       </c>
       <c r="F35">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G35">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -11048,34 +11059,34 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M35" t="s">
         <v>26</v>
       </c>
       <c r="N35" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="O35" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="P35" t="s">
-        <v>216</v>
+        <v>138</v>
       </c>
       <c r="Q35" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="R35" t="s">
-        <v>103</v>
+        <v>254</v>
       </c>
       <c r="S35" t="s">
         <v>27</v>
       </c>
       <c r="T35" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="U35" t="s">
-        <v>27</v>
+        <v>227</v>
       </c>
       <c r="V35" t="s">
         <v>27</v>
@@ -11084,55 +11095,55 @@
         <v>27</v>
       </c>
       <c r="X35" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="Y35" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="Z35">
         <v>20</v>
       </c>
       <c r="AA35">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AB35">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AC35">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AD35">
+        <v>15</v>
+      </c>
+      <c r="AE35">
+        <v>10</v>
+      </c>
+      <c r="AF35">
+        <v>8</v>
+      </c>
+      <c r="AG35">
         <v>5</v>
       </c>
-      <c r="AE35">
+      <c r="AH35">
         <v>5</v>
       </c>
-      <c r="AF35">
-        <v>0</v>
-      </c>
-      <c r="AG35">
-        <v>0</v>
-      </c>
-      <c r="AH35">
-        <v>0</v>
-      </c>
       <c r="AI35">
         <v>0</v>
       </c>
       <c r="AJ35">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AK35">
         <v>10</v>
       </c>
       <c r="AL35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AM35" t="s">
         <v>84</v>
       </c>
       <c r="AN35" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AO35">
         <v>0</v>
@@ -11144,25 +11155,25 @@
         <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="C36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D36" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E36" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F36">
         <v>90</v>
       </c>
       <c r="G36">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="H36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -11180,19 +11191,19 @@
         <v>26</v>
       </c>
       <c r="N36" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="O36" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="P36" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="Q36" t="s">
-        <v>217</v>
+        <v>70</v>
       </c>
       <c r="R36" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="S36" t="s">
         <v>27</v>
@@ -11210,28 +11221,28 @@
         <v>27</v>
       </c>
       <c r="X36" t="s">
-        <v>33</v>
+        <v>211</v>
       </c>
       <c r="Y36" t="s">
-        <v>218</v>
+        <v>27</v>
       </c>
       <c r="Z36">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="AA36">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="AB36">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AC36">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AD36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF36">
         <v>0</v>
@@ -11246,19 +11257,19 @@
         <v>0</v>
       </c>
       <c r="AJ36">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK36">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AL36">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AM36" t="s">
         <v>84</v>
       </c>
       <c r="AN36" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AO36">
         <v>0</v>
@@ -11270,52 +11281,52 @@
         <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>265</v>
       </c>
       <c r="C37" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="D37" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="E37" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F37">
         <v>90</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M37" t="s">
         <v>26</v>
       </c>
       <c r="N37" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="O37" t="s">
-        <v>27</v>
+        <v>230</v>
       </c>
       <c r="P37" t="s">
-        <v>27</v>
+        <v>231</v>
       </c>
       <c r="Q37" t="s">
-        <v>27</v>
+        <v>217</v>
       </c>
       <c r="R37" t="s">
         <v>27</v>
@@ -11336,25 +11347,25 @@
         <v>27</v>
       </c>
       <c r="X37" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="Y37" t="s">
-        <v>27</v>
+        <v>218</v>
       </c>
       <c r="Z37">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AA37">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AB37">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AC37">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE37">
         <v>0</v>
@@ -11372,19 +11383,19 @@
         <v>0</v>
       </c>
       <c r="AJ37">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AK37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM37" t="s">
         <v>84</v>
       </c>
       <c r="AN37" t="s">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="AO37">
         <v>0</v>
@@ -11399,10 +11410,10 @@
         <v>40</v>
       </c>
       <c r="C38" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D38" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E38" t="s">
         <v>48</v>
@@ -11420,7 +11431,7 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -11513,6 +11524,132 @@
         <v>186</v>
       </c>
       <c r="AO38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:41" x14ac:dyDescent="0.4">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>137</v>
+      </c>
+      <c r="B39" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" t="s">
+        <v>160</v>
+      </c>
+      <c r="D39" t="s">
+        <v>161</v>
+      </c>
+      <c r="E39" t="s">
+        <v>48</v>
+      </c>
+      <c r="F39">
+        <v>90</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>9999</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>10</v>
+      </c>
+      <c r="M39" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39" t="s">
+        <v>27</v>
+      </c>
+      <c r="O39" t="s">
+        <v>27</v>
+      </c>
+      <c r="P39" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>27</v>
+      </c>
+      <c r="R39" t="s">
+        <v>27</v>
+      </c>
+      <c r="S39" t="s">
+        <v>27</v>
+      </c>
+      <c r="T39" t="s">
+        <v>27</v>
+      </c>
+      <c r="U39" t="s">
+        <v>27</v>
+      </c>
+      <c r="V39" t="s">
+        <v>27</v>
+      </c>
+      <c r="W39" t="s">
+        <v>27</v>
+      </c>
+      <c r="X39" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z39">
+        <v>60</v>
+      </c>
+      <c r="AA39">
+        <v>25</v>
+      </c>
+      <c r="AB39">
+        <v>12</v>
+      </c>
+      <c r="AC39">
+        <v>3</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39">
+        <v>0</v>
+      </c>
+      <c r="AI39">
+        <v>0</v>
+      </c>
+      <c r="AJ39">
+        <v>95</v>
+      </c>
+      <c r="AK39">
+        <v>5</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN39" t="s">
+        <v>186</v>
+      </c>
+      <c r="AO39">
         <v>1</v>
       </c>
     </row>
@@ -11525,7 +11662,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAD14E5B-6BFE-4D20-B771-5A2DB6950621}">
-  <dimension ref="A1:AO38"/>
+  <dimension ref="A1:AO39"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -12679,7 +12816,7 @@
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A10">
-        <f t="shared" ref="A10:A38" si="1">ROW()-2+100</f>
+        <f t="shared" ref="A10:A39" si="1">ROW()-2+100</f>
         <v>108</v>
       </c>
       <c r="B10" t="s">
@@ -14447,19 +14584,19 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C24" t="s">
-        <v>237</v>
+        <v>294</v>
       </c>
       <c r="D24" t="s">
-        <v>236</v>
+        <v>295</v>
       </c>
       <c r="E24" t="s">
         <v>142</v>
       </c>
       <c r="F24">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -14477,7 +14614,7 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M24" t="s">
         <v>26</v>
@@ -14573,19 +14710,19 @@
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>250</v>
       </c>
       <c r="C25" t="s">
-        <v>167</v>
+        <v>237</v>
       </c>
       <c r="D25" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="E25" t="s">
         <v>142</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -14597,7 +14734,7 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -14699,37 +14836,37 @@
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>287</v>
+        <v>122</v>
       </c>
       <c r="C26" t="s">
-        <v>283</v>
+        <v>167</v>
       </c>
       <c r="D26" t="s">
-        <v>284</v>
+        <v>166</v>
       </c>
       <c r="E26" t="s">
         <v>142</v>
       </c>
       <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
         <v>10</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>9999</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>20</v>
       </c>
       <c r="M26" t="s">
         <v>26</v>
@@ -14771,16 +14908,16 @@
         <v>27</v>
       </c>
       <c r="Z26">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA26">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB26">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AC26">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -14810,10 +14947,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AN26" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -14825,52 +14962,52 @@
         <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>287</v>
       </c>
       <c r="C27" t="s">
-        <v>194</v>
+        <v>283</v>
       </c>
       <c r="D27" t="s">
-        <v>152</v>
+        <v>284</v>
       </c>
       <c r="E27" t="s">
         <v>142</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M27" t="s">
         <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="O27" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P27" t="s">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="Q27" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="R27" t="s">
         <v>27</v>
@@ -14891,25 +15028,25 @@
         <v>27</v>
       </c>
       <c r="X27" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="Y27" t="s">
         <v>27</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA27">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="AB27">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AD27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE27">
         <v>0</v>
@@ -14927,19 +15064,19 @@
         <v>0</v>
       </c>
       <c r="AJ27">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AK27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AN27" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -14951,19 +15088,19 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>259</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D28" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E28" t="s">
         <v>142</v>
       </c>
       <c r="F28">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -14987,25 +15124,25 @@
         <v>26</v>
       </c>
       <c r="N28" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O28" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="P28" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="Q28" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="R28" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="S28" t="s">
-        <v>279</v>
+        <v>27</v>
       </c>
       <c r="T28" t="s">
-        <v>191</v>
+        <v>27</v>
       </c>
       <c r="U28" t="s">
         <v>27</v>
@@ -15017,55 +15154,55 @@
         <v>27</v>
       </c>
       <c r="X28" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="Y28" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>68</v>
+      </c>
+      <c r="AB28">
         <v>15</v>
       </c>
-      <c r="AA28">
-        <v>16</v>
-      </c>
-      <c r="AB28">
-        <v>17</v>
-      </c>
       <c r="AC28">
+        <v>7</v>
+      </c>
+      <c r="AD28">
         <v>10</v>
       </c>
-      <c r="AD28">
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>98</v>
+      </c>
+      <c r="AK28">
         <v>2</v>
       </c>
-      <c r="AE28">
-        <v>10</v>
-      </c>
-      <c r="AF28">
-        <v>4</v>
-      </c>
-      <c r="AG28">
-        <v>26</v>
-      </c>
-      <c r="AH28">
-        <v>0</v>
-      </c>
-      <c r="AI28">
-        <v>0</v>
-      </c>
-      <c r="AJ28">
-        <v>78</v>
-      </c>
-      <c r="AK28">
-        <v>15</v>
-      </c>
       <c r="AL28">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AN28" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -15077,31 +15214,31 @@
         <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C29" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D29" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="E29" t="s">
         <v>142</v>
       </c>
       <c r="F29">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -15113,25 +15250,25 @@
         <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="O29" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="P29" t="s">
-        <v>223</v>
+        <v>25</v>
       </c>
       <c r="Q29" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="R29" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="S29" t="s">
-        <v>127</v>
+        <v>279</v>
       </c>
       <c r="T29" t="s">
-        <v>99</v>
+        <v>191</v>
       </c>
       <c r="U29" t="s">
         <v>27</v>
@@ -15143,34 +15280,34 @@
         <v>27</v>
       </c>
       <c r="X29" t="s">
-        <v>208</v>
+        <v>33</v>
       </c>
       <c r="Y29" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="Z29">
         <v>15</v>
       </c>
       <c r="AA29">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AB29">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC29">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD29">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AE29">
         <v>10</v>
       </c>
       <c r="AF29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG29">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="AH29">
         <v>0</v>
@@ -15179,19 +15316,19 @@
         <v>0</v>
       </c>
       <c r="AJ29">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AK29">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AL29">
         <v>7</v>
       </c>
       <c r="AM29" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AN29" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -15203,13 +15340,13 @@
         <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C30" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D30" t="s">
-        <v>267</v>
+        <v>195</v>
       </c>
       <c r="E30" t="s">
         <v>142</v>
@@ -15218,10 +15355,10 @@
         <v>30</v>
       </c>
       <c r="G30">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -15233,32 +15370,32 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M30" t="s">
         <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P30" t="s">
-        <v>108</v>
+        <v>223</v>
       </c>
       <c r="Q30" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="R30" t="s">
+        <v>128</v>
+      </c>
+      <c r="S30" t="s">
+        <v>127</v>
+      </c>
+      <c r="T30" t="s">
         <v>99</v>
       </c>
-      <c r="S30" t="s">
-        <v>27</v>
-      </c>
-      <c r="T30" t="s">
-        <v>27</v>
-      </c>
       <c r="U30" t="s">
         <v>27</v>
       </c>
@@ -15269,34 +15406,34 @@
         <v>27</v>
       </c>
       <c r="X30" t="s">
-        <v>111</v>
+        <v>208</v>
       </c>
       <c r="Y30" t="s">
-        <v>228</v>
+        <v>136</v>
       </c>
       <c r="Z30">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AA30">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB30">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AC30">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AD30">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AE30">
         <v>10</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH30">
         <v>0</v>
@@ -15305,19 +15442,19 @@
         <v>0</v>
       </c>
       <c r="AJ30">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK30">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AL30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM30" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="AN30" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -15329,13 +15466,13 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="C31" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D31" t="s">
-        <v>197</v>
+        <v>267</v>
       </c>
       <c r="E31" t="s">
         <v>142</v>
@@ -15344,10 +15481,10 @@
         <v>30</v>
       </c>
       <c r="G31">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -15359,7 +15496,7 @@
         <v>1</v>
       </c>
       <c r="L31">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M31" t="s">
         <v>26</v>
@@ -15368,25 +15505,25 @@
         <v>72</v>
       </c>
       <c r="O31" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="P31" t="s">
         <v>108</v>
       </c>
       <c r="Q31" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="R31" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="S31" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="T31" t="s">
-        <v>221</v>
+        <v>27</v>
       </c>
       <c r="U31" t="s">
-        <v>247</v>
+        <v>27</v>
       </c>
       <c r="V31" t="s">
         <v>27</v>
@@ -15395,55 +15532,55 @@
         <v>27</v>
       </c>
       <c r="X31" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="Y31" t="s">
-        <v>111</v>
+        <v>228</v>
       </c>
       <c r="Z31">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AA31">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="AB31">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AC31">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AD31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE31">
         <v>10</v>
       </c>
       <c r="AF31">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>94</v>
+      </c>
+      <c r="AK31">
+        <v>1</v>
+      </c>
+      <c r="AL31">
         <v>5</v>
-      </c>
-      <c r="AI31">
-        <v>0</v>
-      </c>
-      <c r="AJ31">
-        <v>83</v>
-      </c>
-      <c r="AK31">
-        <v>16</v>
-      </c>
-      <c r="AL31">
-        <v>1</v>
       </c>
       <c r="AM31" t="s">
         <v>84</v>
       </c>
       <c r="AN31" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -15455,13 +15592,13 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="D32" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E32" t="s">
         <v>142</v>
@@ -15470,10 +15607,10 @@
         <v>30</v>
       </c>
       <c r="G32">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -15491,28 +15628,28 @@
         <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
       <c r="O32" t="s">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="Q32" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="R32" t="s">
-        <v>222</v>
+        <v>112</v>
       </c>
       <c r="S32" t="s">
-        <v>226</v>
+        <v>74</v>
       </c>
       <c r="T32" t="s">
-        <v>27</v>
+        <v>221</v>
       </c>
       <c r="U32" t="s">
-        <v>27</v>
+        <v>247</v>
       </c>
       <c r="V32" t="s">
         <v>27</v>
@@ -15521,22 +15658,22 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>218</v>
+        <v>72</v>
       </c>
       <c r="Y32" t="s">
-        <v>266</v>
+        <v>111</v>
       </c>
       <c r="Z32">
         <v>20</v>
       </c>
       <c r="AA32">
+        <v>5</v>
+      </c>
+      <c r="AB32">
         <v>20</v>
       </c>
-      <c r="AB32">
-        <v>25</v>
-      </c>
       <c r="AC32">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD32">
         <v>5</v>
@@ -15545,31 +15682,31 @@
         <v>10</v>
       </c>
       <c r="AF32">
+        <v>13</v>
+      </c>
+      <c r="AG32">
         <v>10</v>
       </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
       <c r="AH32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI32">
         <v>0</v>
       </c>
       <c r="AJ32">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AK32">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AL32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM32" t="s">
         <v>84</v>
       </c>
       <c r="AN32" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -15581,25 +15718,25 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>255</v>
+        <v>42</v>
       </c>
       <c r="D33" t="s">
-        <v>257</v>
+        <v>201</v>
       </c>
       <c r="E33" t="s">
         <v>142</v>
       </c>
       <c r="F33">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -15617,22 +15754,22 @@
         <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="O33" t="s">
-        <v>27</v>
+        <v>220</v>
       </c>
       <c r="P33" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q33" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="R33" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="S33" t="s">
-        <v>27</v>
+        <v>226</v>
       </c>
       <c r="T33" t="s">
         <v>27</v>
@@ -15647,31 +15784,31 @@
         <v>27</v>
       </c>
       <c r="X33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Y33" t="s">
-        <v>27</v>
+        <v>266</v>
       </c>
       <c r="Z33">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AA33">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG33">
         <v>0</v>
@@ -15683,19 +15820,19 @@
         <v>0</v>
       </c>
       <c r="AJ33">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="AK33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM33" t="s">
         <v>84</v>
       </c>
       <c r="AN33" t="s">
-        <v>258</v>
+        <v>224</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -15707,13 +15844,13 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C34" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="D34" t="s">
-        <v>198</v>
+        <v>257</v>
       </c>
       <c r="E34" t="s">
         <v>142</v>
@@ -15722,10 +15859,10 @@
         <v>60</v>
       </c>
       <c r="G34">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -15737,34 +15874,34 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M34" t="s">
         <v>26</v>
       </c>
       <c r="N34" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="O34" t="s">
-        <v>215</v>
+        <v>27</v>
       </c>
       <c r="P34" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="Q34" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="R34" t="s">
-        <v>254</v>
+        <v>27</v>
       </c>
       <c r="S34" t="s">
         <v>27</v>
       </c>
       <c r="T34" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="U34" t="s">
-        <v>227</v>
+        <v>27</v>
       </c>
       <c r="V34" t="s">
         <v>27</v>
@@ -15773,55 +15910,55 @@
         <v>27</v>
       </c>
       <c r="X34" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="Y34" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="Z34">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AA34">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AB34">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH34">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI34">
         <v>0</v>
       </c>
       <c r="AJ34">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="AK34">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AL34">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AM34" t="s">
         <v>84</v>
       </c>
       <c r="AN34" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -15833,25 +15970,25 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C35" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D35" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E35" t="s">
         <v>142</v>
       </c>
       <c r="F35">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G35">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -15863,34 +16000,34 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M35" t="s">
         <v>26</v>
       </c>
       <c r="N35" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="O35" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="P35" t="s">
-        <v>216</v>
+        <v>138</v>
       </c>
       <c r="Q35" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="R35" t="s">
-        <v>103</v>
+        <v>254</v>
       </c>
       <c r="S35" t="s">
         <v>27</v>
       </c>
       <c r="T35" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="U35" t="s">
-        <v>27</v>
+        <v>227</v>
       </c>
       <c r="V35" t="s">
         <v>27</v>
@@ -15899,55 +16036,55 @@
         <v>27</v>
       </c>
       <c r="X35" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="Y35" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="Z35">
         <v>20</v>
       </c>
       <c r="AA35">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AB35">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AC35">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AD35">
+        <v>15</v>
+      </c>
+      <c r="AE35">
+        <v>10</v>
+      </c>
+      <c r="AF35">
+        <v>8</v>
+      </c>
+      <c r="AG35">
         <v>5</v>
       </c>
-      <c r="AE35">
+      <c r="AH35">
         <v>5</v>
       </c>
-      <c r="AF35">
-        <v>0</v>
-      </c>
-      <c r="AG35">
-        <v>0</v>
-      </c>
-      <c r="AH35">
-        <v>0</v>
-      </c>
       <c r="AI35">
         <v>0</v>
       </c>
       <c r="AJ35">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AK35">
         <v>10</v>
       </c>
       <c r="AL35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AM35" t="s">
         <v>84</v>
       </c>
       <c r="AN35" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AO35">
         <v>0</v>
@@ -15959,13 +16096,13 @@
         <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="C36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D36" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E36" t="s">
         <v>142</v>
@@ -15974,10 +16111,10 @@
         <v>90</v>
       </c>
       <c r="G36">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="H36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -15995,19 +16132,19 @@
         <v>26</v>
       </c>
       <c r="N36" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="O36" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="P36" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="Q36" t="s">
-        <v>217</v>
+        <v>70</v>
       </c>
       <c r="R36" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="S36" t="s">
         <v>27</v>
@@ -16025,28 +16162,28 @@
         <v>27</v>
       </c>
       <c r="X36" t="s">
-        <v>33</v>
+        <v>211</v>
       </c>
       <c r="Y36" t="s">
-        <v>218</v>
+        <v>27</v>
       </c>
       <c r="Z36">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="AA36">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="AB36">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AC36">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AD36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF36">
         <v>0</v>
@@ -16061,19 +16198,19 @@
         <v>0</v>
       </c>
       <c r="AJ36">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK36">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AL36">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AM36" t="s">
         <v>84</v>
       </c>
       <c r="AN36" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AO36">
         <v>0</v>
@@ -16085,13 +16222,13 @@
         <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>265</v>
       </c>
       <c r="C37" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="D37" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="E37" t="s">
         <v>142</v>
@@ -16100,37 +16237,37 @@
         <v>90</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M37" t="s">
         <v>26</v>
       </c>
       <c r="N37" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="O37" t="s">
-        <v>27</v>
+        <v>230</v>
       </c>
       <c r="P37" t="s">
-        <v>27</v>
+        <v>231</v>
       </c>
       <c r="Q37" t="s">
-        <v>27</v>
+        <v>217</v>
       </c>
       <c r="R37" t="s">
         <v>27</v>
@@ -16151,25 +16288,25 @@
         <v>27</v>
       </c>
       <c r="X37" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="Y37" t="s">
-        <v>27</v>
+        <v>218</v>
       </c>
       <c r="Z37">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AA37">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AB37">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AC37">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE37">
         <v>0</v>
@@ -16187,19 +16324,19 @@
         <v>0</v>
       </c>
       <c r="AJ37">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AK37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM37" t="s">
         <v>84</v>
       </c>
       <c r="AN37" t="s">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="AO37">
         <v>0</v>
@@ -16214,10 +16351,10 @@
         <v>40</v>
       </c>
       <c r="C38" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D38" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E38" t="s">
         <v>142</v>
@@ -16235,7 +16372,7 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -16328,6 +16465,132 @@
         <v>186</v>
       </c>
       <c r="AO38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:41" x14ac:dyDescent="0.4">
+      <c r="A39">
+        <f t="shared" si="1"/>
+        <v>137</v>
+      </c>
+      <c r="B39" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" t="s">
+        <v>160</v>
+      </c>
+      <c r="D39" t="s">
+        <v>161</v>
+      </c>
+      <c r="E39" t="s">
+        <v>142</v>
+      </c>
+      <c r="F39">
+        <v>90</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>9999</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>10</v>
+      </c>
+      <c r="M39" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39" t="s">
+        <v>27</v>
+      </c>
+      <c r="O39" t="s">
+        <v>27</v>
+      </c>
+      <c r="P39" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>27</v>
+      </c>
+      <c r="R39" t="s">
+        <v>27</v>
+      </c>
+      <c r="S39" t="s">
+        <v>27</v>
+      </c>
+      <c r="T39" t="s">
+        <v>27</v>
+      </c>
+      <c r="U39" t="s">
+        <v>27</v>
+      </c>
+      <c r="V39" t="s">
+        <v>27</v>
+      </c>
+      <c r="W39" t="s">
+        <v>27</v>
+      </c>
+      <c r="X39" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z39">
+        <v>60</v>
+      </c>
+      <c r="AA39">
+        <v>25</v>
+      </c>
+      <c r="AB39">
+        <v>12</v>
+      </c>
+      <c r="AC39">
+        <v>3</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39">
+        <v>0</v>
+      </c>
+      <c r="AI39">
+        <v>0</v>
+      </c>
+      <c r="AJ39">
+        <v>95</v>
+      </c>
+      <c r="AK39">
+        <v>5</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN39" t="s">
+        <v>186</v>
+      </c>
+      <c r="AO39">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F21C0C-83AC-4654-8036-5FAA671E801D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD436F1-7C2D-4F74-8789-A298F82FE396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="885" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2625" yWindow="1425" windowWidth="25560" windowHeight="14355" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -10222,10 +10222,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AB28">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AC28">
         <v>7</v>
@@ -15163,10 +15163,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AB28">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AC28">
         <v>7</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD436F1-7C2D-4F74-8789-A298F82FE396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D551DAFB-FA43-4A6D-B5E7-953F9C493D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2625" yWindow="1425" windowWidth="25560" windowHeight="14355" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2835" yWindow="765" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D551DAFB-FA43-4A6D-B5E7-953F9C493D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2959D7C2-6270-4F18-98FF-2FB2DF800729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="765" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2959D7C2-6270-4F18-98FF-2FB2DF800729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56743254-A9EF-45D2-89DE-60AA6D0B4003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14355" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56743254-A9EF-45D2-89DE-60AA6D0B4003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28B4E9F-89A8-4E2C-9525-20E39568A2B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14355" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2355" yWindow="1215" windowWidth="25560" windowHeight="14355" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28B4E9F-89A8-4E2C-9525-20E39568A2B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD10F57D-CEA4-4D6F-8CDA-000E0A21E429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2355" yWindow="1215" windowWidth="25560" windowHeight="14355" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1560" yWindow="1245" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD10F57D-CEA4-4D6F-8CDA-000E0A21E429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592059F9-9E31-4D9F-B154-FF7DD6EB2F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1245" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -10477,16 +10477,16 @@
         <v>30</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC30">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AD30">
         <v>13</v>
       </c>
       <c r="AE30">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AF30">
         <v>8</v>
@@ -15418,16 +15418,16 @@
         <v>30</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC30">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AD30">
         <v>13</v>
       </c>
       <c r="AE30">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AF30">
         <v>8</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533FADC7-B566-4B8D-93A7-CD86743FCE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5DDA325-5717-43F6-B142-BE785312E34A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="585" windowWidth="25485" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2985" yWindow="1140" windowWidth="25485" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -8430,7 +8430,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -8559,7 +8559,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -8688,7 +8688,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -8946,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -9333,7 +9333,7 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -13359,7 +13359,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -13488,7 +13488,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -13617,7 +13617,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -13746,7 +13746,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -14004,7 +14004,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -14391,7 +14391,7 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K20">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5DDA325-5717-43F6-B142-BE785312E34A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611C729D-56DE-4487-8B5C-472163456103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2985" yWindow="1140" windowWidth="25485" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1680" yWindow="930" windowWidth="25485" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="299">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -1751,6 +1751,14 @@
   </si>
   <si>
     <t>place_catLV</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sodaisland_mini_icon</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>winter_town_mini_icon</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -9051,7 +9059,7 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>251</v>
+        <v>297</v>
       </c>
       <c r="C18" t="s">
         <v>288</v>
@@ -9825,7 +9833,7 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>252</v>
+        <v>298</v>
       </c>
       <c r="C24" t="s">
         <v>294</v>
@@ -14109,7 +14117,7 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>251</v>
+        <v>297</v>
       </c>
       <c r="C18" t="s">
         <v>288</v>
@@ -14883,7 +14891,7 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>252</v>
+        <v>298</v>
       </c>
       <c r="C24" t="s">
         <v>294</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611C729D-56DE-4487-8B5C-472163456103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BD04F9-B6FF-48D2-92EE-31E69A39EECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="930" windowWidth="25485" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1530" yWindow="630" windowWidth="25485" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BD04F9-B6FF-48D2-92EE-31E69A39EECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1521645-2F52-4F0B-8DEF-442CB89FA927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="630" windowWidth="25485" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1845" yWindow="1140" windowWidth="25485" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -10787,7 +10787,7 @@
         <v>27</v>
       </c>
       <c r="S31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T31" t="s">
         <v>27</v>
@@ -10823,10 +10823,10 @@
         <v>23</v>
       </c>
       <c r="AE31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AG31">
         <v>0</v>
@@ -11528,7 +11528,7 @@
         <v>600</v>
       </c>
       <c r="H37">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -15845,7 +15845,7 @@
         <v>27</v>
       </c>
       <c r="S31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T31" t="s">
         <v>27</v>
@@ -15881,10 +15881,10 @@
         <v>23</v>
       </c>
       <c r="AE31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AG31">
         <v>0</v>
@@ -16586,7 +16586,7 @@
         <v>600</v>
       </c>
       <c r="H37">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I37">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1521645-2F52-4F0B-8DEF-442CB89FA927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DCAA94-60F7-41D1-85DC-4F36FD45B84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1845" yWindow="1140" windowWidth="25485" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3090" yWindow="1215" windowWidth="25485" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2296" uniqueCount="302">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -1759,6 +1759,24 @@
   </si>
   <si>
     <t>winter_town_mini_icon</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>秘密の花園</t>
+    <rPh sb="0" eb="2">
+      <t>ヒミツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハナゾノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Secret_Garden</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MapBG_SecretGarden</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -6842,7 +6860,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAAE7BC7-74FC-4400-A474-EA5B977D362B}">
-  <dimension ref="A1:AP39"/>
+  <dimension ref="A1:AP40"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -7507,7 +7525,7 @@
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.4">
       <c r="A6">
-        <f t="shared" ref="A6:A39" si="0">ROW()-2+100</f>
+        <f t="shared" ref="A6:A40" si="0">ROW()-2+100</f>
         <v>104</v>
       </c>
       <c r="B6" t="s">
@@ -10736,25 +10754,25 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C31" t="s">
-        <v>205</v>
+        <v>300</v>
       </c>
       <c r="D31" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="E31" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F31">
         <v>30</v>
       </c>
       <c r="G31">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -10766,10 +10784,10 @@
         <v>1</v>
       </c>
       <c r="L31">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N31" t="s">
         <v>26</v>
@@ -10778,16 +10796,16 @@
         <v>72</v>
       </c>
       <c r="P31" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="Q31" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="R31" t="s">
         <v>27</v>
       </c>
       <c r="S31" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="T31" t="s">
         <v>27</v>
@@ -10805,28 +10823,28 @@
         <v>27</v>
       </c>
       <c r="Y31" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="Z31" t="s">
-        <v>228</v>
+        <v>27</v>
       </c>
       <c r="AA31">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AB31">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="AC31">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="AD31">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AG31">
         <v>0</v>
@@ -10841,19 +10859,19 @@
         <v>0</v>
       </c>
       <c r="AK31">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AL31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AM31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AN31" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="AO31" t="s">
-        <v>233</v>
+        <v>301</v>
       </c>
       <c r="AP31">
         <v>0</v>
@@ -10865,25 +10883,25 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="C32" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D32" t="s">
-        <v>197</v>
+        <v>267</v>
       </c>
       <c r="E32" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="F32">
         <v>30</v>
       </c>
       <c r="G32">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -10895,10 +10913,10 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M32">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N32" t="s">
         <v>26</v>
@@ -10907,25 +10925,25 @@
         <v>72</v>
       </c>
       <c r="P32" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="Q32" t="s">
         <v>108</v>
       </c>
       <c r="R32" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="S32" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="T32" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="U32" t="s">
-        <v>221</v>
+        <v>27</v>
       </c>
       <c r="V32" t="s">
-        <v>247</v>
+        <v>27</v>
       </c>
       <c r="W32" t="s">
         <v>27</v>
@@ -10934,55 +10952,55 @@
         <v>27</v>
       </c>
       <c r="Y32" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="Z32" t="s">
-        <v>111</v>
+        <v>228</v>
       </c>
       <c r="AA32">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AB32">
+        <v>25</v>
+      </c>
+      <c r="AC32">
+        <v>16</v>
+      </c>
+      <c r="AD32">
+        <v>23</v>
+      </c>
+      <c r="AE32">
+        <v>6</v>
+      </c>
+      <c r="AF32">
         <v>5</v>
       </c>
-      <c r="AC32">
-        <v>20</v>
-      </c>
-      <c r="AD32">
-        <v>12</v>
-      </c>
-      <c r="AE32">
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>94</v>
+      </c>
+      <c r="AL32">
+        <v>1</v>
+      </c>
+      <c r="AM32">
         <v>5</v>
-      </c>
-      <c r="AF32">
-        <v>10</v>
-      </c>
-      <c r="AG32">
-        <v>13</v>
-      </c>
-      <c r="AH32">
-        <v>10</v>
-      </c>
-      <c r="AI32">
-        <v>5</v>
-      </c>
-      <c r="AJ32">
-        <v>0</v>
-      </c>
-      <c r="AK32">
-        <v>83</v>
-      </c>
-      <c r="AL32">
-        <v>16</v>
-      </c>
-      <c r="AM32">
-        <v>1</v>
       </c>
       <c r="AN32" t="s">
         <v>84</v>
       </c>
       <c r="AO32" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AP32">
         <v>0</v>
@@ -10994,25 +11012,25 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="C33" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="D33" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E33" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F33">
         <v>30</v>
       </c>
       <c r="G33">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -11027,34 +11045,34 @@
         <v>20</v>
       </c>
       <c r="M33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N33" t="s">
         <v>26</v>
       </c>
       <c r="O33" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
       <c r="P33" t="s">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="Q33" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="R33" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="S33" t="s">
-        <v>222</v>
+        <v>112</v>
       </c>
       <c r="T33" t="s">
-        <v>226</v>
+        <v>74</v>
       </c>
       <c r="U33" t="s">
-        <v>27</v>
+        <v>221</v>
       </c>
       <c r="V33" t="s">
-        <v>27</v>
+        <v>247</v>
       </c>
       <c r="W33" t="s">
         <v>27</v>
@@ -11063,22 +11081,22 @@
         <v>27</v>
       </c>
       <c r="Y33" t="s">
-        <v>218</v>
+        <v>72</v>
       </c>
       <c r="Z33" t="s">
-        <v>220</v>
+        <v>111</v>
       </c>
       <c r="AA33">
         <v>20</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC33">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="AD33">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE33">
         <v>5</v>
@@ -11087,31 +11105,31 @@
         <v>10</v>
       </c>
       <c r="AG33">
+        <v>13</v>
+      </c>
+      <c r="AH33">
         <v>10</v>
       </c>
-      <c r="AH33">
-        <v>0</v>
-      </c>
       <c r="AI33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ33">
         <v>0</v>
       </c>
       <c r="AK33">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AL33">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="AM33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AN33" t="s">
         <v>84</v>
       </c>
       <c r="AO33" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP33">
         <v>0</v>
@@ -11123,25 +11141,25 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C34" t="s">
-        <v>255</v>
+        <v>42</v>
       </c>
       <c r="D34" t="s">
-        <v>257</v>
+        <v>201</v>
       </c>
       <c r="E34" t="s">
-        <v>256</v>
+        <v>50</v>
       </c>
       <c r="F34">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -11156,28 +11174,28 @@
         <v>20</v>
       </c>
       <c r="M34">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N34" t="s">
         <v>26</v>
       </c>
       <c r="O34" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="P34" t="s">
-        <v>27</v>
+        <v>220</v>
       </c>
       <c r="Q34" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R34" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="S34" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="T34" t="s">
-        <v>27</v>
+        <v>226</v>
       </c>
       <c r="U34" t="s">
         <v>27</v>
@@ -11192,31 +11210,31 @@
         <v>27</v>
       </c>
       <c r="Y34" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Z34" t="s">
-        <v>27</v>
+        <v>220</v>
       </c>
       <c r="AA34">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AB34">
+        <v>10</v>
+      </c>
+      <c r="AC34">
         <v>35</v>
       </c>
-      <c r="AC34">
-        <v>0</v>
-      </c>
       <c r="AD34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH34">
         <v>0</v>
@@ -11228,19 +11246,19 @@
         <v>0</v>
       </c>
       <c r="AK34">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="AL34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AN34" t="s">
         <v>84</v>
       </c>
       <c r="AO34" t="s">
-        <v>258</v>
+        <v>224</v>
       </c>
       <c r="AP34">
         <v>0</v>
@@ -11252,25 +11270,25 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C35" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="D35" t="s">
-        <v>198</v>
+        <v>257</v>
       </c>
       <c r="E35" t="s">
-        <v>116</v>
+        <v>256</v>
       </c>
       <c r="F35">
         <v>60</v>
       </c>
       <c r="G35">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -11282,37 +11300,37 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N35" t="s">
         <v>26</v>
       </c>
       <c r="O35" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="P35" t="s">
-        <v>215</v>
+        <v>27</v>
       </c>
       <c r="Q35" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="R35" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="S35" t="s">
-        <v>254</v>
+        <v>27</v>
       </c>
       <c r="T35" t="s">
         <v>27</v>
       </c>
       <c r="U35" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="V35" t="s">
-        <v>227</v>
+        <v>27</v>
       </c>
       <c r="W35" t="s">
         <v>27</v>
@@ -11321,55 +11339,55 @@
         <v>27</v>
       </c>
       <c r="Y35" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="Z35" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="AA35">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AB35">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AC35">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG35">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AH35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ35">
         <v>0</v>
       </c>
       <c r="AK35">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="AL35">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AM35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AN35" t="s">
         <v>84</v>
       </c>
       <c r="AO35" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="AP35">
         <v>0</v>
@@ -11381,25 +11399,25 @@
         <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C36" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D36" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E36" t="s">
         <v>116</v>
       </c>
       <c r="F36">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G36">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -11411,37 +11429,37 @@
         <v>1</v>
       </c>
       <c r="L36">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M36">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N36" t="s">
         <v>26</v>
       </c>
       <c r="O36" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="P36" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q36" t="s">
-        <v>216</v>
+        <v>138</v>
       </c>
       <c r="R36" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="S36" t="s">
-        <v>103</v>
+        <v>254</v>
       </c>
       <c r="T36" t="s">
         <v>27</v>
       </c>
       <c r="U36" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="V36" t="s">
-        <v>27</v>
+        <v>227</v>
       </c>
       <c r="W36" t="s">
         <v>27</v>
@@ -11450,55 +11468,55 @@
         <v>27</v>
       </c>
       <c r="Y36" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="Z36" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="AA36">
         <v>20</v>
       </c>
       <c r="AB36">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AC36">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AD36">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE36">
+        <v>15</v>
+      </c>
+      <c r="AF36">
+        <v>10</v>
+      </c>
+      <c r="AG36">
+        <v>8</v>
+      </c>
+      <c r="AH36">
         <v>5</v>
       </c>
-      <c r="AF36">
+      <c r="AI36">
         <v>5</v>
       </c>
-      <c r="AG36">
-        <v>0</v>
-      </c>
-      <c r="AH36">
-        <v>0</v>
-      </c>
-      <c r="AI36">
-        <v>0</v>
-      </c>
       <c r="AJ36">
         <v>0</v>
       </c>
       <c r="AK36">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AL36">
         <v>10</v>
       </c>
       <c r="AM36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AN36" t="s">
         <v>84</v>
       </c>
       <c r="AO36" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AP36">
         <v>0</v>
@@ -11510,25 +11528,25 @@
         <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="C37" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D37" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E37" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F37">
         <v>90</v>
       </c>
       <c r="G37">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="H37">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -11543,25 +11561,25 @@
         <v>40</v>
       </c>
       <c r="M37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N37" t="s">
         <v>26</v>
       </c>
       <c r="O37" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="P37" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="Q37" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="R37" t="s">
-        <v>217</v>
+        <v>70</v>
       </c>
       <c r="S37" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="T37" t="s">
         <v>27</v>
@@ -11579,28 +11597,28 @@
         <v>27</v>
       </c>
       <c r="Y37" t="s">
-        <v>33</v>
+        <v>211</v>
       </c>
       <c r="Z37" t="s">
-        <v>266</v>
+        <v>27</v>
       </c>
       <c r="AA37">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="AB37">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="AC37">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AD37">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AE37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG37">
         <v>0</v>
@@ -11615,19 +11633,19 @@
         <v>0</v>
       </c>
       <c r="AK37">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AL37">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AM37">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AN37" t="s">
         <v>84</v>
       </c>
       <c r="AO37" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AP37">
         <v>0</v>
@@ -11639,55 +11657,55 @@
         <v>136</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>265</v>
       </c>
       <c r="C38" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="E38" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F38">
         <v>90</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I38">
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N38" t="s">
         <v>26</v>
       </c>
       <c r="O38" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="P38" t="s">
-        <v>27</v>
+        <v>230</v>
       </c>
       <c r="Q38" t="s">
-        <v>27</v>
+        <v>231</v>
       </c>
       <c r="R38" t="s">
-        <v>27</v>
+        <v>217</v>
       </c>
       <c r="S38" t="s">
         <v>27</v>
@@ -11708,25 +11726,25 @@
         <v>27</v>
       </c>
       <c r="Y38" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="Z38" t="s">
-        <v>27</v>
+        <v>266</v>
       </c>
       <c r="AA38">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AB38">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AC38">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AD38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF38">
         <v>0</v>
@@ -11744,19 +11762,19 @@
         <v>0</v>
       </c>
       <c r="AK38">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AL38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN38" t="s">
         <v>84</v>
       </c>
       <c r="AO38" t="s">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="AP38">
         <v>0</v>
@@ -11771,10 +11789,10 @@
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D39" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E39" t="s">
         <v>48</v>
@@ -11792,7 +11810,7 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -11888,6 +11906,135 @@
         <v>186</v>
       </c>
       <c r="AP39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:42" x14ac:dyDescent="0.4">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>138</v>
+      </c>
+      <c r="B40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40" t="s">
+        <v>48</v>
+      </c>
+      <c r="F40">
+        <v>90</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>9999</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>10</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>26</v>
+      </c>
+      <c r="O40" t="s">
+        <v>27</v>
+      </c>
+      <c r="P40" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>27</v>
+      </c>
+      <c r="R40" t="s">
+        <v>27</v>
+      </c>
+      <c r="S40" t="s">
+        <v>27</v>
+      </c>
+      <c r="T40" t="s">
+        <v>27</v>
+      </c>
+      <c r="U40" t="s">
+        <v>27</v>
+      </c>
+      <c r="V40" t="s">
+        <v>27</v>
+      </c>
+      <c r="W40" t="s">
+        <v>27</v>
+      </c>
+      <c r="X40" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA40">
+        <v>60</v>
+      </c>
+      <c r="AB40">
+        <v>25</v>
+      </c>
+      <c r="AC40">
+        <v>12</v>
+      </c>
+      <c r="AD40">
+        <v>3</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
+      <c r="AH40">
+        <v>0</v>
+      </c>
+      <c r="AI40">
+        <v>0</v>
+      </c>
+      <c r="AJ40">
+        <v>0</v>
+      </c>
+      <c r="AK40">
+        <v>95</v>
+      </c>
+      <c r="AL40">
+        <v>5</v>
+      </c>
+      <c r="AM40">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO40" t="s">
+        <v>186</v>
+      </c>
+      <c r="AP40">
         <v>1</v>
       </c>
     </row>
@@ -11900,7 +12047,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAD14E5B-6BFE-4D20-B771-5A2DB6950621}">
-  <dimension ref="A1:AP39"/>
+  <dimension ref="A1:AP40"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -13081,7 +13228,7 @@
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.4">
       <c r="A10">
-        <f t="shared" ref="A10:A39" si="1">ROW()-2+100</f>
+        <f t="shared" ref="A10:A40" si="1">ROW()-2+100</f>
         <v>108</v>
       </c>
       <c r="B10" t="s">
@@ -15794,13 +15941,13 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C31" t="s">
-        <v>205</v>
+        <v>300</v>
       </c>
       <c r="D31" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="E31" t="s">
         <v>142</v>
@@ -15809,10 +15956,10 @@
         <v>30</v>
       </c>
       <c r="G31">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -15824,10 +15971,10 @@
         <v>1</v>
       </c>
       <c r="L31">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N31" t="s">
         <v>26</v>
@@ -15836,16 +15983,16 @@
         <v>72</v>
       </c>
       <c r="P31" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="Q31" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="R31" t="s">
         <v>27</v>
       </c>
       <c r="S31" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="T31" t="s">
         <v>27</v>
@@ -15863,28 +16010,28 @@
         <v>27</v>
       </c>
       <c r="Y31" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="Z31" t="s">
-        <v>228</v>
+        <v>27</v>
       </c>
       <c r="AA31">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AB31">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="AC31">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="AD31">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AG31">
         <v>0</v>
@@ -15899,19 +16046,19 @@
         <v>0</v>
       </c>
       <c r="AK31">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AL31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AM31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AN31" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="AO31" t="s">
-        <v>233</v>
+        <v>301</v>
       </c>
       <c r="AP31">
         <v>0</v>
@@ -15923,13 +16070,13 @@
         <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="C32" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D32" t="s">
-        <v>197</v>
+        <v>267</v>
       </c>
       <c r="E32" t="s">
         <v>142</v>
@@ -15938,10 +16085,10 @@
         <v>30</v>
       </c>
       <c r="G32">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -15953,10 +16100,10 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M32">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N32" t="s">
         <v>26</v>
@@ -15965,25 +16112,25 @@
         <v>72</v>
       </c>
       <c r="P32" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="Q32" t="s">
         <v>108</v>
       </c>
       <c r="R32" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="S32" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="T32" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="U32" t="s">
-        <v>221</v>
+        <v>27</v>
       </c>
       <c r="V32" t="s">
-        <v>247</v>
+        <v>27</v>
       </c>
       <c r="W32" t="s">
         <v>27</v>
@@ -15992,55 +16139,55 @@
         <v>27</v>
       </c>
       <c r="Y32" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="Z32" t="s">
-        <v>111</v>
+        <v>228</v>
       </c>
       <c r="AA32">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AB32">
+        <v>25</v>
+      </c>
+      <c r="AC32">
+        <v>16</v>
+      </c>
+      <c r="AD32">
+        <v>23</v>
+      </c>
+      <c r="AE32">
+        <v>6</v>
+      </c>
+      <c r="AF32">
         <v>5</v>
       </c>
-      <c r="AC32">
-        <v>20</v>
-      </c>
-      <c r="AD32">
-        <v>12</v>
-      </c>
-      <c r="AE32">
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>94</v>
+      </c>
+      <c r="AL32">
+        <v>1</v>
+      </c>
+      <c r="AM32">
         <v>5</v>
-      </c>
-      <c r="AF32">
-        <v>10</v>
-      </c>
-      <c r="AG32">
-        <v>13</v>
-      </c>
-      <c r="AH32">
-        <v>10</v>
-      </c>
-      <c r="AI32">
-        <v>5</v>
-      </c>
-      <c r="AJ32">
-        <v>0</v>
-      </c>
-      <c r="AK32">
-        <v>83</v>
-      </c>
-      <c r="AL32">
-        <v>16</v>
-      </c>
-      <c r="AM32">
-        <v>1</v>
       </c>
       <c r="AN32" t="s">
         <v>84</v>
       </c>
       <c r="AO32" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AP32">
         <v>0</v>
@@ -16052,13 +16199,13 @@
         <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="C33" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="D33" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E33" t="s">
         <v>142</v>
@@ -16067,10 +16214,10 @@
         <v>30</v>
       </c>
       <c r="G33">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -16085,34 +16232,34 @@
         <v>20</v>
       </c>
       <c r="M33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N33" t="s">
         <v>26</v>
       </c>
       <c r="O33" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
       <c r="P33" t="s">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="Q33" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="R33" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="S33" t="s">
-        <v>222</v>
+        <v>112</v>
       </c>
       <c r="T33" t="s">
-        <v>226</v>
+        <v>74</v>
       </c>
       <c r="U33" t="s">
-        <v>27</v>
+        <v>221</v>
       </c>
       <c r="V33" t="s">
-        <v>27</v>
+        <v>247</v>
       </c>
       <c r="W33" t="s">
         <v>27</v>
@@ -16121,22 +16268,22 @@
         <v>27</v>
       </c>
       <c r="Y33" t="s">
-        <v>218</v>
+        <v>72</v>
       </c>
       <c r="Z33" t="s">
-        <v>220</v>
+        <v>111</v>
       </c>
       <c r="AA33">
         <v>20</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC33">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="AD33">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE33">
         <v>5</v>
@@ -16145,31 +16292,31 @@
         <v>10</v>
       </c>
       <c r="AG33">
+        <v>13</v>
+      </c>
+      <c r="AH33">
         <v>10</v>
       </c>
-      <c r="AH33">
-        <v>0</v>
-      </c>
       <c r="AI33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ33">
         <v>0</v>
       </c>
       <c r="AK33">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AL33">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="AM33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AN33" t="s">
         <v>84</v>
       </c>
       <c r="AO33" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP33">
         <v>0</v>
@@ -16181,25 +16328,25 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C34" t="s">
-        <v>255</v>
+        <v>42</v>
       </c>
       <c r="D34" t="s">
-        <v>257</v>
+        <v>201</v>
       </c>
       <c r="E34" t="s">
         <v>142</v>
       </c>
       <c r="F34">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -16214,28 +16361,28 @@
         <v>20</v>
       </c>
       <c r="M34">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N34" t="s">
         <v>26</v>
       </c>
       <c r="O34" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="P34" t="s">
-        <v>27</v>
+        <v>220</v>
       </c>
       <c r="Q34" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R34" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="S34" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="T34" t="s">
-        <v>27</v>
+        <v>226</v>
       </c>
       <c r="U34" t="s">
         <v>27</v>
@@ -16250,31 +16397,31 @@
         <v>27</v>
       </c>
       <c r="Y34" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Z34" t="s">
-        <v>27</v>
+        <v>220</v>
       </c>
       <c r="AA34">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AB34">
+        <v>10</v>
+      </c>
+      <c r="AC34">
         <v>35</v>
       </c>
-      <c r="AC34">
-        <v>0</v>
-      </c>
       <c r="AD34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH34">
         <v>0</v>
@@ -16286,19 +16433,19 @@
         <v>0</v>
       </c>
       <c r="AK34">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="AL34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AN34" t="s">
         <v>84</v>
       </c>
       <c r="AO34" t="s">
-        <v>258</v>
+        <v>224</v>
       </c>
       <c r="AP34">
         <v>0</v>
@@ -16310,13 +16457,13 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C35" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="D35" t="s">
-        <v>198</v>
+        <v>257</v>
       </c>
       <c r="E35" t="s">
         <v>142</v>
@@ -16325,10 +16472,10 @@
         <v>60</v>
       </c>
       <c r="G35">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -16340,37 +16487,37 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N35" t="s">
         <v>26</v>
       </c>
       <c r="O35" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="P35" t="s">
-        <v>215</v>
+        <v>27</v>
       </c>
       <c r="Q35" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="R35" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="S35" t="s">
-        <v>254</v>
+        <v>27</v>
       </c>
       <c r="T35" t="s">
         <v>27</v>
       </c>
       <c r="U35" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="V35" t="s">
-        <v>227</v>
+        <v>27</v>
       </c>
       <c r="W35" t="s">
         <v>27</v>
@@ -16379,55 +16526,55 @@
         <v>27</v>
       </c>
       <c r="Y35" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="Z35" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="AA35">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AB35">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AC35">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG35">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AH35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ35">
         <v>0</v>
       </c>
       <c r="AK35">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="AL35">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AM35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AN35" t="s">
         <v>84</v>
       </c>
       <c r="AO35" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="AP35">
         <v>0</v>
@@ -16439,25 +16586,25 @@
         <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C36" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D36" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E36" t="s">
         <v>142</v>
       </c>
       <c r="F36">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G36">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -16469,37 +16616,37 @@
         <v>1</v>
       </c>
       <c r="L36">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M36">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N36" t="s">
         <v>26</v>
       </c>
       <c r="O36" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="P36" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q36" t="s">
-        <v>216</v>
+        <v>138</v>
       </c>
       <c r="R36" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="S36" t="s">
-        <v>103</v>
+        <v>254</v>
       </c>
       <c r="T36" t="s">
         <v>27</v>
       </c>
       <c r="U36" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="V36" t="s">
-        <v>27</v>
+        <v>227</v>
       </c>
       <c r="W36" t="s">
         <v>27</v>
@@ -16508,55 +16655,55 @@
         <v>27</v>
       </c>
       <c r="Y36" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="Z36" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="AA36">
         <v>20</v>
       </c>
       <c r="AB36">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AC36">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AD36">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE36">
+        <v>15</v>
+      </c>
+      <c r="AF36">
+        <v>10</v>
+      </c>
+      <c r="AG36">
+        <v>8</v>
+      </c>
+      <c r="AH36">
         <v>5</v>
       </c>
-      <c r="AF36">
+      <c r="AI36">
         <v>5</v>
       </c>
-      <c r="AG36">
-        <v>0</v>
-      </c>
-      <c r="AH36">
-        <v>0</v>
-      </c>
-      <c r="AI36">
-        <v>0</v>
-      </c>
       <c r="AJ36">
         <v>0</v>
       </c>
       <c r="AK36">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AL36">
         <v>10</v>
       </c>
       <c r="AM36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AN36" t="s">
         <v>84</v>
       </c>
       <c r="AO36" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AP36">
         <v>0</v>
@@ -16568,13 +16715,13 @@
         <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="C37" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D37" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E37" t="s">
         <v>142</v>
@@ -16583,10 +16730,10 @@
         <v>90</v>
       </c>
       <c r="G37">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="H37">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -16601,25 +16748,25 @@
         <v>40</v>
       </c>
       <c r="M37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N37" t="s">
         <v>26</v>
       </c>
       <c r="O37" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="P37" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="Q37" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="R37" t="s">
-        <v>217</v>
+        <v>70</v>
       </c>
       <c r="S37" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="T37" t="s">
         <v>27</v>
@@ -16637,28 +16784,28 @@
         <v>27</v>
       </c>
       <c r="Y37" t="s">
-        <v>33</v>
+        <v>211</v>
       </c>
       <c r="Z37" t="s">
-        <v>266</v>
+        <v>27</v>
       </c>
       <c r="AA37">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="AB37">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="AC37">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AD37">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AE37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG37">
         <v>0</v>
@@ -16673,19 +16820,19 @@
         <v>0</v>
       </c>
       <c r="AK37">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AL37">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AM37">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AN37" t="s">
         <v>84</v>
       </c>
       <c r="AO37" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AP37">
         <v>0</v>
@@ -16697,13 +16844,13 @@
         <v>136</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>265</v>
       </c>
       <c r="C38" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="E38" t="s">
         <v>142</v>
@@ -16712,40 +16859,40 @@
         <v>90</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I38">
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N38" t="s">
         <v>26</v>
       </c>
       <c r="O38" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="P38" t="s">
-        <v>27</v>
+        <v>230</v>
       </c>
       <c r="Q38" t="s">
-        <v>27</v>
+        <v>231</v>
       </c>
       <c r="R38" t="s">
-        <v>27</v>
+        <v>217</v>
       </c>
       <c r="S38" t="s">
         <v>27</v>
@@ -16766,25 +16913,25 @@
         <v>27</v>
       </c>
       <c r="Y38" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="Z38" t="s">
-        <v>27</v>
+        <v>266</v>
       </c>
       <c r="AA38">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AB38">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AC38">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AD38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF38">
         <v>0</v>
@@ -16802,19 +16949,19 @@
         <v>0</v>
       </c>
       <c r="AK38">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AL38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN38" t="s">
         <v>84</v>
       </c>
       <c r="AO38" t="s">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="AP38">
         <v>0</v>
@@ -16829,10 +16976,10 @@
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D39" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E39" t="s">
         <v>142</v>
@@ -16850,7 +16997,7 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -16946,6 +17093,135 @@
         <v>186</v>
       </c>
       <c r="AP39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:42" x14ac:dyDescent="0.4">
+      <c r="A40">
+        <f t="shared" si="1"/>
+        <v>138</v>
+      </c>
+      <c r="B40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40" t="s">
+        <v>142</v>
+      </c>
+      <c r="F40">
+        <v>90</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>9999</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>10</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>26</v>
+      </c>
+      <c r="O40" t="s">
+        <v>27</v>
+      </c>
+      <c r="P40" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>27</v>
+      </c>
+      <c r="R40" t="s">
+        <v>27</v>
+      </c>
+      <c r="S40" t="s">
+        <v>27</v>
+      </c>
+      <c r="T40" t="s">
+        <v>27</v>
+      </c>
+      <c r="U40" t="s">
+        <v>27</v>
+      </c>
+      <c r="V40" t="s">
+        <v>27</v>
+      </c>
+      <c r="W40" t="s">
+        <v>27</v>
+      </c>
+      <c r="X40" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA40">
+        <v>60</v>
+      </c>
+      <c r="AB40">
+        <v>25</v>
+      </c>
+      <c r="AC40">
+        <v>12</v>
+      </c>
+      <c r="AD40">
+        <v>3</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
+      <c r="AH40">
+        <v>0</v>
+      </c>
+      <c r="AI40">
+        <v>0</v>
+      </c>
+      <c r="AJ40">
+        <v>0</v>
+      </c>
+      <c r="AK40">
+        <v>95</v>
+      </c>
+      <c r="AL40">
+        <v>5</v>
+      </c>
+      <c r="AM40">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO40" t="s">
+        <v>186</v>
+      </c>
+      <c r="AP40">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DCAA94-60F7-41D1-85DC-4F36FD45B84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D272835-4CE0-4BF4-B6D0-5AC65C5ED417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="1215" windowWidth="25485" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2760" yWindow="1005" windowWidth="25485" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2296" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2296" uniqueCount="303">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -1777,6 +1777,10 @@
   </si>
   <si>
     <t>MapBG_SecretGarden</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>secretgarden_mini_icon</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -10754,7 +10758,7 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="C31" t="s">
         <v>300</v>
@@ -15941,7 +15945,7 @@
         <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="C31" t="s">
         <v>300</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D272835-4CE0-4BF4-B6D0-5AC65C5ED417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578532BB-FA28-4409-85C5-E13516BFF959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="1005" windowWidth="25485" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1755" yWindow="1080" windowWidth="25005" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -10827,7 +10827,7 @@
         <v>27</v>
       </c>
       <c r="Y31" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="Z31" t="s">
         <v>27</v>
@@ -10866,10 +10866,10 @@
         <v>83</v>
       </c>
       <c r="AL31">
+        <v>7</v>
+      </c>
+      <c r="AM31">
         <v>10</v>
-      </c>
-      <c r="AM31">
-        <v>7</v>
       </c>
       <c r="AN31" t="s">
         <v>91</v>
@@ -16014,7 +16014,7 @@
         <v>27</v>
       </c>
       <c r="Y31" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="Z31" t="s">
         <v>27</v>
@@ -16053,10 +16053,10 @@
         <v>83</v>
       </c>
       <c r="AL31">
+        <v>7</v>
+      </c>
+      <c r="AM31">
         <v>10</v>
-      </c>
-      <c r="AM31">
-        <v>7</v>
       </c>
       <c r="AN31" t="s">
         <v>91</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578532BB-FA28-4409-85C5-E13516BFF959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087EC774-1487-4D75-A756-2D1F1B25A390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="1080" windowWidth="25005" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25005" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -11679,7 +11679,7 @@
         <v>600</v>
       </c>
       <c r="H38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -11712,10 +11712,10 @@
         <v>217</v>
       </c>
       <c r="S38" t="s">
-        <v>27</v>
+        <v>208</v>
       </c>
       <c r="T38" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="U38" t="s">
         <v>27</v>
@@ -11730,16 +11730,16 @@
         <v>27</v>
       </c>
       <c r="Y38" t="s">
-        <v>33</v>
+        <v>217</v>
       </c>
       <c r="Z38" t="s">
         <v>266</v>
       </c>
       <c r="AA38">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="AB38">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AC38">
         <v>9</v>
@@ -11748,13 +11748,13 @@
         <v>6</v>
       </c>
       <c r="AE38">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH38">
         <v>0</v>
@@ -16866,7 +16866,7 @@
         <v>600</v>
       </c>
       <c r="H38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -16899,10 +16899,10 @@
         <v>217</v>
       </c>
       <c r="S38" t="s">
-        <v>27</v>
+        <v>208</v>
       </c>
       <c r="T38" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="U38" t="s">
         <v>27</v>
@@ -16917,16 +16917,16 @@
         <v>27</v>
       </c>
       <c r="Y38" t="s">
-        <v>33</v>
+        <v>217</v>
       </c>
       <c r="Z38" t="s">
         <v>266</v>
       </c>
       <c r="AA38">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="AB38">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AC38">
         <v>9</v>
@@ -16935,13 +16935,13 @@
         <v>6</v>
       </c>
       <c r="AE38">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH38">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087EC774-1487-4D75-A756-2D1F1B25A390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA7D026E-55EE-4BDC-A498-E925B0D07F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25005" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1575" yWindow="1215" windowWidth="25005" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -10803,7 +10803,7 @@
         <v>100</v>
       </c>
       <c r="Q31" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="R31" t="s">
         <v>27</v>
@@ -10833,16 +10833,16 @@
         <v>27</v>
       </c>
       <c r="AA31">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="AB31">
         <v>50</v>
       </c>
       <c r="AC31">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE31">
         <v>0</v>
@@ -10863,10 +10863,10 @@
         <v>0</v>
       </c>
       <c r="AK31">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AL31">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AM31">
         <v>10</v>
@@ -15990,7 +15990,7 @@
         <v>100</v>
       </c>
       <c r="Q31" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="R31" t="s">
         <v>27</v>
@@ -16020,16 +16020,16 @@
         <v>27</v>
       </c>
       <c r="AA31">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="AB31">
         <v>50</v>
       </c>
       <c r="AC31">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE31">
         <v>0</v>
@@ -16050,10 +16050,10 @@
         <v>0</v>
       </c>
       <c r="AK31">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AL31">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AM31">
         <v>10</v>

--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mator\OneDrive\ドキュメント\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA7D026E-55EE-4BDC-A498-E925B0D07F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F321FB8F-F115-48E0-BC83-C009996654ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1575" yWindow="1215" windowWidth="25005" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25050" windowHeight="13455" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -7176,7 +7176,7 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -7305,7 +7305,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -7434,7 +7434,7 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -7692,7 +7692,7 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -7821,7 +7821,7 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -7950,7 +7950,7 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -8466,7 +8466,7 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -8595,7 +8595,7 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -8724,7 +8724,7 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -8952,16 +8952,16 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>251</v>
+        <v>122</v>
       </c>
       <c r="C17" t="s">
-        <v>242</v>
+        <v>150</v>
       </c>
       <c r="D17" t="s">
-        <v>239</v>
+        <v>149</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>151</v>
       </c>
       <c r="F17">
         <v>10</v>
@@ -8982,7 +8982,7 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -9027,16 +9027,16 @@
         <v>27</v>
       </c>
       <c r="AA17">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AB17">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AC17">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AD17">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AE17">
         <v>0</v>
@@ -9066,10 +9066,10 @@
         <v>0</v>
       </c>
       <c r="AN17" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AO17" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="AP17">
         <v>0</v>
@@ -9081,16 +9081,16 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C18" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D18" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>151</v>
       </c>
       <c r="F18">
         <v>10</v>
@@ -9111,7 +9111,7 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -9156,16 +9156,16 @@
         <v>27</v>
       </c>
       <c r="AA18">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AB18">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AC18">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AD18">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AE18">
         <v>0</v>
@@ -9195,10 +9195,10 @@
         <v>0</v>
       </c>
       <c r="AN18" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AO18" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="AP18">
         <v>0</v>
@@ -9210,13 +9210,13 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="C19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E19" t="s">
         <v>48</v>
@@ -9240,7 +9240,7 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -9339,13 +9339,13 @@
         <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>252</v>
+        <v>297</v>
       </c>
       <c r="C20" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="D20" t="s">
-        <v>241</v>
+        <v>289</v>
       </c>
       <c r="E20" t="s">
         <v>48</v>
@@ -9369,7 +9369,7 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -9468,19 +9468,19 @@
         <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C21" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D21" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E21" t="s">
         <v>48</v>
       </c>
       <c r="F21">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -9597,16 +9597,16 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>252</v>
       </c>
       <c r="C22" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="D22" t="s">
-        <v>149</v>
+        <v>241</v>
       </c>
       <c r="E22" t="s">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="F22">
         <v>10</v>
@@ -9672,16 +9672,16 @@
         <v>27</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AB22">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AC22">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AD22">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AE22">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AN22" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="AO22" t="s">
-        <v>27</v>
+        <v>186</v>
       </c>
       <c r="AP22">
         <v>0</v>
@@ -9726,13 +9726,13 @@
         <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C23" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E23" t="s">
         <v>151</v>
@@ -9855,19 +9855,19 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="C24" t="s">
-        <v>294</v>
+        <v>246</v>
       </c>
       <c r="D24" t="s">
-        <v>295</v>
+        <v>245</v>
       </c>
       <c r="E24" t="s">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -9885,7 +9885,7 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -9930,16 +9930,16 @@
         <v>27</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AB24">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AC24">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AD24">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AE24">
         <v>0</v>
@@ -9969,10 +9969,10 @@
         <v>0</v>
       </c>
       <c r="AN24" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="AO24" t="s">
-        <v>27</v>
+        <v>186</v>
       </c>
       <c r="AP24">
         <v>0</v>
@@ -10272,7 +10272,7 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -10917,7 +10917,7 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>6</v>
@@ -11046,7 +11046,7 @@
         <v>1</v>
       </c>
       <c r="L33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>3</v>
@@ -11175,7 +11175,7 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>4</v>
@@ -11304,7 +11304,7 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>9</v>
@@ -11433,7 +11433,7 @@
         <v>1</v>
       </c>
       <c r="L36">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M36">
         <v>6</v>
@@ -11562,7 +11562,7 @@
         <v>1</v>
       </c>
       <c r="L37">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="M37">
         <v>8</v>
@@ -11691,7 +11691,7 @@
         <v>1</v>
       </c>
       <c r="L38">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="M38">
         <v>9</v>
@@ -12363,7 +12363,7 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -12492,7 +12492,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -12621,7 +12621,7 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -12879,7 +12879,7 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -13008,7 +13008,7 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -13137,7 +13137,7 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -13653,7 +13653,7 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -13782,7 +13782,7 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -13911,7 +13911,7 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -14139,13 +14139,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>251</v>
+        <v>122</v>
       </c>
       <c r="C17" t="s">
-        <v>242</v>
+        <v>150</v>
       </c>
       <c r="D17" t="s">
-        <v>239</v>
+        <v>149</v>
       </c>
       <c r="E17" t="s">
         <v>142</v>
@@ -14169,7 +14169,7 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -14214,16 +14214,16 @@
         <v>27</v>
       </c>
       <c r="AA17">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AB17">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AC17">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AD17">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AE17">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="AN17" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AO17" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="AP17">
         <v>0</v>
@@ -14268,13 +14268,13 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C18" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D18" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E18" t="s">
         <v>142</v>
@@ -14298,7 +14298,7 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -14343,16 +14343,16 @@
         <v>27</v>
       </c>
       <c r="AA18">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AB18">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AC18">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AD18">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AE18">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="AN18" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AO18" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="AP18">
         <v>0</v>
@@ -14397,13 +14397,13 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="C19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E19" t="s">
         <v>142</v>
@@ -14427,7 +14427,7 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -14526,13 +14526,13 @@
         <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>252</v>
+        <v>297</v>
       </c>
       <c r="C20" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="D20" t="s">
-        <v>241</v>
+        <v>289</v>
       </c>
       <c r="E20" t="s">
         <v>142</v>
@@ -14556,7 +14556,7 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -14655,19 +14655,19 @@
         <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C21" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D21" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E21" t="s">
         <v>142</v>
       </c>
       <c r="F21">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -14784,13 +14784,13 @@
         <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>252</v>
       </c>
       <c r="C22" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="D22" t="s">
-        <v>149</v>
+        <v>241</v>
       </c>
       <c r="E22" t="s">
         <v>142</v>
@@ -14859,16 +14859,16 @@
         <v>27</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AB22">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AC22">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AD22">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AE22">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="AN22" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="AO22" t="s">
-        <v>27</v>
+        <v>186</v>
       </c>
       <c r="AP22">
         <v>0</v>
@@ -14913,13 +14913,13 @@
         <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C23" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E23" t="s">
         <v>142</v>
@@ -15042,19 +15042,19 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="C24" t="s">
-        <v>294</v>
+        <v>246</v>
       </c>
       <c r="D24" t="s">
-        <v>295</v>
+        <v>245</v>
       </c>
       <c r="E24" t="s">
         <v>142</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -15117,16 +15117,16 @@
         <v>27</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AB24">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AC24">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AD24">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AE24">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="AN24" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="AO24" t="s">
-        <v>27</v>
+        <v>186</v>
       </c>
       <c r="AP24">
         <v>0</v>
@@ -15459,7 +15459,7 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -16104,7 +16104,7 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>6</v>
@@ -16233,7 +16233,7 @@
         <v>1</v>
       </c>
       <c r="L33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>3</v>
@@ -16362,7 +16362,7 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>4</v>
@@ -16491,7 +16491,7 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>9</v>
@@ -16620,7 +16620,7 @@
         <v>1</v>
       </c>
       <c r="L36">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M36">
         <v>6</v>
@@ -16749,7 +16749,7 @@
         <v>1</v>
       </c>
       <c r="L37">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="M37">
         <v>8</v>
@@ -16878,7 +16878,7 @@
         <v>1</v>
       </c>
       <c r="L38">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="M38">
         <v>9</v>
